--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13126,10 +13126,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132367475</v>
+        <v>132367449</v>
       </c>
       <c r="B105" t="n">
-        <v>79072</v>
+        <v>57945</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13137,34 +13137,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>384814</v>
+        <v>385133</v>
       </c>
       <c r="R105" t="n">
-        <v>6858214</v>
+        <v>6858066</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13223,10 +13231,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367394</v>
+        <v>132367444</v>
       </c>
       <c r="B106" t="n">
-        <v>79934</v>
+        <v>57945</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13234,34 +13242,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>384969</v>
+        <v>385280</v>
       </c>
       <c r="R106" t="n">
-        <v>6858130</v>
+        <v>6857923</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13320,10 +13336,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367501</v>
+        <v>132367443</v>
       </c>
       <c r="B107" t="n">
-        <v>78322</v>
+        <v>57945</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13331,34 +13347,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>385084</v>
+        <v>385408</v>
       </c>
       <c r="R107" t="n">
-        <v>6858195</v>
+        <v>6857862</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13399,34 +13423,8 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13443,10 +13441,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367449</v>
+        <v>132367475</v>
       </c>
       <c r="B108" t="n">
-        <v>57945</v>
+        <v>79074</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13454,42 +13452,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>385133</v>
+        <v>384814</v>
       </c>
       <c r="R108" t="n">
-        <v>6858066</v>
+        <v>6858214</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13548,10 +13538,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367444</v>
+        <v>132367394</v>
       </c>
       <c r="B109" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13559,42 +13549,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385280</v>
+        <v>384969</v>
       </c>
       <c r="R109" t="n">
-        <v>6857923</v>
+        <v>6858130</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13653,10 +13635,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367443</v>
+        <v>132367501</v>
       </c>
       <c r="B110" t="n">
-        <v>57945</v>
+        <v>78324</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13664,42 +13646,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385408</v>
+        <v>385084</v>
       </c>
       <c r="R110" t="n">
-        <v>6857862</v>
+        <v>6858195</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13740,8 +13714,34 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -13866,7 +13866,7 @@
         <v>132367463</v>
       </c>
       <c r="B112" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>132367466</v>
       </c>
       <c r="B113" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>132367435</v>
       </c>
       <c r="B116" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>132367396</v>
       </c>
       <c r="B120" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14793,10 +14793,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132367470</v>
+        <v>132367428</v>
       </c>
       <c r="B121" t="n">
-        <v>8455</v>
+        <v>57136</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14804,30 +14804,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14837,10 +14836,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>384910</v>
+        <v>385279</v>
       </c>
       <c r="R121" t="n">
-        <v>6858203</v>
+        <v>6858073</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14875,13 +14874,17 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -14900,7 +14903,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132367428</v>
+        <v>132367432</v>
       </c>
       <c r="B122" t="n">
         <v>57136</v>
@@ -14943,10 +14946,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>385279</v>
+        <v>385185</v>
       </c>
       <c r="R122" t="n">
-        <v>6858073</v>
+        <v>6858160</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14979,11 +14982,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15010,10 +15008,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132367432</v>
+        <v>132367470</v>
       </c>
       <c r="B123" t="n">
-        <v>57136</v>
+        <v>8455</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15021,29 +15019,30 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -15053,10 +15052,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>385185</v>
+        <v>384910</v>
       </c>
       <c r="R123" t="n">
-        <v>6858160</v>
+        <v>6858203</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15097,6 +15096,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -15223,7 +15223,7 @@
         <v>132367462</v>
       </c>
       <c r="B125" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>132367464</v>
       </c>
       <c r="B126" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15414,45 +15414,53 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367395</v>
+        <v>132367425</v>
       </c>
       <c r="B127" t="n">
-        <v>79934</v>
+        <v>57136</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>384944</v>
+        <v>385281</v>
       </c>
       <c r="R127" t="n">
-        <v>6858169</v>
+        <v>6858170</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15511,10 +15519,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367446</v>
+        <v>132367395</v>
       </c>
       <c r="B128" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15522,42 +15530,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>385178</v>
+        <v>384944</v>
       </c>
       <c r="R128" t="n">
-        <v>6858121</v>
+        <v>6858169</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15616,7 +15616,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132367453</v>
+        <v>132367446</v>
       </c>
       <c r="B129" t="n">
         <v>57945</v>
@@ -15649,7 +15649,7 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -15659,10 +15659,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>384934</v>
+        <v>385178</v>
       </c>
       <c r="R129" t="n">
-        <v>6858197</v>
+        <v>6858121</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15721,32 +15721,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132367425</v>
+        <v>132367453</v>
       </c>
       <c r="B130" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15754,7 +15754,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -15764,10 +15764,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>385281</v>
+        <v>384934</v>
       </c>
       <c r="R130" t="n">
-        <v>6858170</v>
+        <v>6858197</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15826,10 +15826,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367392</v>
+        <v>132367455</v>
       </c>
       <c r="B131" t="n">
-        <v>79934</v>
+        <v>57945</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15837,34 +15837,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>385102</v>
+        <v>384840</v>
       </c>
       <c r="R131" t="n">
-        <v>6858138</v>
+        <v>6858190</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15923,10 +15931,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367402</v>
+        <v>132367392</v>
       </c>
       <c r="B132" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15958,10 +15966,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385403</v>
+        <v>385102</v>
       </c>
       <c r="R132" t="n">
-        <v>6857836</v>
+        <v>6858138</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16020,10 +16028,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367455</v>
+        <v>132367402</v>
       </c>
       <c r="B133" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16031,42 +16039,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>384840</v>
+        <v>385403</v>
       </c>
       <c r="R133" t="n">
-        <v>6858190</v>
+        <v>6857836</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16235,53 +16235,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367421</v>
+        <v>132367474</v>
       </c>
       <c r="B135" t="n">
-        <v>57136</v>
+        <v>79074</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385249</v>
+        <v>385318</v>
       </c>
       <c r="R135" t="n">
-        <v>6858148</v>
+        <v>6858113</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16340,53 +16332,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367431</v>
+        <v>132367399</v>
       </c>
       <c r="B136" t="n">
-        <v>57136</v>
+        <v>79936</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>384950</v>
+        <v>384873</v>
       </c>
       <c r="R136" t="n">
-        <v>6858169</v>
+        <v>6858080</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16445,7 +16429,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367413</v>
+        <v>132367421</v>
       </c>
       <c r="B137" t="n">
         <v>57136</v>
@@ -16488,10 +16472,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385181</v>
+        <v>385249</v>
       </c>
       <c r="R137" t="n">
-        <v>6858109</v>
+        <v>6858148</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16550,45 +16534,53 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367404</v>
+        <v>132367431</v>
       </c>
       <c r="B138" t="n">
-        <v>79905</v>
+        <v>57136</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>385227</v>
+        <v>384950</v>
       </c>
       <c r="R138" t="n">
-        <v>6857907</v>
+        <v>6858169</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16647,45 +16639,53 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367474</v>
+        <v>132367413</v>
       </c>
       <c r="B139" t="n">
-        <v>79072</v>
+        <v>57136</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>385318</v>
+        <v>385181</v>
       </c>
       <c r="R139" t="n">
-        <v>6858113</v>
+        <v>6858109</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16744,10 +16744,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367399</v>
+        <v>132367404</v>
       </c>
       <c r="B140" t="n">
-        <v>79934</v>
+        <v>79907</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16755,21 +16755,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16779,10 +16779,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>384873</v>
+        <v>385227</v>
       </c>
       <c r="R140" t="n">
-        <v>6858080</v>
+        <v>6857907</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16946,7 +16946,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367469</v>
+        <v>132367468</v>
       </c>
       <c r="B142" t="n">
         <v>8455</v>
@@ -16980,7 +16980,7 @@
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -16990,10 +16990,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>384988</v>
+        <v>384943</v>
       </c>
       <c r="R142" t="n">
-        <v>6858227</v>
+        <v>6858164</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17053,7 +17053,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367468</v>
+        <v>132367469</v>
       </c>
       <c r="B143" t="n">
         <v>8455</v>
@@ -17087,7 +17087,7 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -17097,10 +17097,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>384943</v>
+        <v>384988</v>
       </c>
       <c r="R143" t="n">
-        <v>6858164</v>
+        <v>6858227</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17163,7 +17163,7 @@
         <v>132367403</v>
       </c>
       <c r="B144" t="n">
-        <v>79905</v>
+        <v>79907</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17257,32 +17257,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132367458</v>
+        <v>132367427</v>
       </c>
       <c r="B145" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17290,7 +17290,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -17300,10 +17300,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>385095</v>
+        <v>385282</v>
       </c>
       <c r="R145" t="n">
-        <v>6857937</v>
+        <v>6858105</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17336,6 +17336,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17362,32 +17367,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132367427</v>
+        <v>132367458</v>
       </c>
       <c r="B146" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17395,7 +17400,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17405,10 +17410,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>385282</v>
+        <v>385095</v>
       </c>
       <c r="R146" t="n">
-        <v>6858105</v>
+        <v>6857937</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17441,11 +17446,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17475,7 +17475,7 @@
         <v>132367389</v>
       </c>
       <c r="B147" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367407</v>
+        <v>132367452</v>
       </c>
       <c r="B148" t="n">
-        <v>79905</v>
+        <v>57945</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17580,34 +17580,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>385124</v>
+        <v>384945</v>
       </c>
       <c r="R148" t="n">
-        <v>6858064</v>
+        <v>6858165</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17666,10 +17674,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367452</v>
+        <v>132367407</v>
       </c>
       <c r="B149" t="n">
-        <v>57945</v>
+        <v>79907</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17677,42 +17685,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>384945</v>
+        <v>385124</v>
       </c>
       <c r="R149" t="n">
-        <v>6858165</v>
+        <v>6858064</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17879,7 +17879,7 @@
         <v>132367410</v>
       </c>
       <c r="B151" t="n">
-        <v>79905</v>
+        <v>79907</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17973,32 +17973,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367459</v>
+        <v>132367398</v>
       </c>
       <c r="B152" t="n">
-        <v>97960</v>
+        <v>79936</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>384655</v>
+        <v>384804</v>
       </c>
       <c r="R152" t="n">
-        <v>6858187</v>
+        <v>6858152</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18044,11 +18044,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18075,32 +18070,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132367405</v>
+        <v>132367459</v>
       </c>
       <c r="B153" t="n">
-        <v>79905</v>
+        <v>97963</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18110,10 +18105,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>385332</v>
+        <v>384655</v>
       </c>
       <c r="R153" t="n">
-        <v>6858161</v>
+        <v>6858187</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18146,6 +18141,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18172,10 +18172,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132367398</v>
+        <v>132367405</v>
       </c>
       <c r="B154" t="n">
-        <v>79934</v>
+        <v>79907</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18183,21 +18183,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18207,10 +18207,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>384804</v>
+        <v>385332</v>
       </c>
       <c r="R154" t="n">
-        <v>6858152</v>
+        <v>6858161</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18272,7 +18272,7 @@
         <v>132367391</v>
       </c>
       <c r="B155" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367434</v>
+        <v>132367406</v>
       </c>
       <c r="B158" t="n">
-        <v>58107</v>
+        <v>79907</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18587,31 +18587,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -18619,10 +18614,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385087</v>
+        <v>385318</v>
       </c>
       <c r="R158" t="n">
-        <v>6858055</v>
+        <v>6858113</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18663,6 +18658,7 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -18681,10 +18677,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367406</v>
+        <v>132367434</v>
       </c>
       <c r="B159" t="n">
-        <v>79905</v>
+        <v>58109</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18692,26 +18688,31 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18719,10 +18720,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385318</v>
+        <v>385087</v>
       </c>
       <c r="R159" t="n">
-        <v>6858113</v>
+        <v>6858055</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18763,7 +18764,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18785,7 +18785,7 @@
         <v>132367471</v>
       </c>
       <c r="B160" t="n">
-        <v>58078</v>
+        <v>58080</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18887,10 +18887,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367495</v>
+        <v>132367420</v>
       </c>
       <c r="B161" t="n">
-        <v>106219</v>
+        <v>57136</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18898,27 +18898,31 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -18926,10 +18930,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>384848</v>
+        <v>385235</v>
       </c>
       <c r="R161" t="n">
-        <v>6858075</v>
+        <v>6858146</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18964,18 +18968,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -18994,10 +18992,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367465</v>
+        <v>132367450</v>
       </c>
       <c r="B162" t="n">
-        <v>79073</v>
+        <v>57945</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19005,34 +19003,42 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385131</v>
+        <v>385107</v>
       </c>
       <c r="R162" t="n">
-        <v>6858065</v>
+        <v>6858161</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19091,45 +19097,53 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367408</v>
+        <v>132367414</v>
       </c>
       <c r="B163" t="n">
-        <v>79905</v>
+        <v>57136</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385062</v>
+        <v>385197</v>
       </c>
       <c r="R163" t="n">
-        <v>6858092</v>
+        <v>6858108</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19188,42 +19202,38 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367450</v>
+        <v>132367495</v>
       </c>
       <c r="B164" t="n">
-        <v>57945</v>
+        <v>106222</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19231,10 +19241,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385107</v>
+        <v>384848</v>
       </c>
       <c r="R164" t="n">
-        <v>6858161</v>
+        <v>6858075</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19269,12 +19279,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -19293,53 +19309,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367420</v>
+        <v>132367465</v>
       </c>
       <c r="B165" t="n">
-        <v>57136</v>
+        <v>79075</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385235</v>
+        <v>385131</v>
       </c>
       <c r="R165" t="n">
-        <v>6858146</v>
+        <v>6858065</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19398,53 +19406,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367414</v>
+        <v>132367408</v>
       </c>
       <c r="B166" t="n">
-        <v>57136</v>
+        <v>79907</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385197</v>
+        <v>385062</v>
       </c>
       <c r="R166" t="n">
-        <v>6858108</v>
+        <v>6858092</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19506,7 +19506,7 @@
         <v>132367467</v>
       </c>
       <c r="B167" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>132367502</v>
       </c>
       <c r="B168" t="n">
-        <v>78718</v>
+        <v>78720</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>132367393</v>
       </c>
       <c r="B169" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>132367461</v>
       </c>
       <c r="B171" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367409</v>
+        <v>132367401</v>
       </c>
       <c r="B172" t="n">
-        <v>79905</v>
+        <v>79936</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,21 +20031,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -20055,10 +20055,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>385075</v>
+        <v>384992</v>
       </c>
       <c r="R172" t="n">
-        <v>6858201</v>
+        <v>6858018</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20117,10 +20117,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132367447</v>
+        <v>132367409</v>
       </c>
       <c r="B173" t="n">
-        <v>57945</v>
+        <v>79907</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20128,42 +20128,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>385333</v>
+        <v>385075</v>
       </c>
       <c r="R173" t="n">
-        <v>6858152</v>
+        <v>6858201</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20222,7 +20214,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367457</v>
+        <v>132367447</v>
       </c>
       <c r="B174" t="n">
         <v>57945</v>
@@ -20255,7 +20247,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -20265,10 +20257,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385184</v>
+        <v>385333</v>
       </c>
       <c r="R174" t="n">
-        <v>6857885</v>
+        <v>6858152</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20327,10 +20319,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132367401</v>
+        <v>132367457</v>
       </c>
       <c r="B175" t="n">
-        <v>79934</v>
+        <v>57945</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20338,34 +20330,42 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>384992</v>
+        <v>385184</v>
       </c>
       <c r="R175" t="n">
-        <v>6858018</v>
+        <v>6857885</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13126,10 +13126,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132367449</v>
+        <v>132367475</v>
       </c>
       <c r="B105" t="n">
-        <v>57945</v>
+        <v>79074</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13137,42 +13137,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>385133</v>
+        <v>384814</v>
       </c>
       <c r="R105" t="n">
-        <v>6858066</v>
+        <v>6858214</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13231,10 +13223,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367444</v>
+        <v>132367394</v>
       </c>
       <c r="B106" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13242,42 +13234,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>385280</v>
+        <v>384969</v>
       </c>
       <c r="R106" t="n">
-        <v>6857923</v>
+        <v>6858130</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13336,10 +13320,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367443</v>
+        <v>132367501</v>
       </c>
       <c r="B107" t="n">
-        <v>57945</v>
+        <v>78324</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13347,42 +13331,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>385408</v>
+        <v>385084</v>
       </c>
       <c r="R107" t="n">
-        <v>6857862</v>
+        <v>6858195</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13423,8 +13399,34 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13441,10 +13443,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367475</v>
+        <v>132367449</v>
       </c>
       <c r="B108" t="n">
-        <v>79074</v>
+        <v>57945</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13452,34 +13454,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>384814</v>
+        <v>385133</v>
       </c>
       <c r="R108" t="n">
-        <v>6858214</v>
+        <v>6858066</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13538,10 +13548,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367394</v>
+        <v>132367444</v>
       </c>
       <c r="B109" t="n">
-        <v>79936</v>
+        <v>57945</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13549,34 +13559,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>384969</v>
+        <v>385280</v>
       </c>
       <c r="R109" t="n">
-        <v>6858130</v>
+        <v>6857923</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13635,10 +13653,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367501</v>
+        <v>132367443</v>
       </c>
       <c r="B110" t="n">
-        <v>78324</v>
+        <v>57945</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13646,34 +13664,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385084</v>
+        <v>385408</v>
       </c>
       <c r="R110" t="n">
-        <v>6858195</v>
+        <v>6857862</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13714,34 +13740,8 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -14376,32 +14376,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132367448</v>
+        <v>132367412</v>
       </c>
       <c r="B117" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14409,7 +14409,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>385252</v>
+        <v>385208</v>
       </c>
       <c r="R117" t="n">
-        <v>6858060</v>
+        <v>6858049</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14481,7 +14481,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132367412</v>
+        <v>132367415</v>
       </c>
       <c r="B118" t="n">
         <v>57136</v>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>385208</v>
+        <v>385185</v>
       </c>
       <c r="R118" t="n">
-        <v>6858049</v>
+        <v>6858127</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14560,6 +14560,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14586,32 +14591,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132367415</v>
+        <v>132367448</v>
       </c>
       <c r="B119" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14619,7 +14624,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -14629,10 +14634,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>385185</v>
+        <v>385252</v>
       </c>
       <c r="R119" t="n">
-        <v>6858127</v>
+        <v>6858060</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14665,11 +14670,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14793,10 +14793,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132367428</v>
+        <v>132367470</v>
       </c>
       <c r="B121" t="n">
-        <v>57136</v>
+        <v>8455</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14804,29 +14804,30 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14836,10 +14837,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>385279</v>
+        <v>384910</v>
       </c>
       <c r="R121" t="n">
-        <v>6858073</v>
+        <v>6858203</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14874,17 +14875,13 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -14903,7 +14900,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132367432</v>
+        <v>132367428</v>
       </c>
       <c r="B122" t="n">
         <v>57136</v>
@@ -14946,10 +14943,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>385185</v>
+        <v>385279</v>
       </c>
       <c r="R122" t="n">
-        <v>6858160</v>
+        <v>6858073</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14982,6 +14979,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15008,10 +15010,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132367470</v>
+        <v>132367432</v>
       </c>
       <c r="B123" t="n">
-        <v>8455</v>
+        <v>57136</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15019,30 +15021,29 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -15052,10 +15053,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>384910</v>
+        <v>385185</v>
       </c>
       <c r="R123" t="n">
-        <v>6858203</v>
+        <v>6858160</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15096,7 +15097,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -17257,32 +17257,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132367427</v>
+        <v>132367458</v>
       </c>
       <c r="B145" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17290,7 +17290,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -17300,10 +17300,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>385282</v>
+        <v>385095</v>
       </c>
       <c r="R145" t="n">
-        <v>6858105</v>
+        <v>6857937</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17336,11 +17336,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17367,32 +17362,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132367458</v>
+        <v>132367427</v>
       </c>
       <c r="B146" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17400,7 +17395,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17410,10 +17405,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>385095</v>
+        <v>385282</v>
       </c>
       <c r="R146" t="n">
-        <v>6857937</v>
+        <v>6858105</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17446,6 +17441,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17973,10 +17973,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367398</v>
+        <v>132367405</v>
       </c>
       <c r="B152" t="n">
-        <v>79936</v>
+        <v>79907</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17984,21 +17984,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>384804</v>
+        <v>385332</v>
       </c>
       <c r="R152" t="n">
-        <v>6858152</v>
+        <v>6858161</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18172,10 +18172,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132367405</v>
+        <v>132367398</v>
       </c>
       <c r="B154" t="n">
-        <v>79907</v>
+        <v>79936</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18183,21 +18183,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18207,10 +18207,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>385332</v>
+        <v>384804</v>
       </c>
       <c r="R154" t="n">
-        <v>6858161</v>
+        <v>6858152</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18269,10 +18269,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367391</v>
+        <v>132367434</v>
       </c>
       <c r="B155" t="n">
-        <v>79936</v>
+        <v>58109</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18280,34 +18280,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385129</v>
+        <v>385087</v>
       </c>
       <c r="R155" t="n">
-        <v>6858060</v>
+        <v>6858055</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18366,53 +18374,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367416</v>
+        <v>132367391</v>
       </c>
       <c r="B156" t="n">
-        <v>57136</v>
+        <v>79936</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385185</v>
+        <v>385129</v>
       </c>
       <c r="R156" t="n">
-        <v>6858146</v>
+        <v>6858060</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18471,7 +18471,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367422</v>
+        <v>132367416</v>
       </c>
       <c r="B157" t="n">
         <v>57136</v>
@@ -18514,10 +18514,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385246</v>
+        <v>385185</v>
       </c>
       <c r="R157" t="n">
-        <v>6858162</v>
+        <v>6858146</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18576,37 +18576,42 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367406</v>
+        <v>132367422</v>
       </c>
       <c r="B158" t="n">
-        <v>79907</v>
+        <v>57136</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -18614,10 +18619,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385318</v>
+        <v>385246</v>
       </c>
       <c r="R158" t="n">
-        <v>6858113</v>
+        <v>6858162</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18658,7 +18663,6 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -18677,10 +18681,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367434</v>
+        <v>132367406</v>
       </c>
       <c r="B159" t="n">
-        <v>58109</v>
+        <v>79907</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18688,31 +18692,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18720,10 +18719,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385087</v>
+        <v>385318</v>
       </c>
       <c r="R159" t="n">
-        <v>6858055</v>
+        <v>6858113</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18764,6 +18763,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18782,10 +18782,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367471</v>
+        <v>132367450</v>
       </c>
       <c r="B160" t="n">
-        <v>58080</v>
+        <v>57945</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18793,21 +18793,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18815,7 +18815,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385400</v>
+        <v>385107</v>
       </c>
       <c r="R160" t="n">
-        <v>6857831</v>
+        <v>6858161</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18992,32 +18992,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367450</v>
+        <v>132367414</v>
       </c>
       <c r="B162" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -19025,7 +19025,7 @@
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -19035,10 +19035,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385107</v>
+        <v>385197</v>
       </c>
       <c r="R162" t="n">
-        <v>6858161</v>
+        <v>6858108</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19097,27 +19097,27 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367414</v>
+        <v>132367471</v>
       </c>
       <c r="B163" t="n">
-        <v>57136</v>
+        <v>58080</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100138</v>
+        <v>205976</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -19130,7 +19130,7 @@
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -19140,10 +19140,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385197</v>
+        <v>385400</v>
       </c>
       <c r="R163" t="n">
-        <v>6858108</v>
+        <v>6857831</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -14376,32 +14376,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132367412</v>
+        <v>132367448</v>
       </c>
       <c r="B117" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14409,7 +14409,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>385208</v>
+        <v>385252</v>
       </c>
       <c r="R117" t="n">
-        <v>6858049</v>
+        <v>6858060</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14481,7 +14481,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132367415</v>
+        <v>132367412</v>
       </c>
       <c r="B118" t="n">
         <v>57136</v>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>385185</v>
+        <v>385208</v>
       </c>
       <c r="R118" t="n">
-        <v>6858127</v>
+        <v>6858049</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14560,11 +14560,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14591,32 +14586,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132367448</v>
+        <v>132367415</v>
       </c>
       <c r="B119" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14624,7 +14619,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -14634,10 +14629,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>385252</v>
+        <v>385185</v>
       </c>
       <c r="R119" t="n">
-        <v>6858060</v>
+        <v>6858127</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14670,6 +14665,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15931,45 +15931,53 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367392</v>
+        <v>132367417</v>
       </c>
       <c r="B132" t="n">
-        <v>79936</v>
+        <v>57136</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385102</v>
+        <v>385203</v>
       </c>
       <c r="R132" t="n">
-        <v>6858138</v>
+        <v>6858134</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16002,6 +16010,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16028,7 +16041,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367402</v>
+        <v>132367392</v>
       </c>
       <c r="B133" t="n">
         <v>79936</v>
@@ -16063,10 +16076,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>385403</v>
+        <v>385102</v>
       </c>
       <c r="R133" t="n">
-        <v>6857836</v>
+        <v>6858138</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16125,53 +16138,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132367417</v>
+        <v>132367402</v>
       </c>
       <c r="B134" t="n">
-        <v>57136</v>
+        <v>79936</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>385203</v>
+        <v>385403</v>
       </c>
       <c r="R134" t="n">
-        <v>6858134</v>
+        <v>6857836</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16204,11 +16209,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17257,32 +17257,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132367458</v>
+        <v>132367427</v>
       </c>
       <c r="B145" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17290,7 +17290,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -17300,10 +17300,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>385095</v>
+        <v>385282</v>
       </c>
       <c r="R145" t="n">
-        <v>6857937</v>
+        <v>6858105</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17336,6 +17336,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17362,32 +17367,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132367427</v>
+        <v>132367458</v>
       </c>
       <c r="B146" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17395,7 +17400,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17405,10 +17410,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>385282</v>
+        <v>385095</v>
       </c>
       <c r="R146" t="n">
-        <v>6858105</v>
+        <v>6857937</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17441,11 +17446,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17973,10 +17973,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367405</v>
+        <v>132367398</v>
       </c>
       <c r="B152" t="n">
-        <v>79907</v>
+        <v>79936</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17984,21 +17984,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>385332</v>
+        <v>384804</v>
       </c>
       <c r="R152" t="n">
-        <v>6858161</v>
+        <v>6858152</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18172,10 +18172,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132367398</v>
+        <v>132367405</v>
       </c>
       <c r="B154" t="n">
-        <v>79936</v>
+        <v>79907</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18183,21 +18183,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18207,10 +18207,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>384804</v>
+        <v>385332</v>
       </c>
       <c r="R154" t="n">
-        <v>6858152</v>
+        <v>6858161</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18782,32 +18782,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367450</v>
+        <v>132367420</v>
       </c>
       <c r="B160" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18815,7 +18815,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385107</v>
+        <v>385235</v>
       </c>
       <c r="R160" t="n">
-        <v>6858161</v>
+        <v>6858146</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,10 +18887,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367420</v>
+        <v>132367495</v>
       </c>
       <c r="B161" t="n">
-        <v>57136</v>
+        <v>106222</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18898,31 +18898,27 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -18930,10 +18926,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385235</v>
+        <v>384848</v>
       </c>
       <c r="R161" t="n">
-        <v>6858146</v>
+        <v>6858075</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18968,12 +18964,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -18992,53 +18994,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367414</v>
+        <v>132367465</v>
       </c>
       <c r="B162" t="n">
-        <v>57136</v>
+        <v>79075</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385197</v>
+        <v>385131</v>
       </c>
       <c r="R162" t="n">
-        <v>6858108</v>
+        <v>6858065</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19097,10 +19091,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367471</v>
+        <v>132367408</v>
       </c>
       <c r="B163" t="n">
-        <v>58080</v>
+        <v>79907</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19108,42 +19102,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>205976</v>
+        <v>229821</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385400</v>
+        <v>385062</v>
       </c>
       <c r="R163" t="n">
-        <v>6857831</v>
+        <v>6858092</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19202,38 +19188,42 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367495</v>
+        <v>132367450</v>
       </c>
       <c r="B164" t="n">
-        <v>106222</v>
+        <v>57945</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19241,10 +19231,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>384848</v>
+        <v>385107</v>
       </c>
       <c r="R164" t="n">
-        <v>6858075</v>
+        <v>6858161</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19279,18 +19269,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -19309,45 +19293,53 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367465</v>
+        <v>132367414</v>
       </c>
       <c r="B165" t="n">
-        <v>79075</v>
+        <v>57136</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385131</v>
+        <v>385197</v>
       </c>
       <c r="R165" t="n">
-        <v>6858065</v>
+        <v>6858108</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19406,10 +19398,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367408</v>
+        <v>132367471</v>
       </c>
       <c r="B166" t="n">
-        <v>79907</v>
+        <v>58080</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19417,34 +19409,42 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>229821</v>
+        <v>205976</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385062</v>
+        <v>385400</v>
       </c>
       <c r="R166" t="n">
-        <v>6858092</v>
+        <v>6857831</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367401</v>
+        <v>132367447</v>
       </c>
       <c r="B172" t="n">
-        <v>79936</v>
+        <v>57945</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,34 +20031,42 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>384992</v>
+        <v>385333</v>
       </c>
       <c r="R172" t="n">
-        <v>6858018</v>
+        <v>6858152</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20117,10 +20125,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132367409</v>
+        <v>132367457</v>
       </c>
       <c r="B173" t="n">
-        <v>79907</v>
+        <v>57945</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20128,34 +20136,42 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>385075</v>
+        <v>385184</v>
       </c>
       <c r="R173" t="n">
-        <v>6858201</v>
+        <v>6857885</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20214,10 +20230,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367447</v>
+        <v>132367409</v>
       </c>
       <c r="B174" t="n">
-        <v>57945</v>
+        <v>79907</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20225,42 +20241,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385333</v>
+        <v>385075</v>
       </c>
       <c r="R174" t="n">
-        <v>6858152</v>
+        <v>6858201</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20319,10 +20327,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132367457</v>
+        <v>132367401</v>
       </c>
       <c r="B175" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20330,42 +20338,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>385184</v>
+        <v>384992</v>
       </c>
       <c r="R175" t="n">
-        <v>6857885</v>
+        <v>6858018</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13320,45 +13320,53 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367501</v>
+        <v>132367430</v>
       </c>
       <c r="B107" t="n">
-        <v>78324</v>
+        <v>57136</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>385084</v>
+        <v>385158</v>
       </c>
       <c r="R107" t="n">
-        <v>6858195</v>
+        <v>6858052</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13399,34 +13407,8 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13443,10 +13425,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367449</v>
+        <v>132367501</v>
       </c>
       <c r="B108" t="n">
-        <v>57945</v>
+        <v>78324</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13454,42 +13436,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>385133</v>
+        <v>385084</v>
       </c>
       <c r="R108" t="n">
-        <v>6858066</v>
+        <v>6858195</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13530,8 +13504,34 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -13548,7 +13548,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367444</v>
+        <v>132367449</v>
       </c>
       <c r="B109" t="n">
         <v>57945</v>
@@ -13581,7 +13581,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -13591,10 +13591,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385280</v>
+        <v>385133</v>
       </c>
       <c r="R109" t="n">
-        <v>6857923</v>
+        <v>6858066</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367443</v>
+        <v>132367444</v>
       </c>
       <c r="B110" t="n">
         <v>57945</v>
@@ -13696,10 +13696,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385408</v>
+        <v>385280</v>
       </c>
       <c r="R110" t="n">
-        <v>6857862</v>
+        <v>6857923</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13758,32 +13758,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132367430</v>
+        <v>132367443</v>
       </c>
       <c r="B111" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13791,7 +13791,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>385158</v>
+        <v>385408</v>
       </c>
       <c r="R111" t="n">
-        <v>6858052</v>
+        <v>6857862</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14793,10 +14793,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132367470</v>
+        <v>132367428</v>
       </c>
       <c r="B121" t="n">
-        <v>8455</v>
+        <v>57136</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14804,30 +14804,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14837,10 +14836,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>384910</v>
+        <v>385279</v>
       </c>
       <c r="R121" t="n">
-        <v>6858203</v>
+        <v>6858073</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14875,13 +14874,17 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -14900,7 +14903,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132367428</v>
+        <v>132367432</v>
       </c>
       <c r="B122" t="n">
         <v>57136</v>
@@ -14943,10 +14946,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>385279</v>
+        <v>385185</v>
       </c>
       <c r="R122" t="n">
-        <v>6858073</v>
+        <v>6858160</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14979,11 +14982,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15010,10 +15008,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132367432</v>
+        <v>132367470</v>
       </c>
       <c r="B123" t="n">
-        <v>57136</v>
+        <v>8455</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15021,29 +15019,30 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -15053,10 +15052,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>385185</v>
+        <v>384910</v>
       </c>
       <c r="R123" t="n">
-        <v>6858160</v>
+        <v>6858203</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15097,6 +15096,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -15220,10 +15220,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367462</v>
+        <v>132367446</v>
       </c>
       <c r="B125" t="n">
-        <v>79075</v>
+        <v>57945</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15231,34 +15231,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>385195</v>
+        <v>385178</v>
       </c>
       <c r="R125" t="n">
-        <v>6858154</v>
+        <v>6858121</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15317,10 +15325,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132367464</v>
+        <v>132367453</v>
       </c>
       <c r="B126" t="n">
-        <v>79075</v>
+        <v>57945</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15328,34 +15336,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>385318</v>
+        <v>384934</v>
       </c>
       <c r="R126" t="n">
-        <v>6858113</v>
+        <v>6858197</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15414,53 +15430,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367425</v>
+        <v>132367395</v>
       </c>
       <c r="B127" t="n">
-        <v>57136</v>
+        <v>79936</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>385281</v>
+        <v>384944</v>
       </c>
       <c r="R127" t="n">
-        <v>6858170</v>
+        <v>6858169</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15519,45 +15527,53 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367395</v>
+        <v>132367425</v>
       </c>
       <c r="B128" t="n">
-        <v>79936</v>
+        <v>57136</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>384944</v>
+        <v>385281</v>
       </c>
       <c r="R128" t="n">
-        <v>6858169</v>
+        <v>6858170</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15616,10 +15632,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132367446</v>
+        <v>132367462</v>
       </c>
       <c r="B129" t="n">
-        <v>57945</v>
+        <v>79075</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15627,42 +15643,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>385178</v>
+        <v>385195</v>
       </c>
       <c r="R129" t="n">
-        <v>6858121</v>
+        <v>6858154</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15721,10 +15729,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132367453</v>
+        <v>132367464</v>
       </c>
       <c r="B130" t="n">
-        <v>57945</v>
+        <v>79075</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15732,42 +15740,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>384934</v>
+        <v>385318</v>
       </c>
       <c r="R130" t="n">
-        <v>6858197</v>
+        <v>6858113</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15826,32 +15826,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367455</v>
+        <v>132367417</v>
       </c>
       <c r="B131" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15859,7 +15859,7 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>384840</v>
+        <v>385203</v>
       </c>
       <c r="R131" t="n">
-        <v>6858190</v>
+        <v>6858134</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15905,6 +15905,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15931,32 +15936,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367417</v>
+        <v>132367455</v>
       </c>
       <c r="B132" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15964,7 +15969,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -15974,10 +15979,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385203</v>
+        <v>384840</v>
       </c>
       <c r="R132" t="n">
-        <v>6858134</v>
+        <v>6858190</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16010,11 +16015,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -17257,32 +17257,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132367427</v>
+        <v>132367458</v>
       </c>
       <c r="B145" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17290,7 +17290,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -17300,10 +17300,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>385282</v>
+        <v>385095</v>
       </c>
       <c r="R145" t="n">
-        <v>6858105</v>
+        <v>6857937</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17336,11 +17336,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17367,32 +17362,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132367458</v>
+        <v>132367427</v>
       </c>
       <c r="B146" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17400,7 +17395,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17410,10 +17405,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>385095</v>
+        <v>385282</v>
       </c>
       <c r="R146" t="n">
-        <v>6857937</v>
+        <v>6858105</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17446,6 +17441,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132367389</v>
+        <v>132367452</v>
       </c>
       <c r="B147" t="n">
-        <v>79936</v>
+        <v>57945</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17483,34 +17483,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>385195</v>
+        <v>384945</v>
       </c>
       <c r="R147" t="n">
-        <v>6858154</v>
+        <v>6858165</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17569,10 +17577,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367452</v>
+        <v>132367389</v>
       </c>
       <c r="B148" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17580,42 +17588,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>384945</v>
+        <v>385195</v>
       </c>
       <c r="R148" t="n">
-        <v>6858165</v>
+        <v>6858154</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17973,32 +17973,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367398</v>
+        <v>132367459</v>
       </c>
       <c r="B152" t="n">
-        <v>79936</v>
+        <v>97963</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>384804</v>
+        <v>384655</v>
       </c>
       <c r="R152" t="n">
-        <v>6858152</v>
+        <v>6858187</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18044,6 +18044,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18070,32 +18075,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132367459</v>
+        <v>132367405</v>
       </c>
       <c r="B153" t="n">
-        <v>97963</v>
+        <v>79907</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18105,10 +18110,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>384655</v>
+        <v>385332</v>
       </c>
       <c r="R153" t="n">
-        <v>6858187</v>
+        <v>6858161</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18141,11 +18146,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18172,10 +18172,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132367405</v>
+        <v>132367398</v>
       </c>
       <c r="B154" t="n">
-        <v>79907</v>
+        <v>79936</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18183,21 +18183,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18207,10 +18207,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>385332</v>
+        <v>384804</v>
       </c>
       <c r="R154" t="n">
-        <v>6858161</v>
+        <v>6858152</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18887,10 +18887,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367495</v>
+        <v>132367414</v>
       </c>
       <c r="B161" t="n">
-        <v>106222</v>
+        <v>57136</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18898,27 +18898,31 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -18926,10 +18930,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>384848</v>
+        <v>385197</v>
       </c>
       <c r="R161" t="n">
-        <v>6858075</v>
+        <v>6858108</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18964,18 +18968,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -18994,45 +18992,49 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367465</v>
+        <v>132367495</v>
       </c>
       <c r="B162" t="n">
-        <v>79075</v>
+        <v>106222</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385131</v>
+        <v>384848</v>
       </c>
       <c r="R162" t="n">
-        <v>6858065</v>
+        <v>6858075</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19067,12 +19069,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -19188,10 +19196,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367450</v>
+        <v>132367471</v>
       </c>
       <c r="B164" t="n">
-        <v>57945</v>
+        <v>58080</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19199,21 +19207,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>205976</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19221,7 +19229,7 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -19231,10 +19239,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385107</v>
+        <v>385400</v>
       </c>
       <c r="R164" t="n">
-        <v>6858161</v>
+        <v>6857831</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19293,53 +19301,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367414</v>
+        <v>132367465</v>
       </c>
       <c r="B165" t="n">
-        <v>57136</v>
+        <v>79075</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385197</v>
+        <v>385131</v>
       </c>
       <c r="R165" t="n">
-        <v>6858108</v>
+        <v>6858065</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19398,10 +19398,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367471</v>
+        <v>132367450</v>
       </c>
       <c r="B166" t="n">
-        <v>58080</v>
+        <v>57945</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19409,21 +19409,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19431,7 +19431,7 @@
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -19441,10 +19441,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385400</v>
+        <v>385107</v>
       </c>
       <c r="R166" t="n">
-        <v>6857831</v>
+        <v>6858161</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19600,10 +19600,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367502</v>
+        <v>132367461</v>
       </c>
       <c r="B168" t="n">
-        <v>78720</v>
+        <v>79075</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19611,37 +19611,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385349</v>
+        <v>385227</v>
       </c>
       <c r="R168" t="n">
-        <v>6857860</v>
+        <v>6857907</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19682,29 +19679,8 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -19721,10 +19697,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367393</v>
+        <v>132367502</v>
       </c>
       <c r="B169" t="n">
-        <v>79936</v>
+        <v>78720</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19732,34 +19708,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385118</v>
+        <v>385349</v>
       </c>
       <c r="R169" t="n">
-        <v>6858178</v>
+        <v>6857860</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19800,8 +19779,29 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
@@ -19818,53 +19818,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367423</v>
+        <v>132367393</v>
       </c>
       <c r="B170" t="n">
-        <v>57136</v>
+        <v>79936</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385263</v>
+        <v>385118</v>
       </c>
       <c r="R170" t="n">
-        <v>6858153</v>
+        <v>6858178</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19923,45 +19915,53 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367461</v>
+        <v>132367423</v>
       </c>
       <c r="B171" t="n">
-        <v>79075</v>
+        <v>57136</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385227</v>
+        <v>385263</v>
       </c>
       <c r="R171" t="n">
-        <v>6857907</v>
+        <v>6858153</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20230,10 +20230,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367409</v>
+        <v>132367401</v>
       </c>
       <c r="B174" t="n">
-        <v>79907</v>
+        <v>79936</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20241,21 +20241,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385075</v>
+        <v>384992</v>
       </c>
       <c r="R174" t="n">
-        <v>6858201</v>
+        <v>6858018</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20327,10 +20327,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132367401</v>
+        <v>132367409</v>
       </c>
       <c r="B175" t="n">
-        <v>79936</v>
+        <v>79907</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20338,21 +20338,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20362,10 +20362,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>384992</v>
+        <v>385075</v>
       </c>
       <c r="R175" t="n">
-        <v>6858018</v>
+        <v>6858201</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13126,10 +13126,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132367475</v>
+        <v>132367463</v>
       </c>
       <c r="B105" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13137,34 +13137,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>384814</v>
+        <v>385332</v>
       </c>
       <c r="R105" t="n">
-        <v>6858214</v>
+        <v>6858162</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13205,6 +13208,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -13223,10 +13227,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367394</v>
+        <v>132367466</v>
       </c>
       <c r="B106" t="n">
-        <v>79936</v>
+        <v>79075</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13234,21 +13238,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13258,10 +13262,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>384969</v>
+        <v>384749</v>
       </c>
       <c r="R106" t="n">
-        <v>6858130</v>
+        <v>6858223</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13320,53 +13324,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367430</v>
+        <v>132367475</v>
       </c>
       <c r="B107" t="n">
-        <v>57136</v>
+        <v>79074</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>385158</v>
+        <v>384814</v>
       </c>
       <c r="R107" t="n">
-        <v>6858052</v>
+        <v>6858214</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13425,10 +13421,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367501</v>
+        <v>132367394</v>
       </c>
       <c r="B108" t="n">
-        <v>78324</v>
+        <v>79936</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13436,21 +13432,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13460,10 +13456,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>385084</v>
+        <v>384969</v>
       </c>
       <c r="R108" t="n">
-        <v>6858195</v>
+        <v>6858130</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13504,34 +13500,8 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -13548,32 +13518,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367449</v>
+        <v>132367430</v>
       </c>
       <c r="B109" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13581,7 +13551,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -13591,10 +13561,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385133</v>
+        <v>385158</v>
       </c>
       <c r="R109" t="n">
-        <v>6858066</v>
+        <v>6858052</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13653,10 +13623,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367444</v>
+        <v>132367501</v>
       </c>
       <c r="B110" t="n">
-        <v>57945</v>
+        <v>78324</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13664,42 +13634,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385280</v>
+        <v>385084</v>
       </c>
       <c r="R110" t="n">
-        <v>6857923</v>
+        <v>6858195</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13740,8 +13702,34 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -13758,7 +13746,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132367443</v>
+        <v>132367449</v>
       </c>
       <c r="B111" t="n">
         <v>57945</v>
@@ -13791,7 +13779,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -13801,10 +13789,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>385408</v>
+        <v>385133</v>
       </c>
       <c r="R111" t="n">
-        <v>6857862</v>
+        <v>6858066</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13863,10 +13851,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132367463</v>
+        <v>132367444</v>
       </c>
       <c r="B112" t="n">
-        <v>79075</v>
+        <v>57945</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13874,26 +13862,31 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13901,10 +13894,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>385332</v>
+        <v>385280</v>
       </c>
       <c r="R112" t="n">
-        <v>6858162</v>
+        <v>6857923</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13945,7 +13938,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -13964,10 +13956,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132367466</v>
+        <v>132367443</v>
       </c>
       <c r="B113" t="n">
-        <v>79075</v>
+        <v>57945</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13975,34 +13967,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>384749</v>
+        <v>385408</v>
       </c>
       <c r="R113" t="n">
-        <v>6858223</v>
+        <v>6857862</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -16429,53 +16429,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367421</v>
+        <v>132367404</v>
       </c>
       <c r="B137" t="n">
-        <v>57136</v>
+        <v>79907</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385249</v>
+        <v>385227</v>
       </c>
       <c r="R137" t="n">
-        <v>6858148</v>
+        <v>6857907</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16534,7 +16526,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367431</v>
+        <v>132367421</v>
       </c>
       <c r="B138" t="n">
         <v>57136</v>
@@ -16577,10 +16569,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>384950</v>
+        <v>385249</v>
       </c>
       <c r="R138" t="n">
-        <v>6858169</v>
+        <v>6858148</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16639,7 +16631,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367413</v>
+        <v>132367431</v>
       </c>
       <c r="B139" t="n">
         <v>57136</v>
@@ -16682,10 +16674,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>385181</v>
+        <v>384950</v>
       </c>
       <c r="R139" t="n">
-        <v>6858109</v>
+        <v>6858169</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16744,45 +16736,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367404</v>
+        <v>132367413</v>
       </c>
       <c r="B140" t="n">
-        <v>79907</v>
+        <v>57136</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>385227</v>
+        <v>385181</v>
       </c>
       <c r="R140" t="n">
-        <v>6857907</v>
+        <v>6858109</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16841,10 +16841,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367424</v>
+        <v>132367468</v>
       </c>
       <c r="B141" t="n">
-        <v>57136</v>
+        <v>8455</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16852,29 +16852,30 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -16884,10 +16885,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>385276</v>
+        <v>384943</v>
       </c>
       <c r="R141" t="n">
-        <v>6858157</v>
+        <v>6858164</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16928,6 +16929,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16946,7 +16948,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367468</v>
+        <v>132367469</v>
       </c>
       <c r="B142" t="n">
         <v>8455</v>
@@ -16980,7 +16982,7 @@
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -16990,10 +16992,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>384943</v>
+        <v>384988</v>
       </c>
       <c r="R142" t="n">
-        <v>6858164</v>
+        <v>6858227</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17053,54 +17055,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367469</v>
+        <v>132367403</v>
       </c>
       <c r="B143" t="n">
-        <v>8455</v>
+        <v>79907</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>384988</v>
+        <v>385374</v>
       </c>
       <c r="R143" t="n">
-        <v>6858227</v>
+        <v>6857880</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17141,7 +17134,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -17160,45 +17152,53 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367403</v>
+        <v>132367424</v>
       </c>
       <c r="B144" t="n">
-        <v>79907</v>
+        <v>57136</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>385374</v>
+        <v>385276</v>
       </c>
       <c r="R144" t="n">
-        <v>6857880</v>
+        <v>6858157</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18782,53 +18782,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367420</v>
+        <v>132367465</v>
       </c>
       <c r="B160" t="n">
-        <v>57136</v>
+        <v>79075</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385235</v>
+        <v>385131</v>
       </c>
       <c r="R160" t="n">
-        <v>6858146</v>
+        <v>6858065</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,27 +18879,27 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367414</v>
+        <v>132367471</v>
       </c>
       <c r="B161" t="n">
-        <v>57136</v>
+        <v>58080</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>205976</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -18920,7 +18912,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -18930,10 +18922,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385197</v>
+        <v>385400</v>
       </c>
       <c r="R161" t="n">
-        <v>6858108</v>
+        <v>6857831</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19196,27 +19188,27 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367471</v>
+        <v>132367414</v>
       </c>
       <c r="B164" t="n">
-        <v>58080</v>
+        <v>57136</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>205976</v>
+        <v>100138</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -19229,7 +19221,7 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -19239,10 +19231,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385400</v>
+        <v>385197</v>
       </c>
       <c r="R164" t="n">
-        <v>6857831</v>
+        <v>6858108</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19301,10 +19293,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367465</v>
+        <v>132367450</v>
       </c>
       <c r="B165" t="n">
-        <v>79075</v>
+        <v>57945</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19312,34 +19304,42 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385131</v>
+        <v>385107</v>
       </c>
       <c r="R165" t="n">
-        <v>6858065</v>
+        <v>6858161</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19398,32 +19398,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367450</v>
+        <v>132367420</v>
       </c>
       <c r="B166" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19431,7 +19431,7 @@
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -19441,10 +19441,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385107</v>
+        <v>385235</v>
       </c>
       <c r="R166" t="n">
-        <v>6858161</v>
+        <v>6858146</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19600,10 +19600,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367461</v>
+        <v>132367502</v>
       </c>
       <c r="B168" t="n">
-        <v>79075</v>
+        <v>78720</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19611,34 +19611,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385227</v>
+        <v>385349</v>
       </c>
       <c r="R168" t="n">
-        <v>6857907</v>
+        <v>6857860</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19679,8 +19682,29 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -19697,10 +19721,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367502</v>
+        <v>132367393</v>
       </c>
       <c r="B169" t="n">
-        <v>78720</v>
+        <v>79936</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19708,37 +19732,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385349</v>
+        <v>385118</v>
       </c>
       <c r="R169" t="n">
-        <v>6857860</v>
+        <v>6858178</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19779,29 +19800,8 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
@@ -19818,45 +19818,53 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367393</v>
+        <v>132367423</v>
       </c>
       <c r="B170" t="n">
-        <v>79936</v>
+        <v>57136</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385118</v>
+        <v>385263</v>
       </c>
       <c r="R170" t="n">
-        <v>6858178</v>
+        <v>6858153</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19915,53 +19923,45 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367423</v>
+        <v>132367461</v>
       </c>
       <c r="B171" t="n">
-        <v>57136</v>
+        <v>79075</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385263</v>
+        <v>385227</v>
       </c>
       <c r="R171" t="n">
-        <v>6858153</v>
+        <v>6857907</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -16429,45 +16429,53 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367404</v>
+        <v>132367421</v>
       </c>
       <c r="B137" t="n">
-        <v>79907</v>
+        <v>57136</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385227</v>
+        <v>385249</v>
       </c>
       <c r="R137" t="n">
-        <v>6857907</v>
+        <v>6858148</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16526,7 +16534,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367421</v>
+        <v>132367431</v>
       </c>
       <c r="B138" t="n">
         <v>57136</v>
@@ -16569,10 +16577,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>385249</v>
+        <v>384950</v>
       </c>
       <c r="R138" t="n">
-        <v>6858148</v>
+        <v>6858169</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16631,7 +16639,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367431</v>
+        <v>132367413</v>
       </c>
       <c r="B139" t="n">
         <v>57136</v>
@@ -16674,10 +16682,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>384950</v>
+        <v>385181</v>
       </c>
       <c r="R139" t="n">
-        <v>6858169</v>
+        <v>6858109</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16736,53 +16744,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367413</v>
+        <v>132367404</v>
       </c>
       <c r="B140" t="n">
-        <v>57136</v>
+        <v>79907</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>385181</v>
+        <v>385227</v>
       </c>
       <c r="R140" t="n">
-        <v>6858109</v>
+        <v>6857907</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17472,10 +17472,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132367452</v>
+        <v>132367389</v>
       </c>
       <c r="B147" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17483,42 +17483,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>384945</v>
+        <v>385195</v>
       </c>
       <c r="R147" t="n">
-        <v>6858165</v>
+        <v>6858154</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17577,10 +17569,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367389</v>
+        <v>132367407</v>
       </c>
       <c r="B148" t="n">
-        <v>79936</v>
+        <v>79907</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17588,21 +17580,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17612,10 +17604,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>385195</v>
+        <v>385124</v>
       </c>
       <c r="R148" t="n">
-        <v>6858154</v>
+        <v>6858064</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17674,10 +17666,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367407</v>
+        <v>132367452</v>
       </c>
       <c r="B149" t="n">
-        <v>79907</v>
+        <v>57945</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17685,34 +17677,42 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>385124</v>
+        <v>384945</v>
       </c>
       <c r="R149" t="n">
-        <v>6858064</v>
+        <v>6858165</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18782,45 +18782,53 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367465</v>
+        <v>132367420</v>
       </c>
       <c r="B160" t="n">
-        <v>79075</v>
+        <v>57136</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385131</v>
+        <v>385235</v>
       </c>
       <c r="R160" t="n">
-        <v>6858065</v>
+        <v>6858146</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18879,27 +18887,27 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367471</v>
+        <v>132367414</v>
       </c>
       <c r="B161" t="n">
-        <v>58080</v>
+        <v>57136</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>205976</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -18912,7 +18920,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -18922,10 +18930,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385400</v>
+        <v>385197</v>
       </c>
       <c r="R161" t="n">
-        <v>6857831</v>
+        <v>6858108</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19188,27 +19196,27 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367414</v>
+        <v>132367471</v>
       </c>
       <c r="B164" t="n">
-        <v>57136</v>
+        <v>58080</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100138</v>
+        <v>205976</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -19221,7 +19229,7 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -19231,10 +19239,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385197</v>
+        <v>385400</v>
       </c>
       <c r="R164" t="n">
-        <v>6858108</v>
+        <v>6857831</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19293,10 +19301,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367450</v>
+        <v>132367465</v>
       </c>
       <c r="B165" t="n">
-        <v>57945</v>
+        <v>79075</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19304,42 +19312,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385107</v>
+        <v>385131</v>
       </c>
       <c r="R165" t="n">
-        <v>6858161</v>
+        <v>6858065</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19398,32 +19398,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367420</v>
+        <v>132367450</v>
       </c>
       <c r="B166" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19431,7 +19431,7 @@
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -19441,10 +19441,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385235</v>
+        <v>385107</v>
       </c>
       <c r="R166" t="n">
-        <v>6858146</v>
+        <v>6858161</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19600,10 +19600,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367502</v>
+        <v>132367461</v>
       </c>
       <c r="B168" t="n">
-        <v>78720</v>
+        <v>79075</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19611,37 +19611,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385349</v>
+        <v>385227</v>
       </c>
       <c r="R168" t="n">
-        <v>6857860</v>
+        <v>6857907</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19682,29 +19679,8 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -19721,10 +19697,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367393</v>
+        <v>132367502</v>
       </c>
       <c r="B169" t="n">
-        <v>79936</v>
+        <v>78720</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19732,34 +19708,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385118</v>
+        <v>385349</v>
       </c>
       <c r="R169" t="n">
-        <v>6858178</v>
+        <v>6857860</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19800,8 +19779,29 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
@@ -19818,53 +19818,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367423</v>
+        <v>132367393</v>
       </c>
       <c r="B170" t="n">
-        <v>57136</v>
+        <v>79936</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385263</v>
+        <v>385118</v>
       </c>
       <c r="R170" t="n">
-        <v>6858153</v>
+        <v>6858178</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19923,45 +19915,53 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367461</v>
+        <v>132367423</v>
       </c>
       <c r="B171" t="n">
-        <v>79075</v>
+        <v>57136</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385227</v>
+        <v>385263</v>
       </c>
       <c r="R171" t="n">
-        <v>6857907</v>
+        <v>6858153</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -16429,53 +16429,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367421</v>
+        <v>132367404</v>
       </c>
       <c r="B137" t="n">
-        <v>57136</v>
+        <v>79907</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385249</v>
+        <v>385227</v>
       </c>
       <c r="R137" t="n">
-        <v>6858148</v>
+        <v>6857907</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16534,7 +16526,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367431</v>
+        <v>132367421</v>
       </c>
       <c r="B138" t="n">
         <v>57136</v>
@@ -16577,10 +16569,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>384950</v>
+        <v>385249</v>
       </c>
       <c r="R138" t="n">
-        <v>6858169</v>
+        <v>6858148</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16639,7 +16631,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367413</v>
+        <v>132367431</v>
       </c>
       <c r="B139" t="n">
         <v>57136</v>
@@ -16682,10 +16674,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>385181</v>
+        <v>384950</v>
       </c>
       <c r="R139" t="n">
-        <v>6858109</v>
+        <v>6858169</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16744,45 +16736,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367404</v>
+        <v>132367413</v>
       </c>
       <c r="B140" t="n">
-        <v>79907</v>
+        <v>57136</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>385227</v>
+        <v>385181</v>
       </c>
       <c r="R140" t="n">
-        <v>6857907</v>
+        <v>6858109</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -18269,10 +18269,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367434</v>
+        <v>132367391</v>
       </c>
       <c r="B155" t="n">
-        <v>58109</v>
+        <v>79936</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18280,42 +18280,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385087</v>
+        <v>385129</v>
       </c>
       <c r="R155" t="n">
-        <v>6858055</v>
+        <v>6858060</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18374,45 +18366,53 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367391</v>
+        <v>132367416</v>
       </c>
       <c r="B156" t="n">
-        <v>79936</v>
+        <v>57136</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385129</v>
+        <v>385185</v>
       </c>
       <c r="R156" t="n">
-        <v>6858060</v>
+        <v>6858146</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18471,7 +18471,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367416</v>
+        <v>132367422</v>
       </c>
       <c r="B157" t="n">
         <v>57136</v>
@@ -18514,10 +18514,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385185</v>
+        <v>385246</v>
       </c>
       <c r="R157" t="n">
-        <v>6858146</v>
+        <v>6858162</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18576,32 +18576,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367422</v>
+        <v>132367434</v>
       </c>
       <c r="B158" t="n">
-        <v>57136</v>
+        <v>58109</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -18619,10 +18619,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385246</v>
+        <v>385087</v>
       </c>
       <c r="R158" t="n">
-        <v>6858162</v>
+        <v>6858055</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18782,53 +18782,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367420</v>
+        <v>132367465</v>
       </c>
       <c r="B160" t="n">
-        <v>57136</v>
+        <v>79075</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385235</v>
+        <v>385131</v>
       </c>
       <c r="R160" t="n">
-        <v>6858146</v>
+        <v>6858065</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,27 +18879,27 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367414</v>
+        <v>132367471</v>
       </c>
       <c r="B161" t="n">
-        <v>57136</v>
+        <v>58080</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>205976</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -18920,7 +18912,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -18930,10 +18922,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385197</v>
+        <v>385400</v>
       </c>
       <c r="R161" t="n">
-        <v>6858108</v>
+        <v>6857831</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19196,27 +19188,27 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367471</v>
+        <v>132367414</v>
       </c>
       <c r="B164" t="n">
-        <v>58080</v>
+        <v>57136</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>205976</v>
+        <v>100138</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -19229,7 +19221,7 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -19239,10 +19231,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385400</v>
+        <v>385197</v>
       </c>
       <c r="R164" t="n">
-        <v>6857831</v>
+        <v>6858108</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19301,10 +19293,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367465</v>
+        <v>132367450</v>
       </c>
       <c r="B165" t="n">
-        <v>79075</v>
+        <v>57945</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19312,34 +19304,42 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385131</v>
+        <v>385107</v>
       </c>
       <c r="R165" t="n">
-        <v>6858065</v>
+        <v>6858161</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19398,32 +19398,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367450</v>
+        <v>132367420</v>
       </c>
       <c r="B166" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19431,7 +19431,7 @@
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -19441,10 +19441,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385107</v>
+        <v>385235</v>
       </c>
       <c r="R166" t="n">
-        <v>6858161</v>
+        <v>6858146</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13126,10 +13126,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132367463</v>
+        <v>132367475</v>
       </c>
       <c r="B105" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13137,37 +13137,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>385332</v>
+        <v>384814</v>
       </c>
       <c r="R105" t="n">
-        <v>6858162</v>
+        <v>6858214</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13208,7 +13205,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -13227,10 +13223,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367466</v>
+        <v>132367394</v>
       </c>
       <c r="B106" t="n">
-        <v>79075</v>
+        <v>79938</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13238,21 +13234,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13262,10 +13258,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>384749</v>
+        <v>384969</v>
       </c>
       <c r="R106" t="n">
-        <v>6858223</v>
+        <v>6858130</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13324,10 +13320,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367475</v>
+        <v>132367501</v>
       </c>
       <c r="B107" t="n">
-        <v>79074</v>
+        <v>78326</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13335,21 +13331,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13359,10 +13355,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>384814</v>
+        <v>385084</v>
       </c>
       <c r="R107" t="n">
-        <v>6858214</v>
+        <v>6858195</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13403,8 +13399,34 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13421,10 +13443,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367394</v>
+        <v>132367449</v>
       </c>
       <c r="B108" t="n">
-        <v>79936</v>
+        <v>57946</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13432,34 +13454,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>384969</v>
+        <v>385133</v>
       </c>
       <c r="R108" t="n">
-        <v>6858130</v>
+        <v>6858066</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13518,32 +13548,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367430</v>
+        <v>132367444</v>
       </c>
       <c r="B109" t="n">
-        <v>57136</v>
+        <v>57946</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13551,7 +13581,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -13561,10 +13591,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385158</v>
+        <v>385280</v>
       </c>
       <c r="R109" t="n">
-        <v>6858052</v>
+        <v>6857923</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13623,10 +13653,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367501</v>
+        <v>132367443</v>
       </c>
       <c r="B110" t="n">
-        <v>78324</v>
+        <v>57946</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13634,34 +13664,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385084</v>
+        <v>385408</v>
       </c>
       <c r="R110" t="n">
-        <v>6858195</v>
+        <v>6857862</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13702,34 +13740,8 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -13746,32 +13758,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132367449</v>
+        <v>132367430</v>
       </c>
       <c r="B111" t="n">
-        <v>57945</v>
+        <v>57137</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13779,7 +13791,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -13789,10 +13801,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>385133</v>
+        <v>385158</v>
       </c>
       <c r="R111" t="n">
-        <v>6858066</v>
+        <v>6858052</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13851,10 +13863,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132367444</v>
+        <v>132367463</v>
       </c>
       <c r="B112" t="n">
-        <v>57945</v>
+        <v>79077</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13862,31 +13874,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13894,10 +13901,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>385280</v>
+        <v>385332</v>
       </c>
       <c r="R112" t="n">
-        <v>6857923</v>
+        <v>6858162</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13938,6 +13945,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -13956,10 +13964,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132367443</v>
+        <v>132367466</v>
       </c>
       <c r="B113" t="n">
-        <v>57945</v>
+        <v>79077</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13967,42 +13975,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>385408</v>
+        <v>384749</v>
       </c>
       <c r="R113" t="n">
-        <v>6857862</v>
+        <v>6858223</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14061,10 +14061,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132367451</v>
+        <v>132367435</v>
       </c>
       <c r="B114" t="n">
-        <v>57945</v>
+        <v>58110</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14072,21 +14072,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14094,7 +14094,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -14104,10 +14104,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>385088</v>
+        <v>384859</v>
       </c>
       <c r="R114" t="n">
-        <v>6858196</v>
+        <v>6858073</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14166,10 +14166,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132367456</v>
+        <v>132367451</v>
       </c>
       <c r="B115" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>385112</v>
+        <v>385088</v>
       </c>
       <c r="R115" t="n">
-        <v>6857918</v>
+        <v>6858196</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14271,10 +14271,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132367435</v>
+        <v>132367456</v>
       </c>
       <c r="B116" t="n">
-        <v>58109</v>
+        <v>57946</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14282,21 +14282,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>384859</v>
+        <v>385112</v>
       </c>
       <c r="R116" t="n">
-        <v>6858073</v>
+        <v>6857918</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14376,32 +14376,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132367448</v>
+        <v>132367412</v>
       </c>
       <c r="B117" t="n">
-        <v>57945</v>
+        <v>57137</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14409,7 +14409,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>385252</v>
+        <v>385208</v>
       </c>
       <c r="R117" t="n">
-        <v>6858060</v>
+        <v>6858049</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14481,10 +14481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132367412</v>
+        <v>132367415</v>
       </c>
       <c r="B118" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>385208</v>
+        <v>385185</v>
       </c>
       <c r="R118" t="n">
-        <v>6858049</v>
+        <v>6858127</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14560,6 +14560,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14586,32 +14591,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132367415</v>
+        <v>132367448</v>
       </c>
       <c r="B119" t="n">
-        <v>57136</v>
+        <v>57946</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14619,7 +14624,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -14629,10 +14634,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>385185</v>
+        <v>385252</v>
       </c>
       <c r="R119" t="n">
-        <v>6858127</v>
+        <v>6858060</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14665,11 +14670,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14699,7 +14699,7 @@
         <v>132367396</v>
       </c>
       <c r="B120" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>132367428</v>
       </c>
       <c r="B121" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>132367432</v>
       </c>
       <c r="B122" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>132367433</v>
       </c>
       <c r="B124" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>132367446</v>
       </c>
       <c r="B125" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>132367453</v>
       </c>
       <c r="B126" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15430,10 +15430,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367395</v>
+        <v>132367462</v>
       </c>
       <c r="B127" t="n">
-        <v>79936</v>
+        <v>79077</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15441,21 +15441,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15465,10 +15465,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>384944</v>
+        <v>385195</v>
       </c>
       <c r="R127" t="n">
-        <v>6858169</v>
+        <v>6858154</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15527,53 +15527,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367425</v>
+        <v>132367464</v>
       </c>
       <c r="B128" t="n">
-        <v>57136</v>
+        <v>79077</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>385281</v>
+        <v>385318</v>
       </c>
       <c r="R128" t="n">
-        <v>6858170</v>
+        <v>6858113</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15632,10 +15624,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132367462</v>
+        <v>132367395</v>
       </c>
       <c r="B129" t="n">
-        <v>79075</v>
+        <v>79938</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15643,21 +15635,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15667,10 +15659,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>385195</v>
+        <v>384944</v>
       </c>
       <c r="R129" t="n">
-        <v>6858154</v>
+        <v>6858169</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15729,45 +15721,53 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132367464</v>
+        <v>132367425</v>
       </c>
       <c r="B130" t="n">
-        <v>79075</v>
+        <v>57137</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>385318</v>
+        <v>385281</v>
       </c>
       <c r="R130" t="n">
-        <v>6858113</v>
+        <v>6858170</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15829,7 +15829,7 @@
         <v>132367417</v>
       </c>
       <c r="B131" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15936,10 +15936,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367455</v>
+        <v>132367392</v>
       </c>
       <c r="B132" t="n">
-        <v>57945</v>
+        <v>79938</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15947,42 +15947,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>384840</v>
+        <v>385102</v>
       </c>
       <c r="R132" t="n">
-        <v>6858190</v>
+        <v>6858138</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16041,10 +16033,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367392</v>
+        <v>132367402</v>
       </c>
       <c r="B133" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16076,10 +16068,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>385102</v>
+        <v>385403</v>
       </c>
       <c r="R133" t="n">
-        <v>6858138</v>
+        <v>6857836</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16138,10 +16130,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132367402</v>
+        <v>132367455</v>
       </c>
       <c r="B134" t="n">
-        <v>79936</v>
+        <v>57946</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16149,34 +16141,42 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>385403</v>
+        <v>384840</v>
       </c>
       <c r="R134" t="n">
-        <v>6857836</v>
+        <v>6858190</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16238,7 +16238,7 @@
         <v>132367474</v>
       </c>
       <c r="B135" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>132367399</v>
       </c>
       <c r="B136" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16429,45 +16429,53 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367404</v>
+        <v>132367421</v>
       </c>
       <c r="B137" t="n">
-        <v>79907</v>
+        <v>57137</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385227</v>
+        <v>385249</v>
       </c>
       <c r="R137" t="n">
-        <v>6857907</v>
+        <v>6858148</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16526,10 +16534,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367421</v>
+        <v>132367431</v>
       </c>
       <c r="B138" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16569,10 +16577,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>385249</v>
+        <v>384950</v>
       </c>
       <c r="R138" t="n">
-        <v>6858148</v>
+        <v>6858169</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16631,10 +16639,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367431</v>
+        <v>132367413</v>
       </c>
       <c r="B139" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16674,10 +16682,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>384950</v>
+        <v>385181</v>
       </c>
       <c r="R139" t="n">
-        <v>6858169</v>
+        <v>6858109</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16736,53 +16744,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367413</v>
+        <v>132367404</v>
       </c>
       <c r="B140" t="n">
-        <v>57136</v>
+        <v>79909</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>385181</v>
+        <v>385227</v>
       </c>
       <c r="R140" t="n">
-        <v>6858109</v>
+        <v>6857907</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16841,10 +16841,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367468</v>
+        <v>132367424</v>
       </c>
       <c r="B141" t="n">
-        <v>8455</v>
+        <v>57137</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16852,30 +16852,29 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -16885,10 +16884,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>384943</v>
+        <v>385276</v>
       </c>
       <c r="R141" t="n">
-        <v>6858164</v>
+        <v>6858157</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16929,7 +16928,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16948,54 +16946,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367469</v>
+        <v>132367403</v>
       </c>
       <c r="B142" t="n">
-        <v>8455</v>
+        <v>79909</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>384988</v>
+        <v>385374</v>
       </c>
       <c r="R142" t="n">
-        <v>6858227</v>
+        <v>6857880</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17036,7 +17025,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17055,45 +17043,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367403</v>
+        <v>132367469</v>
       </c>
       <c r="B143" t="n">
-        <v>79907</v>
+        <v>8455</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>385374</v>
+        <v>384988</v>
       </c>
       <c r="R143" t="n">
-        <v>6857880</v>
+        <v>6858227</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17134,6 +17131,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -17152,10 +17150,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367424</v>
+        <v>132367468</v>
       </c>
       <c r="B144" t="n">
-        <v>57136</v>
+        <v>8455</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17163,29 +17161,30 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -17195,10 +17194,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>385276</v>
+        <v>384943</v>
       </c>
       <c r="R144" t="n">
-        <v>6858157</v>
+        <v>6858164</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17239,6 +17238,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -17260,7 +17260,7 @@
         <v>132367458</v>
       </c>
       <c r="B145" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>132367427</v>
       </c>
       <c r="B146" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>132367389</v>
       </c>
       <c r="B147" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367407</v>
+        <v>132367452</v>
       </c>
       <c r="B148" t="n">
-        <v>79907</v>
+        <v>57946</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17580,34 +17580,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>385124</v>
+        <v>384945</v>
       </c>
       <c r="R148" t="n">
-        <v>6858064</v>
+        <v>6858165</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17666,10 +17674,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367452</v>
+        <v>132367407</v>
       </c>
       <c r="B149" t="n">
-        <v>57945</v>
+        <v>79909</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17677,42 +17685,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>384945</v>
+        <v>385124</v>
       </c>
       <c r="R149" t="n">
-        <v>6858165</v>
+        <v>6858064</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17774,7 +17774,7 @@
         <v>132367418</v>
       </c>
       <c r="B150" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>132367410</v>
       </c>
       <c r="B151" t="n">
-        <v>79907</v>
+        <v>79909</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17973,32 +17973,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367459</v>
+        <v>132367398</v>
       </c>
       <c r="B152" t="n">
-        <v>97963</v>
+        <v>79938</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>384655</v>
+        <v>384804</v>
       </c>
       <c r="R152" t="n">
-        <v>6858187</v>
+        <v>6858152</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18044,11 +18044,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18075,32 +18070,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132367405</v>
+        <v>132367459</v>
       </c>
       <c r="B153" t="n">
-        <v>79907</v>
+        <v>97971</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18110,10 +18105,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>385332</v>
+        <v>384655</v>
       </c>
       <c r="R153" t="n">
-        <v>6858161</v>
+        <v>6858187</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18146,6 +18141,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18172,10 +18172,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132367398</v>
+        <v>132367405</v>
       </c>
       <c r="B154" t="n">
-        <v>79936</v>
+        <v>79909</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18183,21 +18183,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18207,10 +18207,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>384804</v>
+        <v>385332</v>
       </c>
       <c r="R154" t="n">
-        <v>6858152</v>
+        <v>6858161</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18269,10 +18269,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367391</v>
+        <v>132367434</v>
       </c>
       <c r="B155" t="n">
-        <v>79936</v>
+        <v>58110</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18280,34 +18280,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385129</v>
+        <v>385087</v>
       </c>
       <c r="R155" t="n">
-        <v>6858060</v>
+        <v>6858055</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18366,53 +18374,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367416</v>
+        <v>132367391</v>
       </c>
       <c r="B156" t="n">
-        <v>57136</v>
+        <v>79938</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385185</v>
+        <v>385129</v>
       </c>
       <c r="R156" t="n">
-        <v>6858146</v>
+        <v>6858060</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18471,10 +18471,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367422</v>
+        <v>132367416</v>
       </c>
       <c r="B157" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18514,10 +18514,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385246</v>
+        <v>385185</v>
       </c>
       <c r="R157" t="n">
-        <v>6858162</v>
+        <v>6858146</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18576,32 +18576,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367434</v>
+        <v>132367422</v>
       </c>
       <c r="B158" t="n">
-        <v>58109</v>
+        <v>57137</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -18619,10 +18619,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385087</v>
+        <v>385246</v>
       </c>
       <c r="R158" t="n">
-        <v>6858055</v>
+        <v>6858162</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18684,7 +18684,7 @@
         <v>132367406</v>
       </c>
       <c r="B159" t="n">
-        <v>79907</v>
+        <v>79909</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18782,10 +18782,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367465</v>
+        <v>132367450</v>
       </c>
       <c r="B160" t="n">
-        <v>79075</v>
+        <v>57946</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18793,34 +18793,42 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385131</v>
+        <v>385107</v>
       </c>
       <c r="R160" t="n">
-        <v>6858065</v>
+        <v>6858161</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18879,27 +18887,27 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367471</v>
+        <v>132367420</v>
       </c>
       <c r="B161" t="n">
-        <v>58080</v>
+        <v>57137</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>205976</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -18912,7 +18920,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -18922,10 +18930,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385400</v>
+        <v>385235</v>
       </c>
       <c r="R161" t="n">
-        <v>6857831</v>
+        <v>6858146</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18984,10 +18992,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367495</v>
+        <v>132367414</v>
       </c>
       <c r="B162" t="n">
-        <v>106222</v>
+        <v>57137</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18995,27 +19003,31 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
@@ -19023,10 +19035,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>384848</v>
+        <v>385197</v>
       </c>
       <c r="R162" t="n">
-        <v>6858075</v>
+        <v>6858108</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19061,18 +19073,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -19091,45 +19097,49 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367408</v>
+        <v>132367495</v>
       </c>
       <c r="B163" t="n">
-        <v>79907</v>
+        <v>106230</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>229821</v>
+        <v>221144</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385062</v>
+        <v>384848</v>
       </c>
       <c r="R163" t="n">
-        <v>6858092</v>
+        <v>6858075</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19164,12 +19174,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -19188,27 +19204,27 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367414</v>
+        <v>132367471</v>
       </c>
       <c r="B164" t="n">
-        <v>57136</v>
+        <v>58081</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100138</v>
+        <v>205976</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -19221,7 +19237,7 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -19231,10 +19247,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385197</v>
+        <v>385400</v>
       </c>
       <c r="R164" t="n">
-        <v>6858108</v>
+        <v>6857831</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19293,10 +19309,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367450</v>
+        <v>132367465</v>
       </c>
       <c r="B165" t="n">
-        <v>57945</v>
+        <v>79077</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19304,42 +19320,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385107</v>
+        <v>385131</v>
       </c>
       <c r="R165" t="n">
-        <v>6858161</v>
+        <v>6858065</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19398,53 +19406,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367420</v>
+        <v>132367408</v>
       </c>
       <c r="B166" t="n">
-        <v>57136</v>
+        <v>79909</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385235</v>
+        <v>385062</v>
       </c>
       <c r="R166" t="n">
-        <v>6858146</v>
+        <v>6858092</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19506,7 +19506,7 @@
         <v>132367467</v>
       </c>
       <c r="B167" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19600,10 +19600,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367461</v>
+        <v>132367502</v>
       </c>
       <c r="B168" t="n">
-        <v>79075</v>
+        <v>78722</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19611,34 +19611,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385227</v>
+        <v>385349</v>
       </c>
       <c r="R168" t="n">
-        <v>6857907</v>
+        <v>6857860</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19679,8 +19682,29 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -19697,10 +19721,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367502</v>
+        <v>132367393</v>
       </c>
       <c r="B169" t="n">
-        <v>78720</v>
+        <v>79938</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19708,37 +19732,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385349</v>
+        <v>385118</v>
       </c>
       <c r="R169" t="n">
-        <v>6857860</v>
+        <v>6858178</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19779,29 +19800,8 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
@@ -19818,10 +19818,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367393</v>
+        <v>132367461</v>
       </c>
       <c r="B170" t="n">
-        <v>79936</v>
+        <v>79077</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19829,21 +19829,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19853,10 +19853,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385118</v>
+        <v>385227</v>
       </c>
       <c r="R170" t="n">
-        <v>6858178</v>
+        <v>6857907</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19918,7 +19918,7 @@
         <v>132367423</v>
       </c>
       <c r="B171" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367447</v>
+        <v>132367401</v>
       </c>
       <c r="B172" t="n">
-        <v>57945</v>
+        <v>79938</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,42 +20031,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>385333</v>
+        <v>384992</v>
       </c>
       <c r="R172" t="n">
-        <v>6858152</v>
+        <v>6858018</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20125,10 +20117,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132367457</v>
+        <v>132367447</v>
       </c>
       <c r="B173" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20158,7 +20150,7 @@
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
@@ -20168,10 +20160,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>385184</v>
+        <v>385333</v>
       </c>
       <c r="R173" t="n">
-        <v>6857885</v>
+        <v>6858152</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20230,10 +20222,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367401</v>
+        <v>132367457</v>
       </c>
       <c r="B174" t="n">
-        <v>79936</v>
+        <v>57946</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20241,34 +20233,42 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>384992</v>
+        <v>385184</v>
       </c>
       <c r="R174" t="n">
-        <v>6858018</v>
+        <v>6857885</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20330,7 +20330,7 @@
         <v>132367409</v>
       </c>
       <c r="B175" t="n">
-        <v>79907</v>
+        <v>79909</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -16841,10 +16841,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367424</v>
+        <v>132367469</v>
       </c>
       <c r="B141" t="n">
-        <v>57137</v>
+        <v>8455</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16852,29 +16852,30 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -16884,10 +16885,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>385276</v>
+        <v>384988</v>
       </c>
       <c r="R141" t="n">
-        <v>6858157</v>
+        <v>6858227</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16928,6 +16929,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16946,45 +16948,54 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367403</v>
+        <v>132367468</v>
       </c>
       <c r="B142" t="n">
-        <v>79909</v>
+        <v>8455</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>385374</v>
+        <v>384943</v>
       </c>
       <c r="R142" t="n">
-        <v>6857880</v>
+        <v>6858164</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17025,6 +17036,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17043,10 +17055,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367469</v>
+        <v>132367424</v>
       </c>
       <c r="B143" t="n">
-        <v>8455</v>
+        <v>57137</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17054,30 +17066,29 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -17087,10 +17098,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>384988</v>
+        <v>385276</v>
       </c>
       <c r="R143" t="n">
-        <v>6858227</v>
+        <v>6858157</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17131,7 +17142,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -17150,54 +17160,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367468</v>
+        <v>132367403</v>
       </c>
       <c r="B144" t="n">
-        <v>8455</v>
+        <v>79909</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>384943</v>
+        <v>385374</v>
       </c>
       <c r="R144" t="n">
-        <v>6858164</v>
+        <v>6857880</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17238,7 +17239,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -17771,53 +17771,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132367418</v>
+        <v>132367410</v>
       </c>
       <c r="B150" t="n">
-        <v>57137</v>
+        <v>79909</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>385198</v>
+        <v>384959</v>
       </c>
       <c r="R150" t="n">
-        <v>6858144</v>
+        <v>6858242</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17876,45 +17868,53 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>132367410</v>
+        <v>132367418</v>
       </c>
       <c r="B151" t="n">
-        <v>79909</v>
+        <v>57137</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>384959</v>
+        <v>385198</v>
       </c>
       <c r="R151" t="n">
-        <v>6858242</v>
+        <v>6858144</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18269,32 +18269,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367434</v>
+        <v>132367416</v>
       </c>
       <c r="B155" t="n">
-        <v>58110</v>
+        <v>57137</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18302,7 +18302,7 @@
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -18312,10 +18312,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385087</v>
+        <v>385185</v>
       </c>
       <c r="R155" t="n">
-        <v>6858055</v>
+        <v>6858146</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18374,45 +18374,53 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367391</v>
+        <v>132367422</v>
       </c>
       <c r="B156" t="n">
-        <v>79938</v>
+        <v>57137</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385129</v>
+        <v>385246</v>
       </c>
       <c r="R156" t="n">
-        <v>6858060</v>
+        <v>6858162</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18471,42 +18479,37 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367416</v>
+        <v>132367406</v>
       </c>
       <c r="B157" t="n">
-        <v>57137</v>
+        <v>79909</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -18514,10 +18517,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385185</v>
+        <v>385318</v>
       </c>
       <c r="R157" t="n">
-        <v>6858146</v>
+        <v>6858113</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18558,6 +18561,7 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -18576,53 +18580,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367422</v>
+        <v>132367391</v>
       </c>
       <c r="B158" t="n">
-        <v>57137</v>
+        <v>79938</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385246</v>
+        <v>385129</v>
       </c>
       <c r="R158" t="n">
-        <v>6858162</v>
+        <v>6858060</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18681,10 +18677,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367406</v>
+        <v>132367434</v>
       </c>
       <c r="B159" t="n">
-        <v>79909</v>
+        <v>58110</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18692,26 +18688,31 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18719,10 +18720,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385318</v>
+        <v>385087</v>
       </c>
       <c r="R159" t="n">
-        <v>6858113</v>
+        <v>6858055</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18763,7 +18764,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367401</v>
+        <v>132367409</v>
       </c>
       <c r="B172" t="n">
-        <v>79938</v>
+        <v>79909</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,21 +20031,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -20055,10 +20055,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>384992</v>
+        <v>385075</v>
       </c>
       <c r="R172" t="n">
-        <v>6858018</v>
+        <v>6858201</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20117,10 +20117,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132367447</v>
+        <v>132367401</v>
       </c>
       <c r="B173" t="n">
-        <v>57946</v>
+        <v>79938</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20128,42 +20128,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>385333</v>
+        <v>384992</v>
       </c>
       <c r="R173" t="n">
-        <v>6858152</v>
+        <v>6858018</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20222,7 +20214,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367457</v>
+        <v>132367447</v>
       </c>
       <c r="B174" t="n">
         <v>57946</v>
@@ -20255,7 +20247,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -20265,10 +20257,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385184</v>
+        <v>385333</v>
       </c>
       <c r="R174" t="n">
-        <v>6857885</v>
+        <v>6858152</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20327,10 +20319,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132367409</v>
+        <v>132367457</v>
       </c>
       <c r="B175" t="n">
-        <v>79909</v>
+        <v>57946</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20338,34 +20330,42 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>385075</v>
+        <v>385184</v>
       </c>
       <c r="R175" t="n">
-        <v>6858201</v>
+        <v>6857885</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13129,7 +13129,7 @@
         <v>132367475</v>
       </c>
       <c r="B105" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>132367394</v>
       </c>
       <c r="B106" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>132367501</v>
       </c>
       <c r="B107" t="n">
-        <v>78326</v>
+        <v>78334</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>132367449</v>
       </c>
       <c r="B108" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>132367444</v>
       </c>
       <c r="B109" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>132367443</v>
       </c>
       <c r="B110" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>132367430</v>
       </c>
       <c r="B111" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>132367463</v>
       </c>
       <c r="B112" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>132367466</v>
       </c>
       <c r="B113" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14061,10 +14061,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132367435</v>
+        <v>132367451</v>
       </c>
       <c r="B114" t="n">
-        <v>58110</v>
+        <v>57950</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14072,21 +14072,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14094,7 +14094,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -14104,10 +14104,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>384859</v>
+        <v>385088</v>
       </c>
       <c r="R114" t="n">
-        <v>6858073</v>
+        <v>6858196</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14166,10 +14166,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132367451</v>
+        <v>132367456</v>
       </c>
       <c r="B115" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>385088</v>
+        <v>385112</v>
       </c>
       <c r="R115" t="n">
-        <v>6858196</v>
+        <v>6857918</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14271,10 +14271,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132367456</v>
+        <v>132367435</v>
       </c>
       <c r="B116" t="n">
-        <v>57946</v>
+        <v>58114</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14282,21 +14282,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>385112</v>
+        <v>384859</v>
       </c>
       <c r="R116" t="n">
-        <v>6857918</v>
+        <v>6858073</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14376,32 +14376,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132367412</v>
+        <v>132367448</v>
       </c>
       <c r="B117" t="n">
-        <v>57137</v>
+        <v>57950</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14409,7 +14409,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>385208</v>
+        <v>385252</v>
       </c>
       <c r="R117" t="n">
-        <v>6858049</v>
+        <v>6858060</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14481,10 +14481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132367415</v>
+        <v>132367412</v>
       </c>
       <c r="B118" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>385185</v>
+        <v>385208</v>
       </c>
       <c r="R118" t="n">
-        <v>6858127</v>
+        <v>6858049</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14560,11 +14560,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14591,32 +14586,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132367448</v>
+        <v>132367415</v>
       </c>
       <c r="B119" t="n">
-        <v>57946</v>
+        <v>57141</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14624,7 +14619,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -14634,10 +14629,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>385252</v>
+        <v>385185</v>
       </c>
       <c r="R119" t="n">
-        <v>6858060</v>
+        <v>6858127</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14670,6 +14665,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14699,7 +14699,7 @@
         <v>132367396</v>
       </c>
       <c r="B120" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14793,10 +14793,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132367428</v>
+        <v>132367470</v>
       </c>
       <c r="B121" t="n">
-        <v>57137</v>
+        <v>8455</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14804,29 +14804,30 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14836,10 +14837,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>385279</v>
+        <v>384910</v>
       </c>
       <c r="R121" t="n">
-        <v>6858073</v>
+        <v>6858203</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14874,17 +14875,13 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -14906,7 +14903,7 @@
         <v>132367432</v>
       </c>
       <c r="B122" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15008,10 +15005,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132367470</v>
+        <v>132367428</v>
       </c>
       <c r="B123" t="n">
-        <v>8455</v>
+        <v>57141</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15019,30 +15016,29 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -15052,10 +15048,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>384910</v>
+        <v>385279</v>
       </c>
       <c r="R123" t="n">
-        <v>6858203</v>
+        <v>6858073</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15090,13 +15086,17 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>132367433</v>
       </c>
       <c r="B124" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15220,10 +15220,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367446</v>
+        <v>132367395</v>
       </c>
       <c r="B125" t="n">
-        <v>57946</v>
+        <v>79946</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15231,42 +15231,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>385178</v>
+        <v>384944</v>
       </c>
       <c r="R125" t="n">
-        <v>6858121</v>
+        <v>6858169</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15325,10 +15317,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132367453</v>
+        <v>132367446</v>
       </c>
       <c r="B126" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15358,7 +15350,7 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -15368,10 +15360,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>384934</v>
+        <v>385178</v>
       </c>
       <c r="R126" t="n">
-        <v>6858197</v>
+        <v>6858121</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15430,10 +15422,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367462</v>
+        <v>132367453</v>
       </c>
       <c r="B127" t="n">
-        <v>79077</v>
+        <v>57950</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15441,34 +15433,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>385195</v>
+        <v>384934</v>
       </c>
       <c r="R127" t="n">
-        <v>6858154</v>
+        <v>6858197</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15527,45 +15527,53 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367464</v>
+        <v>132367425</v>
       </c>
       <c r="B128" t="n">
-        <v>79077</v>
+        <v>57141</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>385318</v>
+        <v>385281</v>
       </c>
       <c r="R128" t="n">
-        <v>6858113</v>
+        <v>6858170</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15624,10 +15632,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132367395</v>
+        <v>132367462</v>
       </c>
       <c r="B129" t="n">
-        <v>79938</v>
+        <v>79085</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15635,21 +15643,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15659,10 +15667,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>384944</v>
+        <v>385195</v>
       </c>
       <c r="R129" t="n">
-        <v>6858169</v>
+        <v>6858154</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15721,53 +15729,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132367425</v>
+        <v>132367464</v>
       </c>
       <c r="B130" t="n">
-        <v>57137</v>
+        <v>79085</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>385281</v>
+        <v>385318</v>
       </c>
       <c r="R130" t="n">
-        <v>6858170</v>
+        <v>6858113</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15826,53 +15826,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367417</v>
+        <v>132367392</v>
       </c>
       <c r="B131" t="n">
-        <v>57137</v>
+        <v>79946</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>385203</v>
+        <v>385102</v>
       </c>
       <c r="R131" t="n">
-        <v>6858134</v>
+        <v>6858138</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15905,11 +15897,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15936,10 +15923,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367392</v>
+        <v>132367402</v>
       </c>
       <c r="B132" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15971,10 +15958,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385102</v>
+        <v>385403</v>
       </c>
       <c r="R132" t="n">
-        <v>6858138</v>
+        <v>6857836</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16033,45 +16020,53 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367402</v>
+        <v>132367417</v>
       </c>
       <c r="B133" t="n">
-        <v>79938</v>
+        <v>57141</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>385403</v>
+        <v>385203</v>
       </c>
       <c r="R133" t="n">
-        <v>6857836</v>
+        <v>6858134</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16104,6 +16099,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16133,7 +16133,7 @@
         <v>132367455</v>
       </c>
       <c r="B134" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>132367474</v>
       </c>
       <c r="B135" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>132367399</v>
       </c>
       <c r="B136" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16429,53 +16429,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367421</v>
+        <v>132367404</v>
       </c>
       <c r="B137" t="n">
-        <v>57137</v>
+        <v>79917</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385249</v>
+        <v>385227</v>
       </c>
       <c r="R137" t="n">
-        <v>6858148</v>
+        <v>6857907</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16534,10 +16526,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367431</v>
+        <v>132367421</v>
       </c>
       <c r="B138" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16577,10 +16569,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>384950</v>
+        <v>385249</v>
       </c>
       <c r="R138" t="n">
-        <v>6858169</v>
+        <v>6858148</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16642,7 +16634,7 @@
         <v>132367413</v>
       </c>
       <c r="B139" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16744,45 +16736,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367404</v>
+        <v>132367431</v>
       </c>
       <c r="B140" t="n">
-        <v>79909</v>
+        <v>57141</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>385227</v>
+        <v>384950</v>
       </c>
       <c r="R140" t="n">
-        <v>6857907</v>
+        <v>6858169</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16841,54 +16841,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367469</v>
+        <v>132367403</v>
       </c>
       <c r="B141" t="n">
-        <v>8455</v>
+        <v>79917</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>384988</v>
+        <v>385374</v>
       </c>
       <c r="R141" t="n">
-        <v>6858227</v>
+        <v>6857880</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16929,7 +16920,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16948,10 +16938,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367468</v>
+        <v>132367424</v>
       </c>
       <c r="B142" t="n">
-        <v>8455</v>
+        <v>57141</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16959,30 +16949,29 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -16992,10 +16981,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>384943</v>
+        <v>385276</v>
       </c>
       <c r="R142" t="n">
-        <v>6858164</v>
+        <v>6858157</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17036,7 +17025,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17055,10 +17043,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367424</v>
+        <v>132367469</v>
       </c>
       <c r="B143" t="n">
-        <v>57137</v>
+        <v>8455</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17066,29 +17054,30 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -17098,10 +17087,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>385276</v>
+        <v>384988</v>
       </c>
       <c r="R143" t="n">
-        <v>6858157</v>
+        <v>6858227</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17142,6 +17131,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -17160,45 +17150,54 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367403</v>
+        <v>132367468</v>
       </c>
       <c r="B144" t="n">
-        <v>79909</v>
+        <v>8455</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>385374</v>
+        <v>384943</v>
       </c>
       <c r="R144" t="n">
-        <v>6857880</v>
+        <v>6858164</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17239,6 +17238,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -17260,7 +17260,7 @@
         <v>132367458</v>
       </c>
       <c r="B145" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>132367427</v>
       </c>
       <c r="B146" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17472,10 +17472,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132367389</v>
+        <v>132367407</v>
       </c>
       <c r="B147" t="n">
-        <v>79938</v>
+        <v>79917</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17507,10 +17507,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>385195</v>
+        <v>385124</v>
       </c>
       <c r="R147" t="n">
-        <v>6858154</v>
+        <v>6858064</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367452</v>
+        <v>132367389</v>
       </c>
       <c r="B148" t="n">
-        <v>57946</v>
+        <v>79946</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17580,42 +17580,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>384945</v>
+        <v>385195</v>
       </c>
       <c r="R148" t="n">
-        <v>6858165</v>
+        <v>6858154</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17674,10 +17666,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367407</v>
+        <v>132367452</v>
       </c>
       <c r="B149" t="n">
-        <v>79909</v>
+        <v>57950</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17685,34 +17677,42 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>385124</v>
+        <v>384945</v>
       </c>
       <c r="R149" t="n">
-        <v>6858064</v>
+        <v>6858165</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17774,7 +17774,7 @@
         <v>132367410</v>
       </c>
       <c r="B150" t="n">
-        <v>79909</v>
+        <v>79917</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>132367418</v>
       </c>
       <c r="B151" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>132367398</v>
       </c>
       <c r="B152" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>132367459</v>
       </c>
       <c r="B153" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>132367405</v>
       </c>
       <c r="B154" t="n">
-        <v>79909</v>
+        <v>79917</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18269,10 +18269,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367416</v>
+        <v>132367422</v>
       </c>
       <c r="B155" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18312,10 +18312,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385185</v>
+        <v>385246</v>
       </c>
       <c r="R155" t="n">
-        <v>6858146</v>
+        <v>6858162</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18374,10 +18374,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367422</v>
+        <v>132367416</v>
       </c>
       <c r="B156" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18417,10 +18417,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385246</v>
+        <v>385185</v>
       </c>
       <c r="R156" t="n">
-        <v>6858162</v>
+        <v>6858146</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18482,7 +18482,7 @@
         <v>132367406</v>
       </c>
       <c r="B157" t="n">
-        <v>79909</v>
+        <v>79917</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>132367391</v>
       </c>
       <c r="B158" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>132367434</v>
       </c>
       <c r="B159" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18782,32 +18782,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367450</v>
+        <v>132367414</v>
       </c>
       <c r="B160" t="n">
-        <v>57946</v>
+        <v>57141</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18815,7 +18815,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385107</v>
+        <v>385197</v>
       </c>
       <c r="R160" t="n">
-        <v>6858161</v>
+        <v>6858108</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18890,7 +18890,7 @@
         <v>132367420</v>
       </c>
       <c r="B161" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18992,27 +18992,27 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367414</v>
+        <v>132367471</v>
       </c>
       <c r="B162" t="n">
-        <v>57137</v>
+        <v>58085</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>205976</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -19025,7 +19025,7 @@
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -19035,10 +19035,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385197</v>
+        <v>385400</v>
       </c>
       <c r="R162" t="n">
-        <v>6858108</v>
+        <v>6857831</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19097,38 +19097,42 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367495</v>
+        <v>132367450</v>
       </c>
       <c r="B163" t="n">
-        <v>106230</v>
+        <v>57950</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -19136,10 +19140,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>384848</v>
+        <v>385107</v>
       </c>
       <c r="R163" t="n">
-        <v>6858075</v>
+        <v>6858161</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19174,18 +19178,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -19204,42 +19202,38 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367471</v>
+        <v>132367495</v>
       </c>
       <c r="B164" t="n">
-        <v>58081</v>
+        <v>106241</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>205976</v>
+        <v>221144</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19247,10 +19241,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385400</v>
+        <v>384848</v>
       </c>
       <c r="R164" t="n">
-        <v>6857831</v>
+        <v>6858075</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19285,12 +19279,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -19312,7 +19312,7 @@
         <v>132367465</v>
       </c>
       <c r="B165" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>132367408</v>
       </c>
       <c r="B166" t="n">
-        <v>79909</v>
+        <v>79917</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>132367467</v>
       </c>
       <c r="B167" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19600,37 +19600,42 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367502</v>
+        <v>132367423</v>
       </c>
       <c r="B168" t="n">
-        <v>78722</v>
+        <v>57141</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -19638,10 +19643,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385349</v>
+        <v>385263</v>
       </c>
       <c r="R168" t="n">
-        <v>6857860</v>
+        <v>6858153</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19682,29 +19687,8 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -19721,10 +19705,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367393</v>
+        <v>132367461</v>
       </c>
       <c r="B169" t="n">
-        <v>79938</v>
+        <v>79085</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19732,21 +19716,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19756,10 +19740,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385118</v>
+        <v>385227</v>
       </c>
       <c r="R169" t="n">
-        <v>6858178</v>
+        <v>6857907</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19818,10 +19802,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367461</v>
+        <v>132367502</v>
       </c>
       <c r="B170" t="n">
-        <v>79077</v>
+        <v>78730</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19829,34 +19813,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385227</v>
+        <v>385349</v>
       </c>
       <c r="R170" t="n">
-        <v>6857907</v>
+        <v>6857860</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19897,8 +19884,29 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
@@ -19915,53 +19923,45 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367423</v>
+        <v>132367393</v>
       </c>
       <c r="B171" t="n">
-        <v>57137</v>
+        <v>79946</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385263</v>
+        <v>385118</v>
       </c>
       <c r="R171" t="n">
-        <v>6858153</v>
+        <v>6858178</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20023,7 +20023,7 @@
         <v>132367409</v>
       </c>
       <c r="B172" t="n">
-        <v>79909</v>
+        <v>79917</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>132367401</v>
       </c>
       <c r="B173" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>132367447</v>
       </c>
       <c r="B174" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>132367457</v>
       </c>
       <c r="B175" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -14793,10 +14793,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132367470</v>
+        <v>132367428</v>
       </c>
       <c r="B121" t="n">
-        <v>8455</v>
+        <v>57141</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14804,30 +14804,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14837,10 +14836,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>384910</v>
+        <v>385279</v>
       </c>
       <c r="R121" t="n">
-        <v>6858203</v>
+        <v>6858073</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14875,13 +14874,17 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -15005,10 +15008,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132367428</v>
+        <v>132367470</v>
       </c>
       <c r="B123" t="n">
-        <v>57141</v>
+        <v>8455</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15016,29 +15019,30 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -15048,10 +15052,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>385279</v>
+        <v>384910</v>
       </c>
       <c r="R123" t="n">
-        <v>6858073</v>
+        <v>6858203</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15086,17 +15090,13 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -15220,45 +15220,53 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367395</v>
+        <v>132367425</v>
       </c>
       <c r="B125" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>384944</v>
+        <v>385281</v>
       </c>
       <c r="R125" t="n">
-        <v>6858169</v>
+        <v>6858170</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15317,10 +15325,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132367446</v>
+        <v>132367395</v>
       </c>
       <c r="B126" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15328,42 +15336,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>385178</v>
+        <v>384944</v>
       </c>
       <c r="R126" t="n">
-        <v>6858121</v>
+        <v>6858169</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15422,7 +15422,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367453</v>
+        <v>132367446</v>
       </c>
       <c r="B127" t="n">
         <v>57950</v>
@@ -15455,7 +15455,7 @@
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -15465,10 +15465,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>384934</v>
+        <v>385178</v>
       </c>
       <c r="R127" t="n">
-        <v>6858197</v>
+        <v>6858121</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15527,32 +15527,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367425</v>
+        <v>132367453</v>
       </c>
       <c r="B128" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15560,7 +15560,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -15570,10 +15570,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>385281</v>
+        <v>384934</v>
       </c>
       <c r="R128" t="n">
-        <v>6858170</v>
+        <v>6858197</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15826,10 +15826,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367392</v>
+        <v>132367455</v>
       </c>
       <c r="B131" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15837,34 +15837,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>385102</v>
+        <v>384840</v>
       </c>
       <c r="R131" t="n">
-        <v>6858138</v>
+        <v>6858190</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15923,45 +15931,53 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367402</v>
+        <v>132367417</v>
       </c>
       <c r="B132" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385403</v>
+        <v>385203</v>
       </c>
       <c r="R132" t="n">
-        <v>6857836</v>
+        <v>6858134</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15994,6 +16010,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16020,53 +16041,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367417</v>
+        <v>132367392</v>
       </c>
       <c r="B133" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>385203</v>
+        <v>385102</v>
       </c>
       <c r="R133" t="n">
-        <v>6858134</v>
+        <v>6858138</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16099,11 +16112,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16130,10 +16138,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132367455</v>
+        <v>132367402</v>
       </c>
       <c r="B134" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16141,42 +16149,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>384840</v>
+        <v>385403</v>
       </c>
       <c r="R134" t="n">
-        <v>6858190</v>
+        <v>6857836</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16235,45 +16235,53 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367474</v>
+        <v>132367421</v>
       </c>
       <c r="B135" t="n">
-        <v>79084</v>
+        <v>57141</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385318</v>
+        <v>385249</v>
       </c>
       <c r="R135" t="n">
-        <v>6858113</v>
+        <v>6858148</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16332,45 +16340,53 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367399</v>
+        <v>132367431</v>
       </c>
       <c r="B136" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>384873</v>
+        <v>384950</v>
       </c>
       <c r="R136" t="n">
-        <v>6858080</v>
+        <v>6858169</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16429,45 +16445,53 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367404</v>
+        <v>132367413</v>
       </c>
       <c r="B137" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385227</v>
+        <v>385181</v>
       </c>
       <c r="R137" t="n">
-        <v>6857907</v>
+        <v>6858109</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16526,53 +16550,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367421</v>
+        <v>132367474</v>
       </c>
       <c r="B138" t="n">
-        <v>57141</v>
+        <v>79084</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>385249</v>
+        <v>385318</v>
       </c>
       <c r="R138" t="n">
-        <v>6858148</v>
+        <v>6858113</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16631,53 +16647,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367413</v>
+        <v>132367399</v>
       </c>
       <c r="B139" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>385181</v>
+        <v>384873</v>
       </c>
       <c r="R139" t="n">
-        <v>6858109</v>
+        <v>6858080</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16736,53 +16744,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367431</v>
+        <v>132367404</v>
       </c>
       <c r="B140" t="n">
-        <v>57141</v>
+        <v>79917</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>384950</v>
+        <v>385227</v>
       </c>
       <c r="R140" t="n">
-        <v>6858169</v>
+        <v>6857907</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16841,45 +16841,53 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367403</v>
+        <v>132367424</v>
       </c>
       <c r="B141" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>385374</v>
+        <v>385276</v>
       </c>
       <c r="R141" t="n">
-        <v>6857880</v>
+        <v>6858157</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16938,53 +16946,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367424</v>
+        <v>132367403</v>
       </c>
       <c r="B142" t="n">
-        <v>57141</v>
+        <v>79917</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>385276</v>
+        <v>385374</v>
       </c>
       <c r="R142" t="n">
-        <v>6858157</v>
+        <v>6857880</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17472,10 +17472,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132367407</v>
+        <v>132367389</v>
       </c>
       <c r="B147" t="n">
-        <v>79917</v>
+        <v>79946</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17507,10 +17507,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>385124</v>
+        <v>385195</v>
       </c>
       <c r="R147" t="n">
-        <v>6858064</v>
+        <v>6858154</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367389</v>
+        <v>132367452</v>
       </c>
       <c r="B148" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17580,34 +17580,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>385195</v>
+        <v>384945</v>
       </c>
       <c r="R148" t="n">
-        <v>6858154</v>
+        <v>6858165</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17666,10 +17674,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367452</v>
+        <v>132367407</v>
       </c>
       <c r="B149" t="n">
-        <v>57950</v>
+        <v>79917</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17677,42 +17685,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>384945</v>
+        <v>385124</v>
       </c>
       <c r="R149" t="n">
-        <v>6858165</v>
+        <v>6858064</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17771,45 +17771,53 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132367410</v>
+        <v>132367418</v>
       </c>
       <c r="B150" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>384959</v>
+        <v>385198</v>
       </c>
       <c r="R150" t="n">
-        <v>6858242</v>
+        <v>6858144</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17868,53 +17876,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>132367418</v>
+        <v>132367410</v>
       </c>
       <c r="B151" t="n">
-        <v>57141</v>
+        <v>79917</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>385198</v>
+        <v>384959</v>
       </c>
       <c r="R151" t="n">
-        <v>6858144</v>
+        <v>6858242</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18073,7 +18073,7 @@
         <v>132367459</v>
       </c>
       <c r="B153" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18269,53 +18269,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367422</v>
+        <v>132367391</v>
       </c>
       <c r="B155" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385246</v>
+        <v>385129</v>
       </c>
       <c r="R155" t="n">
-        <v>6858162</v>
+        <v>6858060</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18479,37 +18471,42 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367406</v>
+        <v>132367422</v>
       </c>
       <c r="B157" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -18517,10 +18514,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385318</v>
+        <v>385246</v>
       </c>
       <c r="R157" t="n">
-        <v>6858113</v>
+        <v>6858162</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18561,7 +18558,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -18580,10 +18576,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367391</v>
+        <v>132367434</v>
       </c>
       <c r="B158" t="n">
-        <v>79946</v>
+        <v>58114</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18591,34 +18587,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385129</v>
+        <v>385087</v>
       </c>
       <c r="R158" t="n">
-        <v>6858060</v>
+        <v>6858055</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18677,10 +18681,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367434</v>
+        <v>132367406</v>
       </c>
       <c r="B159" t="n">
-        <v>58114</v>
+        <v>79917</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18688,31 +18692,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18720,10 +18719,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385087</v>
+        <v>385318</v>
       </c>
       <c r="R159" t="n">
-        <v>6858055</v>
+        <v>6858113</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18764,6 +18763,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18782,7 +18782,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367414</v>
+        <v>132367420</v>
       </c>
       <c r="B160" t="n">
         <v>57141</v>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385197</v>
+        <v>385235</v>
       </c>
       <c r="R160" t="n">
-        <v>6858108</v>
+        <v>6858146</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,7 +18887,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367420</v>
+        <v>132367414</v>
       </c>
       <c r="B161" t="n">
         <v>57141</v>
@@ -18930,10 +18930,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385235</v>
+        <v>385197</v>
       </c>
       <c r="R161" t="n">
-        <v>6858146</v>
+        <v>6858108</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19097,10 +19097,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367450</v>
+        <v>132367465</v>
       </c>
       <c r="B163" t="n">
-        <v>57950</v>
+        <v>79085</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19108,42 +19108,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385107</v>
+        <v>385131</v>
       </c>
       <c r="R163" t="n">
-        <v>6858161</v>
+        <v>6858065</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19202,49 +19194,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367495</v>
+        <v>132367408</v>
       </c>
       <c r="B164" t="n">
-        <v>106241</v>
+        <v>79917</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221144</v>
+        <v>229821</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>384848</v>
+        <v>385062</v>
       </c>
       <c r="R164" t="n">
-        <v>6858075</v>
+        <v>6858092</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19279,18 +19267,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -19309,10 +19291,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367465</v>
+        <v>132367450</v>
       </c>
       <c r="B165" t="n">
-        <v>79085</v>
+        <v>57950</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19320,34 +19302,42 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385131</v>
+        <v>385107</v>
       </c>
       <c r="R165" t="n">
-        <v>6858065</v>
+        <v>6858161</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19406,45 +19396,49 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367408</v>
+        <v>132367495</v>
       </c>
       <c r="B166" t="n">
-        <v>79917</v>
+        <v>106242</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>229821</v>
+        <v>221144</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385062</v>
+        <v>384848</v>
       </c>
       <c r="R166" t="n">
-        <v>6858092</v>
+        <v>6858075</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19479,12 +19473,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -19600,53 +19600,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367423</v>
+        <v>132367393</v>
       </c>
       <c r="B168" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385263</v>
+        <v>385118</v>
       </c>
       <c r="R168" t="n">
-        <v>6858153</v>
+        <v>6858178</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19705,45 +19697,53 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367461</v>
+        <v>132367423</v>
       </c>
       <c r="B169" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385227</v>
+        <v>385263</v>
       </c>
       <c r="R169" t="n">
-        <v>6857907</v>
+        <v>6858153</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19923,10 +19923,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367393</v>
+        <v>132367461</v>
       </c>
       <c r="B171" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19934,21 +19934,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385118</v>
+        <v>385227</v>
       </c>
       <c r="R171" t="n">
-        <v>6858178</v>
+        <v>6857907</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367409</v>
+        <v>132367447</v>
       </c>
       <c r="B172" t="n">
-        <v>79917</v>
+        <v>57950</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,34 +20031,42 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>385075</v>
+        <v>385333</v>
       </c>
       <c r="R172" t="n">
-        <v>6858201</v>
+        <v>6858152</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20117,10 +20125,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132367401</v>
+        <v>132367457</v>
       </c>
       <c r="B173" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20128,34 +20136,42 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>384992</v>
+        <v>385184</v>
       </c>
       <c r="R173" t="n">
-        <v>6858018</v>
+        <v>6857885</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20214,10 +20230,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367447</v>
+        <v>132367401</v>
       </c>
       <c r="B174" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20225,42 +20241,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385333</v>
+        <v>384992</v>
       </c>
       <c r="R174" t="n">
-        <v>6858152</v>
+        <v>6858018</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20319,10 +20327,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132367457</v>
+        <v>132367409</v>
       </c>
       <c r="B175" t="n">
-        <v>57950</v>
+        <v>79917</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20330,42 +20338,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>385184</v>
+        <v>385075</v>
       </c>
       <c r="R175" t="n">
-        <v>6857885</v>
+        <v>6858201</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13126,10 +13126,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132367475</v>
+        <v>132367449</v>
       </c>
       <c r="B105" t="n">
-        <v>79084</v>
+        <v>57950</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13137,34 +13137,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>384814</v>
+        <v>385133</v>
       </c>
       <c r="R105" t="n">
-        <v>6858214</v>
+        <v>6858066</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13223,10 +13231,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367394</v>
+        <v>132367475</v>
       </c>
       <c r="B106" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13234,21 +13242,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13258,10 +13266,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>384969</v>
+        <v>384814</v>
       </c>
       <c r="R106" t="n">
-        <v>6858130</v>
+        <v>6858214</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13320,10 +13328,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367501</v>
+        <v>132367394</v>
       </c>
       <c r="B107" t="n">
-        <v>78334</v>
+        <v>79946</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13331,21 +13339,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13355,10 +13363,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>385084</v>
+        <v>384969</v>
       </c>
       <c r="R107" t="n">
-        <v>6858195</v>
+        <v>6858130</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13399,34 +13407,8 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13443,10 +13425,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367449</v>
+        <v>132367501</v>
       </c>
       <c r="B108" t="n">
-        <v>57950</v>
+        <v>78334</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13454,42 +13436,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>385133</v>
+        <v>385084</v>
       </c>
       <c r="R108" t="n">
-        <v>6858066</v>
+        <v>6858195</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13530,8 +13504,34 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -13548,7 +13548,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367444</v>
+        <v>132367443</v>
       </c>
       <c r="B109" t="n">
         <v>57950</v>
@@ -13591,10 +13591,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385280</v>
+        <v>385408</v>
       </c>
       <c r="R109" t="n">
-        <v>6857923</v>
+        <v>6857862</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367443</v>
+        <v>132367444</v>
       </c>
       <c r="B110" t="n">
         <v>57950</v>
@@ -13696,10 +13696,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385408</v>
+        <v>385280</v>
       </c>
       <c r="R110" t="n">
-        <v>6857862</v>
+        <v>6857923</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14061,10 +14061,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132367451</v>
+        <v>132367435</v>
       </c>
       <c r="B114" t="n">
-        <v>57950</v>
+        <v>58114</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14072,21 +14072,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14094,7 +14094,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -14104,10 +14104,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>385088</v>
+        <v>384859</v>
       </c>
       <c r="R114" t="n">
-        <v>6858196</v>
+        <v>6858073</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14166,7 +14166,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132367456</v>
+        <v>132367451</v>
       </c>
       <c r="B115" t="n">
         <v>57950</v>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>385112</v>
+        <v>385088</v>
       </c>
       <c r="R115" t="n">
-        <v>6857918</v>
+        <v>6858196</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14271,10 +14271,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132367435</v>
+        <v>132367456</v>
       </c>
       <c r="B116" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14282,21 +14282,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>384859</v>
+        <v>385112</v>
       </c>
       <c r="R116" t="n">
-        <v>6858073</v>
+        <v>6857918</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15220,32 +15220,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367425</v>
+        <v>132367446</v>
       </c>
       <c r="B125" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15253,7 +15253,7 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -15263,10 +15263,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>385281</v>
+        <v>385178</v>
       </c>
       <c r="R125" t="n">
-        <v>6858170</v>
+        <v>6858121</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15325,10 +15325,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132367395</v>
+        <v>132367453</v>
       </c>
       <c r="B126" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15336,34 +15336,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>384944</v>
+        <v>384934</v>
       </c>
       <c r="R126" t="n">
-        <v>6858169</v>
+        <v>6858197</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15422,10 +15430,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367446</v>
+        <v>132367462</v>
       </c>
       <c r="B127" t="n">
-        <v>57950</v>
+        <v>79085</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15433,42 +15441,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>385178</v>
+        <v>385195</v>
       </c>
       <c r="R127" t="n">
-        <v>6858121</v>
+        <v>6858154</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15527,10 +15527,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367453</v>
+        <v>132367464</v>
       </c>
       <c r="B128" t="n">
-        <v>57950</v>
+        <v>79085</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15538,42 +15538,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>384934</v>
+        <v>385318</v>
       </c>
       <c r="R128" t="n">
-        <v>6858197</v>
+        <v>6858113</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15632,10 +15624,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132367462</v>
+        <v>132367395</v>
       </c>
       <c r="B129" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15643,21 +15635,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15667,10 +15659,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>385195</v>
+        <v>384944</v>
       </c>
       <c r="R129" t="n">
-        <v>6858154</v>
+        <v>6858169</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15729,45 +15721,53 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132367464</v>
+        <v>132367425</v>
       </c>
       <c r="B130" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>385318</v>
+        <v>385281</v>
       </c>
       <c r="R130" t="n">
-        <v>6858113</v>
+        <v>6858170</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15826,10 +15826,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367455</v>
+        <v>132367392</v>
       </c>
       <c r="B131" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15837,42 +15837,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>384840</v>
+        <v>385102</v>
       </c>
       <c r="R131" t="n">
-        <v>6858190</v>
+        <v>6858138</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15931,53 +15923,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367417</v>
+        <v>132367402</v>
       </c>
       <c r="B132" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385203</v>
+        <v>385403</v>
       </c>
       <c r="R132" t="n">
-        <v>6858134</v>
+        <v>6857836</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16010,11 +15994,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16041,10 +16020,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367392</v>
+        <v>132367455</v>
       </c>
       <c r="B133" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16052,34 +16031,42 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>385102</v>
+        <v>384840</v>
       </c>
       <c r="R133" t="n">
-        <v>6858138</v>
+        <v>6858190</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16138,45 +16125,53 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132367402</v>
+        <v>132367417</v>
       </c>
       <c r="B134" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>385403</v>
+        <v>385203</v>
       </c>
       <c r="R134" t="n">
-        <v>6857836</v>
+        <v>6858134</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16209,6 +16204,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16235,53 +16235,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367421</v>
+        <v>132367474</v>
       </c>
       <c r="B135" t="n">
-        <v>57141</v>
+        <v>79084</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385249</v>
+        <v>385318</v>
       </c>
       <c r="R135" t="n">
-        <v>6858148</v>
+        <v>6858113</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16340,53 +16332,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367431</v>
+        <v>132367399</v>
       </c>
       <c r="B136" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>384950</v>
+        <v>384873</v>
       </c>
       <c r="R136" t="n">
-        <v>6858169</v>
+        <v>6858080</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16445,7 +16429,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367413</v>
+        <v>132367421</v>
       </c>
       <c r="B137" t="n">
         <v>57141</v>
@@ -16488,10 +16472,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385181</v>
+        <v>385249</v>
       </c>
       <c r="R137" t="n">
-        <v>6858109</v>
+        <v>6858148</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16550,45 +16534,53 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367474</v>
+        <v>132367431</v>
       </c>
       <c r="B138" t="n">
-        <v>79084</v>
+        <v>57141</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>385318</v>
+        <v>384950</v>
       </c>
       <c r="R138" t="n">
-        <v>6858113</v>
+        <v>6858169</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16647,45 +16639,53 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367399</v>
+        <v>132367413</v>
       </c>
       <c r="B139" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>384873</v>
+        <v>385181</v>
       </c>
       <c r="R139" t="n">
-        <v>6858080</v>
+        <v>6858109</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16841,53 +16841,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367424</v>
+        <v>132367403</v>
       </c>
       <c r="B141" t="n">
-        <v>57141</v>
+        <v>79917</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>385276</v>
+        <v>385374</v>
       </c>
       <c r="R141" t="n">
-        <v>6858157</v>
+        <v>6857880</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16946,45 +16938,53 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367403</v>
+        <v>132367424</v>
       </c>
       <c r="B142" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>385374</v>
+        <v>385276</v>
       </c>
       <c r="R142" t="n">
-        <v>6857880</v>
+        <v>6858157</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17043,7 +17043,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367469</v>
+        <v>132367468</v>
       </c>
       <c r="B143" t="n">
         <v>8455</v>
@@ -17077,7 +17077,7 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>384988</v>
+        <v>384943</v>
       </c>
       <c r="R143" t="n">
-        <v>6858227</v>
+        <v>6858164</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17150,7 +17150,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367468</v>
+        <v>132367469</v>
       </c>
       <c r="B144" t="n">
         <v>8455</v>
@@ -17184,7 +17184,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -17194,10 +17194,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>384943</v>
+        <v>384988</v>
       </c>
       <c r="R144" t="n">
-        <v>6858164</v>
+        <v>6858227</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -18073,7 +18073,7 @@
         <v>132367459</v>
       </c>
       <c r="B153" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18269,10 +18269,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367391</v>
+        <v>132367434</v>
       </c>
       <c r="B155" t="n">
-        <v>79946</v>
+        <v>58114</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18280,34 +18280,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385129</v>
+        <v>385087</v>
       </c>
       <c r="R155" t="n">
-        <v>6858060</v>
+        <v>6858055</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18366,42 +18374,37 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367416</v>
+        <v>132367406</v>
       </c>
       <c r="B156" t="n">
-        <v>57141</v>
+        <v>79917</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -18409,10 +18412,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385185</v>
+        <v>385318</v>
       </c>
       <c r="R156" t="n">
-        <v>6858146</v>
+        <v>6858113</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18453,6 +18456,7 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -18471,53 +18475,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367422</v>
+        <v>132367391</v>
       </c>
       <c r="B157" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385246</v>
+        <v>385129</v>
       </c>
       <c r="R157" t="n">
-        <v>6858162</v>
+        <v>6858060</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18576,32 +18572,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367434</v>
+        <v>132367416</v>
       </c>
       <c r="B158" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18609,7 +18605,7 @@
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -18619,10 +18615,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385087</v>
+        <v>385185</v>
       </c>
       <c r="R158" t="n">
-        <v>6858055</v>
+        <v>6858146</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18681,37 +18677,42 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367406</v>
+        <v>132367422</v>
       </c>
       <c r="B159" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18719,10 +18720,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385318</v>
+        <v>385246</v>
       </c>
       <c r="R159" t="n">
-        <v>6858113</v>
+        <v>6858162</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18763,7 +18764,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18782,27 +18782,27 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367420</v>
+        <v>132367471</v>
       </c>
       <c r="B160" t="n">
-        <v>57141</v>
+        <v>58085</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100138</v>
+        <v>205976</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -18815,7 +18815,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385235</v>
+        <v>385400</v>
       </c>
       <c r="R160" t="n">
-        <v>6858146</v>
+        <v>6857831</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,53 +18887,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367414</v>
+        <v>132367465</v>
       </c>
       <c r="B161" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385197</v>
+        <v>385131</v>
       </c>
       <c r="R161" t="n">
-        <v>6858108</v>
+        <v>6858065</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18992,10 +18984,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367471</v>
+        <v>132367408</v>
       </c>
       <c r="B162" t="n">
-        <v>58085</v>
+        <v>79917</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19003,42 +18995,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>205976</v>
+        <v>229821</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385400</v>
+        <v>385062</v>
       </c>
       <c r="R162" t="n">
-        <v>6857831</v>
+        <v>6858092</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19097,10 +19081,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367465</v>
+        <v>132367450</v>
       </c>
       <c r="B163" t="n">
-        <v>79085</v>
+        <v>57950</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19108,34 +19092,42 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385131</v>
+        <v>385107</v>
       </c>
       <c r="R163" t="n">
-        <v>6858065</v>
+        <v>6858161</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19194,45 +19186,53 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367408</v>
+        <v>132367420</v>
       </c>
       <c r="B164" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385062</v>
+        <v>385235</v>
       </c>
       <c r="R164" t="n">
-        <v>6858092</v>
+        <v>6858146</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19291,32 +19291,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367450</v>
+        <v>132367414</v>
       </c>
       <c r="B165" t="n">
-        <v>57950</v>
+        <v>57141</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19324,7 +19324,7 @@
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
@@ -19334,10 +19334,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385107</v>
+        <v>385197</v>
       </c>
       <c r="R165" t="n">
-        <v>6858161</v>
+        <v>6858108</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19399,7 +19399,7 @@
         <v>132367495</v>
       </c>
       <c r="B166" t="n">
-        <v>106242</v>
+        <v>106243</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19600,10 +19600,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367393</v>
+        <v>132367461</v>
       </c>
       <c r="B168" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19611,21 +19611,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19635,10 +19635,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385118</v>
+        <v>385227</v>
       </c>
       <c r="R168" t="n">
-        <v>6858178</v>
+        <v>6857907</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19923,10 +19923,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367461</v>
+        <v>132367393</v>
       </c>
       <c r="B171" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19934,21 +19934,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385227</v>
+        <v>385118</v>
       </c>
       <c r="R171" t="n">
-        <v>6857907</v>
+        <v>6858178</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367447</v>
+        <v>132367401</v>
       </c>
       <c r="B172" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,42 +20031,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>385333</v>
+        <v>384992</v>
       </c>
       <c r="R172" t="n">
-        <v>6858152</v>
+        <v>6858018</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20230,10 +20222,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367401</v>
+        <v>132367447</v>
       </c>
       <c r="B174" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20241,34 +20233,42 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>384992</v>
+        <v>385333</v>
       </c>
       <c r="R174" t="n">
-        <v>6858018</v>
+        <v>6858152</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13548,32 +13548,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367443</v>
+        <v>132367430</v>
       </c>
       <c r="B109" t="n">
-        <v>57950</v>
+        <v>57141</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13581,7 +13581,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -13591,10 +13591,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385408</v>
+        <v>385158</v>
       </c>
       <c r="R109" t="n">
-        <v>6857862</v>
+        <v>6858052</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367444</v>
+        <v>132367443</v>
       </c>
       <c r="B110" t="n">
         <v>57950</v>
@@ -13696,10 +13696,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385280</v>
+        <v>385408</v>
       </c>
       <c r="R110" t="n">
-        <v>6857923</v>
+        <v>6857862</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13758,32 +13758,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132367430</v>
+        <v>132367444</v>
       </c>
       <c r="B111" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13791,7 +13791,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>385158</v>
+        <v>385280</v>
       </c>
       <c r="R111" t="n">
-        <v>6858052</v>
+        <v>6857923</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -16235,45 +16235,53 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367474</v>
+        <v>132367421</v>
       </c>
       <c r="B135" t="n">
-        <v>79084</v>
+        <v>57141</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385318</v>
+        <v>385249</v>
       </c>
       <c r="R135" t="n">
-        <v>6858113</v>
+        <v>6858148</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16332,10 +16340,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367399</v>
+        <v>132367474</v>
       </c>
       <c r="B136" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16343,21 +16351,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16367,10 +16375,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>384873</v>
+        <v>385318</v>
       </c>
       <c r="R136" t="n">
-        <v>6858080</v>
+        <v>6858113</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16429,53 +16437,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367421</v>
+        <v>132367399</v>
       </c>
       <c r="B137" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385249</v>
+        <v>384873</v>
       </c>
       <c r="R137" t="n">
-        <v>6858148</v>
+        <v>6858080</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17973,10 +17973,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367398</v>
+        <v>132367405</v>
       </c>
       <c r="B152" t="n">
-        <v>79946</v>
+        <v>79917</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17984,21 +17984,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>384804</v>
+        <v>385332</v>
       </c>
       <c r="R152" t="n">
-        <v>6858152</v>
+        <v>6858161</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18070,32 +18070,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132367459</v>
+        <v>132367398</v>
       </c>
       <c r="B153" t="n">
-        <v>97983</v>
+        <v>79946</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18105,10 +18105,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>384655</v>
+        <v>384804</v>
       </c>
       <c r="R153" t="n">
-        <v>6858187</v>
+        <v>6858152</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18141,11 +18141,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18172,32 +18167,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132367405</v>
+        <v>132367459</v>
       </c>
       <c r="B154" t="n">
-        <v>79917</v>
+        <v>97983</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18207,10 +18202,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>385332</v>
+        <v>384655</v>
       </c>
       <c r="R154" t="n">
-        <v>6858161</v>
+        <v>6858187</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18243,6 +18238,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18475,45 +18475,53 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367391</v>
+        <v>132367416</v>
       </c>
       <c r="B157" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385129</v>
+        <v>385185</v>
       </c>
       <c r="R157" t="n">
-        <v>6858060</v>
+        <v>6858146</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18572,7 +18580,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367416</v>
+        <v>132367422</v>
       </c>
       <c r="B158" t="n">
         <v>57141</v>
@@ -18615,10 +18623,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385185</v>
+        <v>385246</v>
       </c>
       <c r="R158" t="n">
-        <v>6858146</v>
+        <v>6858162</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18677,53 +18685,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367422</v>
+        <v>132367391</v>
       </c>
       <c r="B159" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385246</v>
+        <v>385129</v>
       </c>
       <c r="R159" t="n">
-        <v>6858162</v>
+        <v>6858060</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13231,10 +13231,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367475</v>
+        <v>132367443</v>
       </c>
       <c r="B106" t="n">
-        <v>79084</v>
+        <v>57950</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13242,34 +13242,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>384814</v>
+        <v>385408</v>
       </c>
       <c r="R106" t="n">
-        <v>6858214</v>
+        <v>6857862</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13328,45 +13336,53 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367394</v>
+        <v>132367430</v>
       </c>
       <c r="B107" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>384969</v>
+        <v>385158</v>
       </c>
       <c r="R107" t="n">
-        <v>6858130</v>
+        <v>6858052</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13425,10 +13441,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367501</v>
+        <v>132367463</v>
       </c>
       <c r="B108" t="n">
-        <v>78334</v>
+        <v>79085</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13436,34 +13452,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>385084</v>
+        <v>385332</v>
       </c>
       <c r="R108" t="n">
-        <v>6858195</v>
+        <v>6858162</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13507,31 +13526,6 @@
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -13548,53 +13542,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367430</v>
+        <v>132367466</v>
       </c>
       <c r="B109" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385158</v>
+        <v>384749</v>
       </c>
       <c r="R109" t="n">
-        <v>6858052</v>
+        <v>6858223</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13653,10 +13639,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367443</v>
+        <v>132367501</v>
       </c>
       <c r="B110" t="n">
-        <v>57950</v>
+        <v>78334</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13664,42 +13650,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385408</v>
+        <v>385084</v>
       </c>
       <c r="R110" t="n">
-        <v>6857862</v>
+        <v>6858195</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13740,8 +13718,34 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -13758,10 +13762,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132367444</v>
+        <v>132367475</v>
       </c>
       <c r="B111" t="n">
-        <v>57950</v>
+        <v>79084</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13769,42 +13773,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>385280</v>
+        <v>384814</v>
       </c>
       <c r="R111" t="n">
-        <v>6857923</v>
+        <v>6858214</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13863,10 +13859,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132367463</v>
+        <v>132367394</v>
       </c>
       <c r="B112" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13874,37 +13870,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>385332</v>
+        <v>384969</v>
       </c>
       <c r="R112" t="n">
-        <v>6858162</v>
+        <v>6858130</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13945,7 +13938,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -13964,10 +13956,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132367466</v>
+        <v>132367444</v>
       </c>
       <c r="B113" t="n">
-        <v>79085</v>
+        <v>57950</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13975,34 +13967,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>384749</v>
+        <v>385280</v>
       </c>
       <c r="R113" t="n">
-        <v>6858223</v>
+        <v>6857923</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14061,10 +14061,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132367435</v>
+        <v>132367451</v>
       </c>
       <c r="B114" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14072,21 +14072,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14094,7 +14094,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -14104,10 +14104,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>384859</v>
+        <v>385088</v>
       </c>
       <c r="R114" t="n">
-        <v>6858073</v>
+        <v>6858196</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14166,7 +14166,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132367451</v>
+        <v>132367456</v>
       </c>
       <c r="B115" t="n">
         <v>57950</v>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>385088</v>
+        <v>385112</v>
       </c>
       <c r="R115" t="n">
-        <v>6858196</v>
+        <v>6857918</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14271,10 +14271,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132367456</v>
+        <v>132367435</v>
       </c>
       <c r="B116" t="n">
-        <v>57950</v>
+        <v>58114</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14282,21 +14282,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>385112</v>
+        <v>384859</v>
       </c>
       <c r="R116" t="n">
-        <v>6857918</v>
+        <v>6858073</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14793,10 +14793,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132367428</v>
+        <v>132367470</v>
       </c>
       <c r="B121" t="n">
-        <v>57141</v>
+        <v>8455</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14804,29 +14804,30 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14836,10 +14837,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>385279</v>
+        <v>384910</v>
       </c>
       <c r="R121" t="n">
-        <v>6858073</v>
+        <v>6858203</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14874,17 +14875,13 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -14903,7 +14900,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132367432</v>
+        <v>132367428</v>
       </c>
       <c r="B122" t="n">
         <v>57141</v>
@@ -14946,10 +14943,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>385185</v>
+        <v>385279</v>
       </c>
       <c r="R122" t="n">
-        <v>6858160</v>
+        <v>6858073</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14982,6 +14979,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15008,10 +15010,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132367470</v>
+        <v>132367432</v>
       </c>
       <c r="B123" t="n">
-        <v>8455</v>
+        <v>57141</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15019,30 +15021,29 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -15052,10 +15053,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>384910</v>
+        <v>385185</v>
       </c>
       <c r="R123" t="n">
-        <v>6858203</v>
+        <v>6858160</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15096,7 +15097,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -15220,10 +15220,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367446</v>
+        <v>132367395</v>
       </c>
       <c r="B125" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15231,42 +15231,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>385178</v>
+        <v>384944</v>
       </c>
       <c r="R125" t="n">
-        <v>6858121</v>
+        <v>6858169</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15325,7 +15317,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132367453</v>
+        <v>132367446</v>
       </c>
       <c r="B126" t="n">
         <v>57950</v>
@@ -15358,7 +15350,7 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -15368,10 +15360,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>384934</v>
+        <v>385178</v>
       </c>
       <c r="R126" t="n">
-        <v>6858197</v>
+        <v>6858121</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15430,45 +15422,53 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367462</v>
+        <v>132367425</v>
       </c>
       <c r="B127" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>385195</v>
+        <v>385281</v>
       </c>
       <c r="R127" t="n">
-        <v>6858154</v>
+        <v>6858170</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15527,10 +15527,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367464</v>
+        <v>132367453</v>
       </c>
       <c r="B128" t="n">
-        <v>79085</v>
+        <v>57950</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15538,34 +15538,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>385318</v>
+        <v>384934</v>
       </c>
       <c r="R128" t="n">
-        <v>6858113</v>
+        <v>6858197</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15624,10 +15632,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132367395</v>
+        <v>132367462</v>
       </c>
       <c r="B129" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15635,21 +15643,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15659,10 +15667,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>384944</v>
+        <v>385195</v>
       </c>
       <c r="R129" t="n">
-        <v>6858169</v>
+        <v>6858154</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15721,53 +15729,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132367425</v>
+        <v>132367464</v>
       </c>
       <c r="B130" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>385281</v>
+        <v>385318</v>
       </c>
       <c r="R130" t="n">
-        <v>6858170</v>
+        <v>6858113</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15826,7 +15826,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367392</v>
+        <v>132367402</v>
       </c>
       <c r="B131" t="n">
         <v>79946</v>
@@ -15861,10 +15861,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>385102</v>
+        <v>385403</v>
       </c>
       <c r="R131" t="n">
-        <v>6858138</v>
+        <v>6857836</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15923,7 +15923,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367402</v>
+        <v>132367392</v>
       </c>
       <c r="B132" t="n">
         <v>79946</v>
@@ -15958,10 +15958,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385403</v>
+        <v>385102</v>
       </c>
       <c r="R132" t="n">
-        <v>6857836</v>
+        <v>6858138</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16235,53 +16235,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367421</v>
+        <v>132367404</v>
       </c>
       <c r="B135" t="n">
-        <v>57141</v>
+        <v>79917</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385249</v>
+        <v>385227</v>
       </c>
       <c r="R135" t="n">
-        <v>6858148</v>
+        <v>6857907</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16340,10 +16332,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367474</v>
+        <v>132367399</v>
       </c>
       <c r="B136" t="n">
-        <v>79084</v>
+        <v>79946</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16351,21 +16343,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16375,10 +16367,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>385318</v>
+        <v>384873</v>
       </c>
       <c r="R136" t="n">
-        <v>6858113</v>
+        <v>6858080</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16437,10 +16429,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367399</v>
+        <v>132367474</v>
       </c>
       <c r="B137" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16448,21 +16440,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16472,10 +16464,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>384873</v>
+        <v>385318</v>
       </c>
       <c r="R137" t="n">
-        <v>6858080</v>
+        <v>6858113</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16534,7 +16526,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367431</v>
+        <v>132367421</v>
       </c>
       <c r="B138" t="n">
         <v>57141</v>
@@ -16577,10 +16569,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>384950</v>
+        <v>385249</v>
       </c>
       <c r="R138" t="n">
-        <v>6858169</v>
+        <v>6858148</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16639,7 +16631,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367413</v>
+        <v>132367431</v>
       </c>
       <c r="B139" t="n">
         <v>57141</v>
@@ -16682,10 +16674,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>385181</v>
+        <v>384950</v>
       </c>
       <c r="R139" t="n">
-        <v>6858109</v>
+        <v>6858169</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16744,45 +16736,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367404</v>
+        <v>132367413</v>
       </c>
       <c r="B140" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>385227</v>
+        <v>385181</v>
       </c>
       <c r="R140" t="n">
-        <v>6857907</v>
+        <v>6858109</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16841,45 +16841,53 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367403</v>
+        <v>132367424</v>
       </c>
       <c r="B141" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>385374</v>
+        <v>385276</v>
       </c>
       <c r="R141" t="n">
-        <v>6857880</v>
+        <v>6858157</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16938,10 +16946,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367424</v>
+        <v>132367469</v>
       </c>
       <c r="B142" t="n">
-        <v>57141</v>
+        <v>8455</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16949,29 +16957,30 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -16981,10 +16990,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>385276</v>
+        <v>384988</v>
       </c>
       <c r="R142" t="n">
-        <v>6858157</v>
+        <v>6858227</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17025,6 +17034,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17150,54 +17160,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367469</v>
+        <v>132367403</v>
       </c>
       <c r="B144" t="n">
-        <v>8455</v>
+        <v>79917</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>384988</v>
+        <v>385374</v>
       </c>
       <c r="R144" t="n">
-        <v>6858227</v>
+        <v>6857880</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17238,7 +17239,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -17472,10 +17472,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132367389</v>
+        <v>132367407</v>
       </c>
       <c r="B147" t="n">
-        <v>79946</v>
+        <v>79917</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17507,10 +17507,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>385195</v>
+        <v>385124</v>
       </c>
       <c r="R147" t="n">
-        <v>6858154</v>
+        <v>6858064</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17674,10 +17674,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367407</v>
+        <v>132367389</v>
       </c>
       <c r="B149" t="n">
-        <v>79917</v>
+        <v>79946</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17685,21 +17685,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17709,10 +17709,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>385124</v>
+        <v>385195</v>
       </c>
       <c r="R149" t="n">
-        <v>6858064</v>
+        <v>6858154</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17771,53 +17771,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132367418</v>
+        <v>132367410</v>
       </c>
       <c r="B150" t="n">
-        <v>57141</v>
+        <v>79917</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>385198</v>
+        <v>384959</v>
       </c>
       <c r="R150" t="n">
-        <v>6858144</v>
+        <v>6858242</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17876,45 +17868,53 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>132367410</v>
+        <v>132367418</v>
       </c>
       <c r="B151" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>384959</v>
+        <v>385198</v>
       </c>
       <c r="R151" t="n">
-        <v>6858242</v>
+        <v>6858144</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17973,10 +17973,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367405</v>
+        <v>132367398</v>
       </c>
       <c r="B152" t="n">
-        <v>79917</v>
+        <v>79946</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17984,21 +17984,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>385332</v>
+        <v>384804</v>
       </c>
       <c r="R152" t="n">
-        <v>6858161</v>
+        <v>6858152</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18070,10 +18070,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132367398</v>
+        <v>132367405</v>
       </c>
       <c r="B153" t="n">
-        <v>79946</v>
+        <v>79917</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18081,21 +18081,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18105,10 +18105,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>384804</v>
+        <v>385332</v>
       </c>
       <c r="R153" t="n">
-        <v>6858152</v>
+        <v>6858161</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18475,53 +18475,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367416</v>
+        <v>132367391</v>
       </c>
       <c r="B157" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385185</v>
+        <v>385129</v>
       </c>
       <c r="R157" t="n">
-        <v>6858146</v>
+        <v>6858060</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18580,7 +18572,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367422</v>
+        <v>132367416</v>
       </c>
       <c r="B158" t="n">
         <v>57141</v>
@@ -18623,10 +18615,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385246</v>
+        <v>385185</v>
       </c>
       <c r="R158" t="n">
-        <v>6858162</v>
+        <v>6858146</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18685,45 +18677,53 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367391</v>
+        <v>132367422</v>
       </c>
       <c r="B159" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385129</v>
+        <v>385246</v>
       </c>
       <c r="R159" t="n">
-        <v>6858060</v>
+        <v>6858162</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18782,10 +18782,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367471</v>
+        <v>132367450</v>
       </c>
       <c r="B160" t="n">
-        <v>58085</v>
+        <v>57950</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18793,21 +18793,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18815,7 +18815,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385400</v>
+        <v>385107</v>
       </c>
       <c r="R160" t="n">
-        <v>6857831</v>
+        <v>6858161</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,45 +18887,53 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367465</v>
+        <v>132367420</v>
       </c>
       <c r="B161" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385131</v>
+        <v>385235</v>
       </c>
       <c r="R161" t="n">
-        <v>6858065</v>
+        <v>6858146</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18984,45 +18992,53 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367408</v>
+        <v>132367414</v>
       </c>
       <c r="B162" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385062</v>
+        <v>385197</v>
       </c>
       <c r="R162" t="n">
-        <v>6858092</v>
+        <v>6858108</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19081,10 +19097,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367450</v>
+        <v>132367471</v>
       </c>
       <c r="B163" t="n">
-        <v>57950</v>
+        <v>58085</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19092,21 +19108,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>205976</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -19114,7 +19130,7 @@
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -19124,10 +19140,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385107</v>
+        <v>385400</v>
       </c>
       <c r="R163" t="n">
-        <v>6858161</v>
+        <v>6857831</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19186,10 +19202,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367420</v>
+        <v>132367495</v>
       </c>
       <c r="B164" t="n">
-        <v>57141</v>
+        <v>106244</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19197,31 +19213,27 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19229,10 +19241,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385235</v>
+        <v>384848</v>
       </c>
       <c r="R164" t="n">
-        <v>6858146</v>
+        <v>6858075</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19267,12 +19279,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -19291,53 +19309,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367414</v>
+        <v>132367465</v>
       </c>
       <c r="B165" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385197</v>
+        <v>385131</v>
       </c>
       <c r="R165" t="n">
-        <v>6858108</v>
+        <v>6858065</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19396,49 +19406,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367495</v>
+        <v>132367408</v>
       </c>
       <c r="B166" t="n">
-        <v>106243</v>
+        <v>79917</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221144</v>
+        <v>229821</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>384848</v>
+        <v>385062</v>
       </c>
       <c r="R166" t="n">
-        <v>6858075</v>
+        <v>6858092</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19473,18 +19479,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -19697,42 +19697,37 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367423</v>
+        <v>132367502</v>
       </c>
       <c r="B169" t="n">
-        <v>57141</v>
+        <v>78730</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
@@ -19740,10 +19735,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385263</v>
+        <v>385349</v>
       </c>
       <c r="R169" t="n">
-        <v>6858153</v>
+        <v>6857860</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19784,8 +19779,29 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
@@ -19802,10 +19818,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367502</v>
+        <v>132367393</v>
       </c>
       <c r="B170" t="n">
-        <v>78730</v>
+        <v>79946</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19813,37 +19829,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385349</v>
+        <v>385118</v>
       </c>
       <c r="R170" t="n">
-        <v>6857860</v>
+        <v>6858178</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19884,29 +19897,8 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
@@ -19923,45 +19915,53 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367393</v>
+        <v>132367423</v>
       </c>
       <c r="B171" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385118</v>
+        <v>385263</v>
       </c>
       <c r="R171" t="n">
-        <v>6858178</v>
+        <v>6858153</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367401</v>
+        <v>132367447</v>
       </c>
       <c r="B172" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,34 +20031,42 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>384992</v>
+        <v>385333</v>
       </c>
       <c r="R172" t="n">
-        <v>6858018</v>
+        <v>6858152</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20117,10 +20125,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132367457</v>
+        <v>132367401</v>
       </c>
       <c r="B173" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20128,42 +20136,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>385184</v>
+        <v>384992</v>
       </c>
       <c r="R173" t="n">
-        <v>6857885</v>
+        <v>6858018</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20222,7 +20222,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367447</v>
+        <v>132367457</v>
       </c>
       <c r="B174" t="n">
         <v>57950</v>
@@ -20255,7 +20255,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385333</v>
+        <v>385184</v>
       </c>
       <c r="R174" t="n">
-        <v>6858152</v>
+        <v>6857885</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -17472,10 +17472,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132367407</v>
+        <v>132367389</v>
       </c>
       <c r="B147" t="n">
-        <v>79917</v>
+        <v>79946</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17483,21 +17483,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17507,10 +17507,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>385124</v>
+        <v>385195</v>
       </c>
       <c r="R147" t="n">
-        <v>6858064</v>
+        <v>6858154</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17674,10 +17674,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367389</v>
+        <v>132367407</v>
       </c>
       <c r="B149" t="n">
-        <v>79946</v>
+        <v>79917</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17685,21 +17685,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17709,10 +17709,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>385195</v>
+        <v>385124</v>
       </c>
       <c r="R149" t="n">
-        <v>6858154</v>
+        <v>6858064</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18269,10 +18269,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367434</v>
+        <v>132367391</v>
       </c>
       <c r="B155" t="n">
-        <v>58114</v>
+        <v>79946</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18280,42 +18280,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385087</v>
+        <v>385129</v>
       </c>
       <c r="R155" t="n">
-        <v>6858055</v>
+        <v>6858060</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18374,37 +18366,42 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367406</v>
+        <v>132367416</v>
       </c>
       <c r="B156" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -18412,10 +18409,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385318</v>
+        <v>385185</v>
       </c>
       <c r="R156" t="n">
-        <v>6858113</v>
+        <v>6858146</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18456,7 +18453,6 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -18475,45 +18471,53 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367391</v>
+        <v>132367422</v>
       </c>
       <c r="B157" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385129</v>
+        <v>385246</v>
       </c>
       <c r="R157" t="n">
-        <v>6858060</v>
+        <v>6858162</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18572,32 +18576,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367416</v>
+        <v>132367434</v>
       </c>
       <c r="B158" t="n">
-        <v>57141</v>
+        <v>58114</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18605,7 +18609,7 @@
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -18615,10 +18619,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385185</v>
+        <v>385087</v>
       </c>
       <c r="R158" t="n">
-        <v>6858146</v>
+        <v>6858055</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18677,42 +18681,37 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367422</v>
+        <v>132367406</v>
       </c>
       <c r="B159" t="n">
-        <v>57141</v>
+        <v>79917</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18720,10 +18719,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385246</v>
+        <v>385318</v>
       </c>
       <c r="R159" t="n">
-        <v>6858162</v>
+        <v>6858113</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18764,6 +18763,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18782,32 +18782,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367450</v>
+        <v>132367420</v>
       </c>
       <c r="B160" t="n">
-        <v>57950</v>
+        <v>57141</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18815,7 +18815,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385107</v>
+        <v>385235</v>
       </c>
       <c r="R160" t="n">
-        <v>6858161</v>
+        <v>6858146</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,7 +18887,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367420</v>
+        <v>132367414</v>
       </c>
       <c r="B161" t="n">
         <v>57141</v>
@@ -18930,10 +18930,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385235</v>
+        <v>385197</v>
       </c>
       <c r="R161" t="n">
-        <v>6858146</v>
+        <v>6858108</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18992,10 +18992,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367414</v>
+        <v>132367495</v>
       </c>
       <c r="B162" t="n">
-        <v>57141</v>
+        <v>106244</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19003,31 +19003,27 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
@@ -19035,10 +19031,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385197</v>
+        <v>384848</v>
       </c>
       <c r="R162" t="n">
-        <v>6858108</v>
+        <v>6858075</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19073,12 +19069,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -19097,10 +19099,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367471</v>
+        <v>132367450</v>
       </c>
       <c r="B163" t="n">
-        <v>58085</v>
+        <v>57950</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19108,21 +19110,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -19130,7 +19132,7 @@
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -19140,10 +19142,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385400</v>
+        <v>385107</v>
       </c>
       <c r="R163" t="n">
-        <v>6857831</v>
+        <v>6858161</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19202,38 +19204,42 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367495</v>
+        <v>132367471</v>
       </c>
       <c r="B164" t="n">
-        <v>106244</v>
+        <v>58085</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221144</v>
+        <v>205976</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19241,10 +19247,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>384848</v>
+        <v>385400</v>
       </c>
       <c r="R164" t="n">
-        <v>6858075</v>
+        <v>6857831</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19279,18 +19285,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -19600,45 +19600,53 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367461</v>
+        <v>132367423</v>
       </c>
       <c r="B168" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385227</v>
+        <v>385263</v>
       </c>
       <c r="R168" t="n">
-        <v>6857907</v>
+        <v>6858153</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19697,10 +19705,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367502</v>
+        <v>132367461</v>
       </c>
       <c r="B169" t="n">
-        <v>78730</v>
+        <v>79085</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19708,37 +19716,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385349</v>
+        <v>385227</v>
       </c>
       <c r="R169" t="n">
-        <v>6857860</v>
+        <v>6857907</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19779,29 +19784,8 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
@@ -19818,10 +19802,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367393</v>
+        <v>132367502</v>
       </c>
       <c r="B170" t="n">
-        <v>79946</v>
+        <v>78730</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19829,34 +19813,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385118</v>
+        <v>385349</v>
       </c>
       <c r="R170" t="n">
-        <v>6858178</v>
+        <v>6857860</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19897,8 +19884,29 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
@@ -19915,53 +19923,45 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367423</v>
+        <v>132367393</v>
       </c>
       <c r="B171" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385263</v>
+        <v>385118</v>
       </c>
       <c r="R171" t="n">
-        <v>6858153</v>
+        <v>6858178</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367447</v>
+        <v>132367409</v>
       </c>
       <c r="B172" t="n">
-        <v>57950</v>
+        <v>79917</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,42 +20031,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>385333</v>
+        <v>385075</v>
       </c>
       <c r="R172" t="n">
-        <v>6858152</v>
+        <v>6858201</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20222,7 +20214,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367457</v>
+        <v>132367447</v>
       </c>
       <c r="B174" t="n">
         <v>57950</v>
@@ -20255,7 +20247,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -20265,10 +20257,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385184</v>
+        <v>385333</v>
       </c>
       <c r="R174" t="n">
-        <v>6857885</v>
+        <v>6858152</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20327,10 +20319,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132367409</v>
+        <v>132367457</v>
       </c>
       <c r="B175" t="n">
-        <v>79917</v>
+        <v>57950</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20338,34 +20330,42 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>385075</v>
+        <v>385184</v>
       </c>
       <c r="R175" t="n">
-        <v>6858201</v>
+        <v>6857885</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13126,10 +13126,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132367449</v>
+        <v>132367463</v>
       </c>
       <c r="B105" t="n">
-        <v>57950</v>
+        <v>79086</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13137,31 +13137,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -13169,10 +13164,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>385133</v>
+        <v>385332</v>
       </c>
       <c r="R105" t="n">
-        <v>6858066</v>
+        <v>6858162</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13213,6 +13208,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -13231,10 +13227,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367443</v>
+        <v>132367466</v>
       </c>
       <c r="B106" t="n">
-        <v>57950</v>
+        <v>79086</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13242,42 +13238,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>385408</v>
+        <v>384749</v>
       </c>
       <c r="R106" t="n">
-        <v>6857862</v>
+        <v>6858223</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13336,53 +13324,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367430</v>
+        <v>132367475</v>
       </c>
       <c r="B107" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>385158</v>
+        <v>384814</v>
       </c>
       <c r="R107" t="n">
-        <v>6858052</v>
+        <v>6858214</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13441,10 +13421,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367463</v>
+        <v>132367394</v>
       </c>
       <c r="B108" t="n">
-        <v>79085</v>
+        <v>79947</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13452,37 +13432,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>385332</v>
+        <v>384969</v>
       </c>
       <c r="R108" t="n">
-        <v>6858162</v>
+        <v>6858130</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13523,7 +13500,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13542,10 +13518,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367466</v>
+        <v>132367501</v>
       </c>
       <c r="B109" t="n">
-        <v>79085</v>
+        <v>78335</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13553,21 +13529,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13577,10 +13553,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>384749</v>
+        <v>385084</v>
       </c>
       <c r="R109" t="n">
-        <v>6858223</v>
+        <v>6858195</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13621,8 +13597,34 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -13639,10 +13641,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367501</v>
+        <v>132367449</v>
       </c>
       <c r="B110" t="n">
-        <v>78334</v>
+        <v>57951</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13650,34 +13652,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385084</v>
+        <v>385133</v>
       </c>
       <c r="R110" t="n">
-        <v>6858195</v>
+        <v>6858066</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13718,34 +13728,8 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -13762,10 +13746,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132367475</v>
+        <v>132367444</v>
       </c>
       <c r="B111" t="n">
-        <v>79084</v>
+        <v>57951</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13773,34 +13757,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>384814</v>
+        <v>385280</v>
       </c>
       <c r="R111" t="n">
-        <v>6858214</v>
+        <v>6857923</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13859,10 +13851,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132367394</v>
+        <v>132367443</v>
       </c>
       <c r="B112" t="n">
-        <v>79946</v>
+        <v>57951</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13870,34 +13862,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>384969</v>
+        <v>385408</v>
       </c>
       <c r="R112" t="n">
-        <v>6858130</v>
+        <v>6857862</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13956,32 +13956,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132367444</v>
+        <v>132367430</v>
       </c>
       <c r="B113" t="n">
-        <v>57950</v>
+        <v>57142</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13989,7 +13989,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -13999,10 +13999,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>385280</v>
+        <v>385158</v>
       </c>
       <c r="R113" t="n">
-        <v>6857923</v>
+        <v>6858052</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14064,7 +14064,7 @@
         <v>132367451</v>
       </c>
       <c r="B114" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>132367456</v>
       </c>
       <c r="B115" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>132367435</v>
       </c>
       <c r="B116" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>132367448</v>
       </c>
       <c r="B117" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>132367412</v>
       </c>
       <c r="B118" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>132367415</v>
       </c>
       <c r="B119" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>132367396</v>
       </c>
       <c r="B120" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14793,10 +14793,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132367470</v>
+        <v>132367428</v>
       </c>
       <c r="B121" t="n">
-        <v>8455</v>
+        <v>57142</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14804,30 +14804,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14837,10 +14836,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>384910</v>
+        <v>385279</v>
       </c>
       <c r="R121" t="n">
-        <v>6858203</v>
+        <v>6858073</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14875,13 +14874,17 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -14900,10 +14903,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132367428</v>
+        <v>132367432</v>
       </c>
       <c r="B122" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14943,10 +14946,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>385279</v>
+        <v>385185</v>
       </c>
       <c r="R122" t="n">
-        <v>6858073</v>
+        <v>6858160</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14979,11 +14982,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15010,10 +15008,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132367432</v>
+        <v>132367470</v>
       </c>
       <c r="B123" t="n">
-        <v>57141</v>
+        <v>8455</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15021,29 +15019,30 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -15053,10 +15052,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>385185</v>
+        <v>384910</v>
       </c>
       <c r="R123" t="n">
-        <v>6858160</v>
+        <v>6858203</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15097,6 +15096,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>132367433</v>
       </c>
       <c r="B124" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15220,10 +15220,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367395</v>
+        <v>132367446</v>
       </c>
       <c r="B125" t="n">
-        <v>79946</v>
+        <v>57951</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15231,34 +15231,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>384944</v>
+        <v>385178</v>
       </c>
       <c r="R125" t="n">
-        <v>6858169</v>
+        <v>6858121</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15317,10 +15325,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132367446</v>
+        <v>132367453</v>
       </c>
       <c r="B126" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15350,7 +15358,7 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -15360,10 +15368,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>385178</v>
+        <v>384934</v>
       </c>
       <c r="R126" t="n">
-        <v>6858121</v>
+        <v>6858197</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15422,53 +15430,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367425</v>
+        <v>132367395</v>
       </c>
       <c r="B127" t="n">
-        <v>57141</v>
+        <v>79947</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>385281</v>
+        <v>384944</v>
       </c>
       <c r="R127" t="n">
-        <v>6858170</v>
+        <v>6858169</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15527,32 +15527,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367453</v>
+        <v>132367425</v>
       </c>
       <c r="B128" t="n">
-        <v>57950</v>
+        <v>57142</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15560,7 +15560,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -15570,10 +15570,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>384934</v>
+        <v>385281</v>
       </c>
       <c r="R128" t="n">
-        <v>6858197</v>
+        <v>6858170</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15635,7 +15635,7 @@
         <v>132367462</v>
       </c>
       <c r="B129" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>132367464</v>
       </c>
       <c r="B130" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15826,10 +15826,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367402</v>
+        <v>132367455</v>
       </c>
       <c r="B131" t="n">
-        <v>79946</v>
+        <v>57951</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15837,34 +15837,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>385403</v>
+        <v>384840</v>
       </c>
       <c r="R131" t="n">
-        <v>6857836</v>
+        <v>6858190</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15926,7 +15934,7 @@
         <v>132367392</v>
       </c>
       <c r="B132" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16020,10 +16028,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367455</v>
+        <v>132367402</v>
       </c>
       <c r="B133" t="n">
-        <v>57950</v>
+        <v>79947</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16031,42 +16039,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>384840</v>
+        <v>385403</v>
       </c>
       <c r="R133" t="n">
-        <v>6858190</v>
+        <v>6857836</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16128,7 +16128,7 @@
         <v>132367417</v>
       </c>
       <c r="B134" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16235,10 +16235,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367404</v>
+        <v>132367474</v>
       </c>
       <c r="B135" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16246,21 +16246,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16270,10 +16270,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385227</v>
+        <v>385318</v>
       </c>
       <c r="R135" t="n">
-        <v>6857907</v>
+        <v>6858113</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16335,7 +16335,7 @@
         <v>132367399</v>
       </c>
       <c r="B136" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16429,45 +16429,53 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367474</v>
+        <v>132367421</v>
       </c>
       <c r="B137" t="n">
-        <v>79084</v>
+        <v>57142</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385318</v>
+        <v>385249</v>
       </c>
       <c r="R137" t="n">
-        <v>6858113</v>
+        <v>6858148</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16526,10 +16534,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367421</v>
+        <v>132367431</v>
       </c>
       <c r="B138" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16569,10 +16577,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>385249</v>
+        <v>384950</v>
       </c>
       <c r="R138" t="n">
-        <v>6858148</v>
+        <v>6858169</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16631,10 +16639,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367431</v>
+        <v>132367413</v>
       </c>
       <c r="B139" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16674,10 +16682,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>384950</v>
+        <v>385181</v>
       </c>
       <c r="R139" t="n">
-        <v>6858169</v>
+        <v>6858109</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16736,53 +16744,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367413</v>
+        <v>132367404</v>
       </c>
       <c r="B140" t="n">
-        <v>57141</v>
+        <v>79918</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>385181</v>
+        <v>385227</v>
       </c>
       <c r="R140" t="n">
-        <v>6858109</v>
+        <v>6857907</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16841,53 +16841,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367424</v>
+        <v>132367403</v>
       </c>
       <c r="B141" t="n">
-        <v>57141</v>
+        <v>79918</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>385276</v>
+        <v>385374</v>
       </c>
       <c r="R141" t="n">
-        <v>6858157</v>
+        <v>6857880</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16946,10 +16938,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367469</v>
+        <v>132367424</v>
       </c>
       <c r="B142" t="n">
-        <v>8455</v>
+        <v>57142</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16957,30 +16949,29 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -16990,10 +16981,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>384988</v>
+        <v>385276</v>
       </c>
       <c r="R142" t="n">
-        <v>6858227</v>
+        <v>6858157</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17034,7 +17025,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17053,7 +17043,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367468</v>
+        <v>132367469</v>
       </c>
       <c r="B143" t="n">
         <v>8455</v>
@@ -17087,7 +17077,7 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -17097,10 +17087,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>384943</v>
+        <v>384988</v>
       </c>
       <c r="R143" t="n">
-        <v>6858164</v>
+        <v>6858227</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17160,45 +17150,54 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367403</v>
+        <v>132367468</v>
       </c>
       <c r="B144" t="n">
-        <v>79917</v>
+        <v>8455</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>385374</v>
+        <v>384943</v>
       </c>
       <c r="R144" t="n">
-        <v>6857880</v>
+        <v>6858164</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17239,6 +17238,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -17260,7 +17260,7 @@
         <v>132367458</v>
       </c>
       <c r="B145" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>132367427</v>
       </c>
       <c r="B146" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>132367389</v>
       </c>
       <c r="B147" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>132367452</v>
       </c>
       <c r="B148" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>132367407</v>
       </c>
       <c r="B149" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17771,45 +17771,53 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132367410</v>
+        <v>132367418</v>
       </c>
       <c r="B150" t="n">
-        <v>79917</v>
+        <v>57142</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>384959</v>
+        <v>385198</v>
       </c>
       <c r="R150" t="n">
-        <v>6858242</v>
+        <v>6858144</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17868,53 +17876,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>132367418</v>
+        <v>132367410</v>
       </c>
       <c r="B151" t="n">
-        <v>57141</v>
+        <v>79918</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>385198</v>
+        <v>384959</v>
       </c>
       <c r="R151" t="n">
-        <v>6858144</v>
+        <v>6858242</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17973,32 +17973,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367398</v>
+        <v>132367459</v>
       </c>
       <c r="B152" t="n">
-        <v>79946</v>
+        <v>97984</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>384804</v>
+        <v>384655</v>
       </c>
       <c r="R152" t="n">
-        <v>6858152</v>
+        <v>6858187</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18044,6 +18044,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18070,10 +18075,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132367405</v>
+        <v>132367398</v>
       </c>
       <c r="B153" t="n">
-        <v>79917</v>
+        <v>79947</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18081,21 +18086,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18105,10 +18110,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>385332</v>
+        <v>384804</v>
       </c>
       <c r="R153" t="n">
-        <v>6858161</v>
+        <v>6858152</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18167,32 +18172,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132367459</v>
+        <v>132367405</v>
       </c>
       <c r="B154" t="n">
-        <v>97983</v>
+        <v>79918</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18202,10 +18207,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>384655</v>
+        <v>385332</v>
       </c>
       <c r="R154" t="n">
-        <v>6858187</v>
+        <v>6858161</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18238,11 +18243,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18272,7 +18272,7 @@
         <v>132367391</v>
       </c>
       <c r="B155" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>132367416</v>
       </c>
       <c r="B156" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         <v>132367422</v>
       </c>
       <c r="B157" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>132367434</v>
       </c>
       <c r="B158" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>132367406</v>
       </c>
       <c r="B159" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>132367420</v>
       </c>
       <c r="B160" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>132367414</v>
       </c>
       <c r="B161" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>132367495</v>
       </c>
       <c r="B162" t="n">
-        <v>106244</v>
+        <v>106245</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>132367450</v>
       </c>
       <c r="B163" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>132367471</v>
       </c>
       <c r="B164" t="n">
-        <v>58085</v>
+        <v>58086</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>132367465</v>
       </c>
       <c r="B165" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>132367408</v>
       </c>
       <c r="B166" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>132367467</v>
       </c>
       <c r="B167" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>132367423</v>
       </c>
       <c r="B168" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19705,10 +19705,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367461</v>
+        <v>132367502</v>
       </c>
       <c r="B169" t="n">
-        <v>79085</v>
+        <v>78731</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19716,34 +19716,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385227</v>
+        <v>385349</v>
       </c>
       <c r="R169" t="n">
-        <v>6857907</v>
+        <v>6857860</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19784,8 +19787,29 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
@@ -19802,10 +19826,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367502</v>
+        <v>132367393</v>
       </c>
       <c r="B170" t="n">
-        <v>78730</v>
+        <v>79947</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19813,37 +19837,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385349</v>
+        <v>385118</v>
       </c>
       <c r="R170" t="n">
-        <v>6857860</v>
+        <v>6858178</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19884,29 +19905,8 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
@@ -19923,10 +19923,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367393</v>
+        <v>132367461</v>
       </c>
       <c r="B171" t="n">
-        <v>79946</v>
+        <v>79086</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19934,21 +19934,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385118</v>
+        <v>385227</v>
       </c>
       <c r="R171" t="n">
-        <v>6858178</v>
+        <v>6857907</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20023,7 +20023,7 @@
         <v>132367409</v>
       </c>
       <c r="B172" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>132367401</v>
       </c>
       <c r="B173" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>132367447</v>
       </c>
       <c r="B174" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>132367457</v>
       </c>
       <c r="B175" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13126,10 +13126,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132367463</v>
+        <v>132367449</v>
       </c>
       <c r="B105" t="n">
-        <v>79086</v>
+        <v>57951</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13137,26 +13137,31 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -13164,10 +13169,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>385332</v>
+        <v>385133</v>
       </c>
       <c r="R105" t="n">
-        <v>6858162</v>
+        <v>6858066</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13208,7 +13213,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -13227,10 +13231,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367466</v>
+        <v>132367444</v>
       </c>
       <c r="B106" t="n">
-        <v>79086</v>
+        <v>57951</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13238,34 +13242,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>384749</v>
+        <v>385280</v>
       </c>
       <c r="R106" t="n">
-        <v>6858223</v>
+        <v>6857923</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13324,10 +13336,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367475</v>
+        <v>132367443</v>
       </c>
       <c r="B107" t="n">
-        <v>79085</v>
+        <v>57951</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13335,34 +13347,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>384814</v>
+        <v>385408</v>
       </c>
       <c r="R107" t="n">
-        <v>6858214</v>
+        <v>6857862</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13421,45 +13441,53 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367394</v>
+        <v>132367430</v>
       </c>
       <c r="B108" t="n">
-        <v>79947</v>
+        <v>57142</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>384969</v>
+        <v>385158</v>
       </c>
       <c r="R108" t="n">
-        <v>6858130</v>
+        <v>6858052</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13518,10 +13546,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367501</v>
+        <v>132367475</v>
       </c>
       <c r="B109" t="n">
-        <v>78335</v>
+        <v>79085</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13529,21 +13557,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13553,10 +13581,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385084</v>
+        <v>384814</v>
       </c>
       <c r="R109" t="n">
-        <v>6858195</v>
+        <v>6858214</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13597,34 +13625,8 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -13641,10 +13643,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367449</v>
+        <v>132367394</v>
       </c>
       <c r="B110" t="n">
-        <v>57951</v>
+        <v>79947</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13652,42 +13654,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385133</v>
+        <v>384969</v>
       </c>
       <c r="R110" t="n">
-        <v>6858066</v>
+        <v>6858130</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13746,10 +13740,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132367444</v>
+        <v>132367501</v>
       </c>
       <c r="B111" t="n">
-        <v>57951</v>
+        <v>78335</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13757,42 +13751,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>385280</v>
+        <v>385084</v>
       </c>
       <c r="R111" t="n">
-        <v>6857923</v>
+        <v>6858195</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13833,8 +13819,34 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13851,10 +13863,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132367443</v>
+        <v>132367463</v>
       </c>
       <c r="B112" t="n">
-        <v>57951</v>
+        <v>79086</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13862,31 +13874,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13894,10 +13901,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>385408</v>
+        <v>385332</v>
       </c>
       <c r="R112" t="n">
-        <v>6857862</v>
+        <v>6858162</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13938,6 +13945,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -13956,53 +13964,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132367430</v>
+        <v>132367466</v>
       </c>
       <c r="B113" t="n">
-        <v>57142</v>
+        <v>79086</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>385158</v>
+        <v>384749</v>
       </c>
       <c r="R113" t="n">
-        <v>6858052</v>
+        <v>6858223</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14166,10 +14166,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132367456</v>
+        <v>132367435</v>
       </c>
       <c r="B115" t="n">
-        <v>57951</v>
+        <v>58115</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14177,21 +14177,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14199,7 +14199,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>385112</v>
+        <v>384859</v>
       </c>
       <c r="R115" t="n">
-        <v>6857918</v>
+        <v>6858073</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14271,10 +14271,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132367435</v>
+        <v>132367456</v>
       </c>
       <c r="B116" t="n">
-        <v>58115</v>
+        <v>57951</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14282,21 +14282,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>384859</v>
+        <v>385112</v>
       </c>
       <c r="R116" t="n">
-        <v>6858073</v>
+        <v>6857918</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14376,32 +14376,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132367448</v>
+        <v>132367412</v>
       </c>
       <c r="B117" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14409,7 +14409,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>385252</v>
+        <v>385208</v>
       </c>
       <c r="R117" t="n">
-        <v>6858060</v>
+        <v>6858049</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14481,7 +14481,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132367412</v>
+        <v>132367415</v>
       </c>
       <c r="B118" t="n">
         <v>57142</v>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>385208</v>
+        <v>385185</v>
       </c>
       <c r="R118" t="n">
-        <v>6858049</v>
+        <v>6858127</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14560,6 +14560,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14586,32 +14591,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132367415</v>
+        <v>132367448</v>
       </c>
       <c r="B119" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14619,7 +14624,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -14629,10 +14634,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>385185</v>
+        <v>385252</v>
       </c>
       <c r="R119" t="n">
-        <v>6858127</v>
+        <v>6858060</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14665,11 +14670,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15220,10 +15220,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367446</v>
+        <v>132367395</v>
       </c>
       <c r="B125" t="n">
-        <v>57951</v>
+        <v>79947</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15231,42 +15231,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>385178</v>
+        <v>384944</v>
       </c>
       <c r="R125" t="n">
-        <v>6858121</v>
+        <v>6858169</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15325,7 +15317,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132367453</v>
+        <v>132367446</v>
       </c>
       <c r="B126" t="n">
         <v>57951</v>
@@ -15358,7 +15350,7 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -15368,10 +15360,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>384934</v>
+        <v>385178</v>
       </c>
       <c r="R126" t="n">
-        <v>6858197</v>
+        <v>6858121</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15430,10 +15422,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367395</v>
+        <v>132367453</v>
       </c>
       <c r="B127" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15441,34 +15433,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>384944</v>
+        <v>384934</v>
       </c>
       <c r="R127" t="n">
-        <v>6858169</v>
+        <v>6858197</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15826,10 +15826,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367455</v>
+        <v>132367392</v>
       </c>
       <c r="B131" t="n">
-        <v>57951</v>
+        <v>79947</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15837,42 +15837,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>384840</v>
+        <v>385102</v>
       </c>
       <c r="R131" t="n">
-        <v>6858190</v>
+        <v>6858138</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15931,7 +15923,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367392</v>
+        <v>132367402</v>
       </c>
       <c r="B132" t="n">
         <v>79947</v>
@@ -15966,10 +15958,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385102</v>
+        <v>385403</v>
       </c>
       <c r="R132" t="n">
-        <v>6858138</v>
+        <v>6857836</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16028,45 +16020,53 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367402</v>
+        <v>132367417</v>
       </c>
       <c r="B133" t="n">
-        <v>79947</v>
+        <v>57142</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>385403</v>
+        <v>385203</v>
       </c>
       <c r="R133" t="n">
-        <v>6857836</v>
+        <v>6858134</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16099,6 +16099,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16125,32 +16130,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132367417</v>
+        <v>132367455</v>
       </c>
       <c r="B134" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -16158,7 +16163,7 @@
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -16168,10 +16173,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>385203</v>
+        <v>384840</v>
       </c>
       <c r="R134" t="n">
-        <v>6858134</v>
+        <v>6858190</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16204,11 +16209,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16235,10 +16235,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367474</v>
+        <v>132367404</v>
       </c>
       <c r="B135" t="n">
-        <v>79085</v>
+        <v>79918</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16246,21 +16246,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16270,10 +16270,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385318</v>
+        <v>385227</v>
       </c>
       <c r="R135" t="n">
-        <v>6858113</v>
+        <v>6857907</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16332,45 +16332,53 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367399</v>
+        <v>132367431</v>
       </c>
       <c r="B136" t="n">
-        <v>79947</v>
+        <v>57142</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>384873</v>
+        <v>384950</v>
       </c>
       <c r="R136" t="n">
-        <v>6858080</v>
+        <v>6858169</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16429,53 +16437,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367421</v>
+        <v>132367474</v>
       </c>
       <c r="B137" t="n">
-        <v>57142</v>
+        <v>79085</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385249</v>
+        <v>385318</v>
       </c>
       <c r="R137" t="n">
-        <v>6858148</v>
+        <v>6858113</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16534,53 +16534,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367431</v>
+        <v>132367399</v>
       </c>
       <c r="B138" t="n">
-        <v>57142</v>
+        <v>79947</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>384950</v>
+        <v>384873</v>
       </c>
       <c r="R138" t="n">
-        <v>6858169</v>
+        <v>6858080</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16639,7 +16631,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367413</v>
+        <v>132367421</v>
       </c>
       <c r="B139" t="n">
         <v>57142</v>
@@ -16682,10 +16674,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>385181</v>
+        <v>385249</v>
       </c>
       <c r="R139" t="n">
-        <v>6858109</v>
+        <v>6858148</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16744,45 +16736,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367404</v>
+        <v>132367413</v>
       </c>
       <c r="B140" t="n">
-        <v>79918</v>
+        <v>57142</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>385227</v>
+        <v>385181</v>
       </c>
       <c r="R140" t="n">
-        <v>6857907</v>
+        <v>6858109</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16841,45 +16841,54 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367403</v>
+        <v>132367469</v>
       </c>
       <c r="B141" t="n">
-        <v>79918</v>
+        <v>8455</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>385374</v>
+        <v>384988</v>
       </c>
       <c r="R141" t="n">
-        <v>6857880</v>
+        <v>6858227</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16920,6 +16929,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16938,10 +16948,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367424</v>
+        <v>132367468</v>
       </c>
       <c r="B142" t="n">
-        <v>57142</v>
+        <v>8455</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16949,29 +16959,30 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -16981,10 +16992,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>385276</v>
+        <v>384943</v>
       </c>
       <c r="R142" t="n">
-        <v>6858157</v>
+        <v>6858164</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17025,6 +17036,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17043,10 +17055,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367469</v>
+        <v>132367424</v>
       </c>
       <c r="B143" t="n">
-        <v>8455</v>
+        <v>57142</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17054,30 +17066,29 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -17087,10 +17098,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>384988</v>
+        <v>385276</v>
       </c>
       <c r="R143" t="n">
-        <v>6858227</v>
+        <v>6858157</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17131,7 +17142,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -17150,54 +17160,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367468</v>
+        <v>132367403</v>
       </c>
       <c r="B144" t="n">
-        <v>8455</v>
+        <v>79918</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>384943</v>
+        <v>385374</v>
       </c>
       <c r="R144" t="n">
-        <v>6858164</v>
+        <v>6857880</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17238,7 +17239,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -17771,53 +17771,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132367418</v>
+        <v>132367410</v>
       </c>
       <c r="B150" t="n">
-        <v>57142</v>
+        <v>79918</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>385198</v>
+        <v>384959</v>
       </c>
       <c r="R150" t="n">
-        <v>6858144</v>
+        <v>6858242</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17876,45 +17868,53 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>132367410</v>
+        <v>132367418</v>
       </c>
       <c r="B151" t="n">
-        <v>79918</v>
+        <v>57142</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>384959</v>
+        <v>385198</v>
       </c>
       <c r="R151" t="n">
-        <v>6858242</v>
+        <v>6858144</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17976,7 +17976,7 @@
         <v>132367459</v>
       </c>
       <c r="B152" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18075,10 +18075,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132367398</v>
+        <v>132367405</v>
       </c>
       <c r="B153" t="n">
-        <v>79947</v>
+        <v>79918</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18086,21 +18086,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18110,10 +18110,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>384804</v>
+        <v>385332</v>
       </c>
       <c r="R153" t="n">
-        <v>6858152</v>
+        <v>6858161</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18172,10 +18172,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132367405</v>
+        <v>132367398</v>
       </c>
       <c r="B154" t="n">
-        <v>79918</v>
+        <v>79947</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18183,21 +18183,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18207,10 +18207,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>385332</v>
+        <v>384804</v>
       </c>
       <c r="R154" t="n">
-        <v>6858161</v>
+        <v>6858152</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18269,45 +18269,53 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367391</v>
+        <v>132367416</v>
       </c>
       <c r="B155" t="n">
-        <v>79947</v>
+        <v>57142</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385129</v>
+        <v>385185</v>
       </c>
       <c r="R155" t="n">
-        <v>6858060</v>
+        <v>6858146</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18366,7 +18374,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367416</v>
+        <v>132367422</v>
       </c>
       <c r="B156" t="n">
         <v>57142</v>
@@ -18409,10 +18417,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385185</v>
+        <v>385246</v>
       </c>
       <c r="R156" t="n">
-        <v>6858146</v>
+        <v>6858162</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18471,53 +18479,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367422</v>
+        <v>132367391</v>
       </c>
       <c r="B157" t="n">
-        <v>57142</v>
+        <v>79947</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385246</v>
+        <v>385129</v>
       </c>
       <c r="R157" t="n">
-        <v>6858162</v>
+        <v>6858060</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18576,10 +18576,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367434</v>
+        <v>132367406</v>
       </c>
       <c r="B158" t="n">
-        <v>58115</v>
+        <v>79918</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18587,31 +18587,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -18619,10 +18614,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385087</v>
+        <v>385318</v>
       </c>
       <c r="R158" t="n">
-        <v>6858055</v>
+        <v>6858113</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18663,6 +18658,7 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -18681,10 +18677,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367406</v>
+        <v>132367434</v>
       </c>
       <c r="B159" t="n">
-        <v>79918</v>
+        <v>58115</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18692,26 +18688,31 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18719,10 +18720,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385318</v>
+        <v>385087</v>
       </c>
       <c r="R159" t="n">
-        <v>6858113</v>
+        <v>6858055</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18763,7 +18764,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18782,27 +18782,27 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367420</v>
+        <v>132367471</v>
       </c>
       <c r="B160" t="n">
-        <v>57142</v>
+        <v>58086</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100138</v>
+        <v>205976</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -18815,7 +18815,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385235</v>
+        <v>385400</v>
       </c>
       <c r="R160" t="n">
-        <v>6858146</v>
+        <v>6857831</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,32 +18887,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367414</v>
+        <v>132367450</v>
       </c>
       <c r="B161" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18920,7 +18920,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -18930,10 +18930,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385197</v>
+        <v>385107</v>
       </c>
       <c r="R161" t="n">
-        <v>6858108</v>
+        <v>6858161</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18992,10 +18992,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367495</v>
+        <v>132367420</v>
       </c>
       <c r="B162" t="n">
-        <v>106245</v>
+        <v>57142</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19003,27 +19003,31 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
@@ -19031,10 +19035,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>384848</v>
+        <v>385235</v>
       </c>
       <c r="R162" t="n">
-        <v>6858075</v>
+        <v>6858146</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19069,18 +19073,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -19099,32 +19097,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367450</v>
+        <v>132367414</v>
       </c>
       <c r="B163" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -19132,7 +19130,7 @@
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -19142,10 +19140,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385107</v>
+        <v>385197</v>
       </c>
       <c r="R163" t="n">
-        <v>6858161</v>
+        <v>6858108</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19204,42 +19202,38 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367471</v>
+        <v>132367495</v>
       </c>
       <c r="B164" t="n">
-        <v>58086</v>
+        <v>106247</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>205976</v>
+        <v>221144</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19247,10 +19241,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385400</v>
+        <v>384848</v>
       </c>
       <c r="R164" t="n">
-        <v>6857831</v>
+        <v>6858075</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19285,12 +19279,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13126,10 +13126,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132367449</v>
+        <v>132367463</v>
       </c>
       <c r="B105" t="n">
-        <v>57951</v>
+        <v>79087</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13137,31 +13137,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -13169,10 +13164,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>385133</v>
+        <v>385332</v>
       </c>
       <c r="R105" t="n">
-        <v>6858066</v>
+        <v>6858162</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13213,6 +13208,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -13231,10 +13227,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367444</v>
+        <v>132367466</v>
       </c>
       <c r="B106" t="n">
-        <v>57951</v>
+        <v>79087</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13242,42 +13238,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>385280</v>
+        <v>384749</v>
       </c>
       <c r="R106" t="n">
-        <v>6857923</v>
+        <v>6858223</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13336,10 +13324,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367443</v>
+        <v>132367475</v>
       </c>
       <c r="B107" t="n">
-        <v>57951</v>
+        <v>79086</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13347,42 +13335,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>385408</v>
+        <v>384814</v>
       </c>
       <c r="R107" t="n">
-        <v>6857862</v>
+        <v>6858214</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13441,53 +13421,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367430</v>
+        <v>132367394</v>
       </c>
       <c r="B108" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>385158</v>
+        <v>384969</v>
       </c>
       <c r="R108" t="n">
-        <v>6858052</v>
+        <v>6858130</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13546,10 +13518,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367475</v>
+        <v>132367501</v>
       </c>
       <c r="B109" t="n">
-        <v>79085</v>
+        <v>78336</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13557,21 +13529,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13581,10 +13553,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>384814</v>
+        <v>385084</v>
       </c>
       <c r="R109" t="n">
-        <v>6858214</v>
+        <v>6858195</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13625,8 +13597,34 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -13643,10 +13641,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367394</v>
+        <v>132367449</v>
       </c>
       <c r="B110" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13654,34 +13652,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>384969</v>
+        <v>385133</v>
       </c>
       <c r="R110" t="n">
-        <v>6858130</v>
+        <v>6858066</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13740,10 +13746,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132367501</v>
+        <v>132367444</v>
       </c>
       <c r="B111" t="n">
-        <v>78335</v>
+        <v>57951</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13751,34 +13757,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>385084</v>
+        <v>385280</v>
       </c>
       <c r="R111" t="n">
-        <v>6858195</v>
+        <v>6857923</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13819,34 +13833,8 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13863,10 +13851,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132367463</v>
+        <v>132367443</v>
       </c>
       <c r="B112" t="n">
-        <v>79086</v>
+        <v>57951</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13874,26 +13862,31 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13901,10 +13894,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>385332</v>
+        <v>385408</v>
       </c>
       <c r="R112" t="n">
-        <v>6858162</v>
+        <v>6857862</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13945,7 +13938,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -13964,45 +13956,53 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132367466</v>
+        <v>132367430</v>
       </c>
       <c r="B113" t="n">
-        <v>79086</v>
+        <v>57142</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>384749</v>
+        <v>385158</v>
       </c>
       <c r="R113" t="n">
-        <v>6858223</v>
+        <v>6858052</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14166,10 +14166,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132367435</v>
+        <v>132367456</v>
       </c>
       <c r="B115" t="n">
-        <v>58115</v>
+        <v>57951</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14177,21 +14177,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -14199,7 +14199,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>384859</v>
+        <v>385112</v>
       </c>
       <c r="R115" t="n">
-        <v>6858073</v>
+        <v>6857918</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14271,10 +14271,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132367456</v>
+        <v>132367435</v>
       </c>
       <c r="B116" t="n">
-        <v>57951</v>
+        <v>58115</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14282,21 +14282,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>385112</v>
+        <v>384859</v>
       </c>
       <c r="R116" t="n">
-        <v>6857918</v>
+        <v>6858073</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14376,32 +14376,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132367412</v>
+        <v>132367448</v>
       </c>
       <c r="B117" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14409,7 +14409,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>385208</v>
+        <v>385252</v>
       </c>
       <c r="R117" t="n">
-        <v>6858049</v>
+        <v>6858060</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14481,7 +14481,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132367415</v>
+        <v>132367412</v>
       </c>
       <c r="B118" t="n">
         <v>57142</v>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>385185</v>
+        <v>385208</v>
       </c>
       <c r="R118" t="n">
-        <v>6858127</v>
+        <v>6858049</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14560,11 +14560,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14591,32 +14586,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132367448</v>
+        <v>132367415</v>
       </c>
       <c r="B119" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14624,7 +14619,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -14634,10 +14629,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>385252</v>
+        <v>385185</v>
       </c>
       <c r="R119" t="n">
-        <v>6858060</v>
+        <v>6858127</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14670,6 +14665,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14699,7 +14699,7 @@
         <v>132367396</v>
       </c>
       <c r="B120" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15220,10 +15220,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367395</v>
+        <v>132367453</v>
       </c>
       <c r="B125" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15231,34 +15231,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>384944</v>
+        <v>384934</v>
       </c>
       <c r="R125" t="n">
-        <v>6858169</v>
+        <v>6858197</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15317,32 +15325,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132367446</v>
+        <v>132367425</v>
       </c>
       <c r="B126" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -15350,7 +15358,7 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -15360,10 +15368,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>385178</v>
+        <v>385281</v>
       </c>
       <c r="R126" t="n">
-        <v>6858121</v>
+        <v>6858170</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15422,10 +15430,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367453</v>
+        <v>132367395</v>
       </c>
       <c r="B127" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15433,42 +15441,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>384934</v>
+        <v>384944</v>
       </c>
       <c r="R127" t="n">
-        <v>6858197</v>
+        <v>6858169</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15527,32 +15527,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367425</v>
+        <v>132367446</v>
       </c>
       <c r="B128" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15560,7 +15560,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -15570,10 +15570,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>385281</v>
+        <v>385178</v>
       </c>
       <c r="R128" t="n">
-        <v>6858170</v>
+        <v>6858121</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15635,7 +15635,7 @@
         <v>132367462</v>
       </c>
       <c r="B129" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>132367464</v>
       </c>
       <c r="B130" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15826,45 +15826,53 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367392</v>
+        <v>132367417</v>
       </c>
       <c r="B131" t="n">
-        <v>79947</v>
+        <v>57142</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>385102</v>
+        <v>385203</v>
       </c>
       <c r="R131" t="n">
-        <v>6858138</v>
+        <v>6858134</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15897,6 +15905,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15923,10 +15936,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367402</v>
+        <v>132367455</v>
       </c>
       <c r="B132" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15934,34 +15947,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385403</v>
+        <v>384840</v>
       </c>
       <c r="R132" t="n">
-        <v>6857836</v>
+        <v>6858190</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16020,53 +16041,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367417</v>
+        <v>132367392</v>
       </c>
       <c r="B133" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>385203</v>
+        <v>385102</v>
       </c>
       <c r="R133" t="n">
-        <v>6858134</v>
+        <v>6858138</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16099,11 +16112,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16130,10 +16138,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132367455</v>
+        <v>132367402</v>
       </c>
       <c r="B134" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16141,42 +16149,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>384840</v>
+        <v>385403</v>
       </c>
       <c r="R134" t="n">
-        <v>6858190</v>
+        <v>6857836</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16235,45 +16235,53 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367404</v>
+        <v>132367421</v>
       </c>
       <c r="B135" t="n">
-        <v>79918</v>
+        <v>57142</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385227</v>
+        <v>385249</v>
       </c>
       <c r="R135" t="n">
-        <v>6857907</v>
+        <v>6858148</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16440,7 +16448,7 @@
         <v>132367474</v>
       </c>
       <c r="B137" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16537,7 +16545,7 @@
         <v>132367399</v>
       </c>
       <c r="B138" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16631,7 +16639,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367421</v>
+        <v>132367413</v>
       </c>
       <c r="B139" t="n">
         <v>57142</v>
@@ -16674,10 +16682,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>385249</v>
+        <v>385181</v>
       </c>
       <c r="R139" t="n">
-        <v>6858148</v>
+        <v>6858109</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16736,53 +16744,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367413</v>
+        <v>132367404</v>
       </c>
       <c r="B140" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>385181</v>
+        <v>385227</v>
       </c>
       <c r="R140" t="n">
-        <v>6858109</v>
+        <v>6857907</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16841,54 +16841,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367469</v>
+        <v>132367403</v>
       </c>
       <c r="B141" t="n">
-        <v>8455</v>
+        <v>79919</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>384988</v>
+        <v>385374</v>
       </c>
       <c r="R141" t="n">
-        <v>6858227</v>
+        <v>6857880</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16929,7 +16920,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16948,10 +16938,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367468</v>
+        <v>132367424</v>
       </c>
       <c r="B142" t="n">
-        <v>8455</v>
+        <v>57142</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16959,30 +16949,29 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -16992,10 +16981,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>384943</v>
+        <v>385276</v>
       </c>
       <c r="R142" t="n">
-        <v>6858164</v>
+        <v>6858157</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17036,7 +17025,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17055,10 +17043,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367424</v>
+        <v>132367469</v>
       </c>
       <c r="B143" t="n">
-        <v>57142</v>
+        <v>8455</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17066,29 +17054,30 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -17098,10 +17087,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>385276</v>
+        <v>384988</v>
       </c>
       <c r="R143" t="n">
-        <v>6858157</v>
+        <v>6858227</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17142,6 +17131,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -17160,45 +17150,54 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367403</v>
+        <v>132367468</v>
       </c>
       <c r="B144" t="n">
-        <v>79918</v>
+        <v>8455</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>385374</v>
+        <v>384943</v>
       </c>
       <c r="R144" t="n">
-        <v>6857880</v>
+        <v>6858164</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17239,6 +17238,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -17472,10 +17472,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132367389</v>
+        <v>132367452</v>
       </c>
       <c r="B147" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17483,34 +17483,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>385195</v>
+        <v>384945</v>
       </c>
       <c r="R147" t="n">
-        <v>6858154</v>
+        <v>6858165</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17569,10 +17577,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367452</v>
+        <v>132367407</v>
       </c>
       <c r="B148" t="n">
-        <v>57951</v>
+        <v>79919</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17580,42 +17588,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>384945</v>
+        <v>385124</v>
       </c>
       <c r="R148" t="n">
-        <v>6858165</v>
+        <v>6858064</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17674,10 +17674,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367407</v>
+        <v>132367389</v>
       </c>
       <c r="B149" t="n">
-        <v>79918</v>
+        <v>79948</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17685,21 +17685,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17709,10 +17709,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>385124</v>
+        <v>385195</v>
       </c>
       <c r="R149" t="n">
-        <v>6858064</v>
+        <v>6858154</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17771,45 +17771,53 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132367410</v>
+        <v>132367418</v>
       </c>
       <c r="B150" t="n">
-        <v>79918</v>
+        <v>57142</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>384959</v>
+        <v>385198</v>
       </c>
       <c r="R150" t="n">
-        <v>6858242</v>
+        <v>6858144</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17868,53 +17876,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>132367418</v>
+        <v>132367410</v>
       </c>
       <c r="B151" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>385198</v>
+        <v>384959</v>
       </c>
       <c r="R151" t="n">
-        <v>6858144</v>
+        <v>6858242</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17973,32 +17973,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367459</v>
+        <v>132367405</v>
       </c>
       <c r="B152" t="n">
-        <v>97986</v>
+        <v>79919</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>384655</v>
+        <v>385332</v>
       </c>
       <c r="R152" t="n">
-        <v>6858187</v>
+        <v>6858161</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18044,11 +18044,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18075,32 +18070,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132367405</v>
+        <v>132367459</v>
       </c>
       <c r="B153" t="n">
-        <v>79918</v>
+        <v>97987</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18110,10 +18105,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>385332</v>
+        <v>384655</v>
       </c>
       <c r="R153" t="n">
-        <v>6858161</v>
+        <v>6858187</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18146,6 +18141,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18175,7 +18175,7 @@
         <v>132367398</v>
       </c>
       <c r="B154" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18269,32 +18269,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367416</v>
+        <v>132367434</v>
       </c>
       <c r="B155" t="n">
-        <v>57142</v>
+        <v>58115</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18302,7 +18302,7 @@
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -18312,10 +18312,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385185</v>
+        <v>385087</v>
       </c>
       <c r="R155" t="n">
-        <v>6858146</v>
+        <v>6858055</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18374,53 +18374,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367422</v>
+        <v>132367391</v>
       </c>
       <c r="B156" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385246</v>
+        <v>385129</v>
       </c>
       <c r="R156" t="n">
-        <v>6858162</v>
+        <v>6858060</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18479,45 +18471,53 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367391</v>
+        <v>132367416</v>
       </c>
       <c r="B157" t="n">
-        <v>79947</v>
+        <v>57142</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385129</v>
+        <v>385185</v>
       </c>
       <c r="R157" t="n">
-        <v>6858060</v>
+        <v>6858146</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18576,37 +18576,42 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367406</v>
+        <v>132367422</v>
       </c>
       <c r="B158" t="n">
-        <v>79918</v>
+        <v>57142</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -18614,10 +18619,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385318</v>
+        <v>385246</v>
       </c>
       <c r="R158" t="n">
-        <v>6858113</v>
+        <v>6858162</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18658,7 +18663,6 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -18677,10 +18681,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367434</v>
+        <v>132367406</v>
       </c>
       <c r="B159" t="n">
-        <v>58115</v>
+        <v>79919</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18688,31 +18692,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18720,10 +18719,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385087</v>
+        <v>385318</v>
       </c>
       <c r="R159" t="n">
-        <v>6858055</v>
+        <v>6858113</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18764,6 +18763,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18782,10 +18782,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367471</v>
+        <v>132367450</v>
       </c>
       <c r="B160" t="n">
-        <v>58086</v>
+        <v>57951</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18793,21 +18793,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18815,7 +18815,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385400</v>
+        <v>385107</v>
       </c>
       <c r="R160" t="n">
-        <v>6857831</v>
+        <v>6858161</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,32 +18887,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367450</v>
+        <v>132367420</v>
       </c>
       <c r="B161" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18920,7 +18920,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -18930,10 +18930,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385107</v>
+        <v>385235</v>
       </c>
       <c r="R161" t="n">
-        <v>6858161</v>
+        <v>6858146</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18992,7 +18992,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367420</v>
+        <v>132367414</v>
       </c>
       <c r="B162" t="n">
         <v>57142</v>
@@ -19035,10 +19035,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385235</v>
+        <v>385197</v>
       </c>
       <c r="R162" t="n">
-        <v>6858146</v>
+        <v>6858108</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19097,10 +19097,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367414</v>
+        <v>132367495</v>
       </c>
       <c r="B163" t="n">
-        <v>57142</v>
+        <v>106248</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19108,31 +19108,27 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -19140,10 +19136,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385197</v>
+        <v>384848</v>
       </c>
       <c r="R163" t="n">
-        <v>6858108</v>
+        <v>6858075</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19178,12 +19174,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -19202,38 +19204,42 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367495</v>
+        <v>132367471</v>
       </c>
       <c r="B164" t="n">
-        <v>106247</v>
+        <v>58086</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221144</v>
+        <v>205976</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19241,10 +19247,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>384848</v>
+        <v>385400</v>
       </c>
       <c r="R164" t="n">
-        <v>6858075</v>
+        <v>6857831</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19279,18 +19285,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -19312,7 +19312,7 @@
         <v>132367465</v>
       </c>
       <c r="B165" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>132367408</v>
       </c>
       <c r="B166" t="n">
-        <v>79918</v>
+        <v>79919</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>132367467</v>
       </c>
       <c r="B167" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19600,53 +19600,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367423</v>
+        <v>132367461</v>
       </c>
       <c r="B168" t="n">
-        <v>57142</v>
+        <v>79087</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385263</v>
+        <v>385227</v>
       </c>
       <c r="R168" t="n">
-        <v>6858153</v>
+        <v>6857907</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19705,37 +19697,42 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367502</v>
+        <v>132367423</v>
       </c>
       <c r="B169" t="n">
-        <v>78731</v>
+        <v>57142</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
@@ -19743,10 +19740,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385349</v>
+        <v>385263</v>
       </c>
       <c r="R169" t="n">
-        <v>6857860</v>
+        <v>6858153</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19787,29 +19784,8 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
@@ -19826,10 +19802,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367393</v>
+        <v>132367502</v>
       </c>
       <c r="B170" t="n">
-        <v>79947</v>
+        <v>78732</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19837,34 +19813,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385118</v>
+        <v>385349</v>
       </c>
       <c r="R170" t="n">
-        <v>6858178</v>
+        <v>6857860</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19905,8 +19884,29 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
@@ -19923,10 +19923,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367461</v>
+        <v>132367393</v>
       </c>
       <c r="B171" t="n">
-        <v>79086</v>
+        <v>79948</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19934,21 +19934,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385227</v>
+        <v>385118</v>
       </c>
       <c r="R171" t="n">
-        <v>6857907</v>
+        <v>6858178</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367409</v>
+        <v>132367401</v>
       </c>
       <c r="B172" t="n">
-        <v>79918</v>
+        <v>79948</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,21 +20031,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -20055,10 +20055,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>385075</v>
+        <v>384992</v>
       </c>
       <c r="R172" t="n">
-        <v>6858201</v>
+        <v>6858018</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20117,10 +20117,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132367401</v>
+        <v>132367447</v>
       </c>
       <c r="B173" t="n">
-        <v>79947</v>
+        <v>57951</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20128,34 +20128,42 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>384992</v>
+        <v>385333</v>
       </c>
       <c r="R173" t="n">
-        <v>6858018</v>
+        <v>6858152</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20214,7 +20222,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367447</v>
+        <v>132367457</v>
       </c>
       <c r="B174" t="n">
         <v>57951</v>
@@ -20247,7 +20255,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -20257,10 +20265,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385333</v>
+        <v>385184</v>
       </c>
       <c r="R174" t="n">
-        <v>6858152</v>
+        <v>6857885</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20319,10 +20327,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132367457</v>
+        <v>132367409</v>
       </c>
       <c r="B175" t="n">
-        <v>57951</v>
+        <v>79919</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20330,42 +20338,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>385184</v>
+        <v>385075</v>
       </c>
       <c r="R175" t="n">
-        <v>6857885</v>
+        <v>6858201</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -14061,10 +14061,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132367451</v>
+        <v>132367435</v>
       </c>
       <c r="B114" t="n">
-        <v>57951</v>
+        <v>58115</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14072,21 +14072,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14094,7 +14094,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -14104,10 +14104,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>385088</v>
+        <v>384859</v>
       </c>
       <c r="R114" t="n">
-        <v>6858196</v>
+        <v>6858073</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14166,7 +14166,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132367456</v>
+        <v>132367451</v>
       </c>
       <c r="B115" t="n">
         <v>57951</v>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>385112</v>
+        <v>385088</v>
       </c>
       <c r="R115" t="n">
-        <v>6857918</v>
+        <v>6858196</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14271,10 +14271,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132367435</v>
+        <v>132367456</v>
       </c>
       <c r="B116" t="n">
-        <v>58115</v>
+        <v>57951</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14282,21 +14282,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>384859</v>
+        <v>385112</v>
       </c>
       <c r="R116" t="n">
-        <v>6858073</v>
+        <v>6857918</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15220,32 +15220,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367453</v>
+        <v>132367425</v>
       </c>
       <c r="B125" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15253,7 +15253,7 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -15263,10 +15263,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>384934</v>
+        <v>385281</v>
       </c>
       <c r="R125" t="n">
-        <v>6858197</v>
+        <v>6858170</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15325,53 +15325,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132367425</v>
+        <v>132367395</v>
       </c>
       <c r="B126" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>385281</v>
+        <v>384944</v>
       </c>
       <c r="R126" t="n">
-        <v>6858170</v>
+        <v>6858169</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15430,10 +15422,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367395</v>
+        <v>132367446</v>
       </c>
       <c r="B127" t="n">
-        <v>79948</v>
+        <v>57951</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15441,34 +15433,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>384944</v>
+        <v>385178</v>
       </c>
       <c r="R127" t="n">
-        <v>6858169</v>
+        <v>6858121</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15527,7 +15527,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367446</v>
+        <v>132367453</v>
       </c>
       <c r="B128" t="n">
         <v>57951</v>
@@ -15560,7 +15560,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -15570,10 +15570,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>385178</v>
+        <v>384934</v>
       </c>
       <c r="R128" t="n">
-        <v>6858121</v>
+        <v>6858197</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15826,32 +15826,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367417</v>
+        <v>132367455</v>
       </c>
       <c r="B131" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15859,7 +15859,7 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>385203</v>
+        <v>384840</v>
       </c>
       <c r="R131" t="n">
-        <v>6858134</v>
+        <v>6858190</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15905,11 +15905,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15936,32 +15931,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367455</v>
+        <v>132367417</v>
       </c>
       <c r="B132" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15969,7 +15964,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -15979,10 +15974,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>384840</v>
+        <v>385203</v>
       </c>
       <c r="R132" t="n">
-        <v>6858190</v>
+        <v>6858134</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16015,6 +16010,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16235,53 +16235,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367421</v>
+        <v>132367404</v>
       </c>
       <c r="B135" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385249</v>
+        <v>385227</v>
       </c>
       <c r="R135" t="n">
-        <v>6858148</v>
+        <v>6857907</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16340,7 +16332,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367431</v>
+        <v>132367421</v>
       </c>
       <c r="B136" t="n">
         <v>57142</v>
@@ -16383,10 +16375,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>384950</v>
+        <v>385249</v>
       </c>
       <c r="R136" t="n">
-        <v>6858169</v>
+        <v>6858148</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16445,45 +16437,53 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367474</v>
+        <v>132367431</v>
       </c>
       <c r="B137" t="n">
-        <v>79086</v>
+        <v>57142</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385318</v>
+        <v>384950</v>
       </c>
       <c r="R137" t="n">
-        <v>6858113</v>
+        <v>6858169</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16542,45 +16542,53 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367399</v>
+        <v>132367413</v>
       </c>
       <c r="B138" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>384873</v>
+        <v>385181</v>
       </c>
       <c r="R138" t="n">
-        <v>6858080</v>
+        <v>6858109</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16639,53 +16647,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367413</v>
+        <v>132367474</v>
       </c>
       <c r="B139" t="n">
-        <v>57142</v>
+        <v>79086</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>385181</v>
+        <v>385318</v>
       </c>
       <c r="R139" t="n">
-        <v>6858109</v>
+        <v>6858113</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16744,10 +16744,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367404</v>
+        <v>132367399</v>
       </c>
       <c r="B140" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16755,21 +16755,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16779,10 +16779,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>385227</v>
+        <v>384873</v>
       </c>
       <c r="R140" t="n">
-        <v>6857907</v>
+        <v>6858080</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16841,45 +16841,53 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367403</v>
+        <v>132367424</v>
       </c>
       <c r="B141" t="n">
-        <v>79919</v>
+        <v>57142</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>385374</v>
+        <v>385276</v>
       </c>
       <c r="R141" t="n">
-        <v>6857880</v>
+        <v>6858157</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16938,10 +16946,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367424</v>
+        <v>132367469</v>
       </c>
       <c r="B142" t="n">
-        <v>57142</v>
+        <v>8455</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16949,29 +16957,30 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -16981,10 +16990,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>385276</v>
+        <v>384988</v>
       </c>
       <c r="R142" t="n">
-        <v>6858157</v>
+        <v>6858227</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17025,6 +17034,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17043,7 +17053,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367469</v>
+        <v>132367468</v>
       </c>
       <c r="B143" t="n">
         <v>8455</v>
@@ -17077,7 +17087,7 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
@@ -17087,10 +17097,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>384988</v>
+        <v>384943</v>
       </c>
       <c r="R143" t="n">
-        <v>6858227</v>
+        <v>6858164</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17150,54 +17160,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367468</v>
+        <v>132367403</v>
       </c>
       <c r="B144" t="n">
-        <v>8455</v>
+        <v>79919</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>384943</v>
+        <v>385374</v>
       </c>
       <c r="R144" t="n">
-        <v>6858164</v>
+        <v>6857880</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17238,7 +17239,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -17257,32 +17257,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132367458</v>
+        <v>132367427</v>
       </c>
       <c r="B145" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17290,7 +17290,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -17300,10 +17300,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>385095</v>
+        <v>385282</v>
       </c>
       <c r="R145" t="n">
-        <v>6857937</v>
+        <v>6858105</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17336,6 +17336,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17362,32 +17367,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132367427</v>
+        <v>132367458</v>
       </c>
       <c r="B146" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17395,7 +17400,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17405,10 +17410,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>385282</v>
+        <v>385095</v>
       </c>
       <c r="R146" t="n">
-        <v>6858105</v>
+        <v>6857937</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17441,11 +17446,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132367452</v>
+        <v>132367389</v>
       </c>
       <c r="B147" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17483,42 +17483,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>384945</v>
+        <v>385195</v>
       </c>
       <c r="R147" t="n">
-        <v>6858165</v>
+        <v>6858154</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17577,10 +17569,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367407</v>
+        <v>132367452</v>
       </c>
       <c r="B148" t="n">
-        <v>79919</v>
+        <v>57951</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17588,34 +17580,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>385124</v>
+        <v>384945</v>
       </c>
       <c r="R148" t="n">
-        <v>6858064</v>
+        <v>6858165</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17674,10 +17674,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367389</v>
+        <v>132367407</v>
       </c>
       <c r="B149" t="n">
-        <v>79948</v>
+        <v>79919</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17685,21 +17685,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17709,10 +17709,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>385195</v>
+        <v>385124</v>
       </c>
       <c r="R149" t="n">
-        <v>6858154</v>
+        <v>6858064</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17771,53 +17771,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132367418</v>
+        <v>132367410</v>
       </c>
       <c r="B150" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>385198</v>
+        <v>384959</v>
       </c>
       <c r="R150" t="n">
-        <v>6858144</v>
+        <v>6858242</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17876,45 +17868,53 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>132367410</v>
+        <v>132367418</v>
       </c>
       <c r="B151" t="n">
-        <v>79919</v>
+        <v>57142</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>384959</v>
+        <v>385198</v>
       </c>
       <c r="R151" t="n">
-        <v>6858242</v>
+        <v>6858144</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18782,10 +18782,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367450</v>
+        <v>132367471</v>
       </c>
       <c r="B160" t="n">
-        <v>57951</v>
+        <v>58086</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18793,21 +18793,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>205976</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18815,7 +18815,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385107</v>
+        <v>385400</v>
       </c>
       <c r="R160" t="n">
-        <v>6858161</v>
+        <v>6857831</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,10 +18887,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367420</v>
+        <v>132367495</v>
       </c>
       <c r="B161" t="n">
-        <v>57142</v>
+        <v>106248</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18898,31 +18898,27 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -18930,10 +18926,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385235</v>
+        <v>384848</v>
       </c>
       <c r="R161" t="n">
-        <v>6858146</v>
+        <v>6858075</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18968,12 +18964,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -18992,53 +18994,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367414</v>
+        <v>132367465</v>
       </c>
       <c r="B162" t="n">
-        <v>57142</v>
+        <v>79087</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385197</v>
+        <v>385131</v>
       </c>
       <c r="R162" t="n">
-        <v>6858108</v>
+        <v>6858065</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19097,49 +19091,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367495</v>
+        <v>132367408</v>
       </c>
       <c r="B163" t="n">
-        <v>106248</v>
+        <v>79919</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>221144</v>
+        <v>229821</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>384848</v>
+        <v>385062</v>
       </c>
       <c r="R163" t="n">
-        <v>6858075</v>
+        <v>6858092</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19174,18 +19164,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -19204,10 +19188,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367471</v>
+        <v>132367450</v>
       </c>
       <c r="B164" t="n">
-        <v>58086</v>
+        <v>57951</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19215,21 +19199,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19237,7 +19221,7 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
@@ -19247,10 +19231,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385400</v>
+        <v>385107</v>
       </c>
       <c r="R164" t="n">
-        <v>6857831</v>
+        <v>6858161</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19309,45 +19293,53 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367465</v>
+        <v>132367420</v>
       </c>
       <c r="B165" t="n">
-        <v>79087</v>
+        <v>57142</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385131</v>
+        <v>385235</v>
       </c>
       <c r="R165" t="n">
-        <v>6858065</v>
+        <v>6858146</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19406,45 +19398,53 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367408</v>
+        <v>132367414</v>
       </c>
       <c r="B166" t="n">
-        <v>79919</v>
+        <v>57142</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385062</v>
+        <v>385197</v>
       </c>
       <c r="R166" t="n">
-        <v>6858092</v>
+        <v>6858108</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19600,10 +19600,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367461</v>
+        <v>132367502</v>
       </c>
       <c r="B168" t="n">
-        <v>79087</v>
+        <v>78732</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19611,34 +19611,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385227</v>
+        <v>385349</v>
       </c>
       <c r="R168" t="n">
-        <v>6857907</v>
+        <v>6857860</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19679,8 +19682,29 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -19697,53 +19721,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367423</v>
+        <v>132367393</v>
       </c>
       <c r="B169" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385263</v>
+        <v>385118</v>
       </c>
       <c r="R169" t="n">
-        <v>6858153</v>
+        <v>6858178</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19802,37 +19818,42 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367502</v>
+        <v>132367423</v>
       </c>
       <c r="B170" t="n">
-        <v>78732</v>
+        <v>57142</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -19840,10 +19861,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385349</v>
+        <v>385263</v>
       </c>
       <c r="R170" t="n">
-        <v>6857860</v>
+        <v>6858153</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19884,29 +19905,8 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
@@ -19923,10 +19923,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367393</v>
+        <v>132367461</v>
       </c>
       <c r="B171" t="n">
-        <v>79948</v>
+        <v>79087</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19934,21 +19934,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19958,10 +19958,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385118</v>
+        <v>385227</v>
       </c>
       <c r="R171" t="n">
-        <v>6858178</v>
+        <v>6857907</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367401</v>
+        <v>132367409</v>
       </c>
       <c r="B172" t="n">
-        <v>79948</v>
+        <v>79919</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,21 +20031,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -20055,10 +20055,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>384992</v>
+        <v>385075</v>
       </c>
       <c r="R172" t="n">
-        <v>6858018</v>
+        <v>6858201</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20117,10 +20117,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132367447</v>
+        <v>132367401</v>
       </c>
       <c r="B173" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20128,42 +20128,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>385333</v>
+        <v>384992</v>
       </c>
       <c r="R173" t="n">
-        <v>6858152</v>
+        <v>6858018</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20222,7 +20214,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367457</v>
+        <v>132367447</v>
       </c>
       <c r="B174" t="n">
         <v>57951</v>
@@ -20255,7 +20247,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -20265,10 +20257,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385184</v>
+        <v>385333</v>
       </c>
       <c r="R174" t="n">
-        <v>6857885</v>
+        <v>6858152</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20327,10 +20319,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132367409</v>
+        <v>132367457</v>
       </c>
       <c r="B175" t="n">
-        <v>79919</v>
+        <v>57951</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20338,34 +20330,42 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>385075</v>
+        <v>385184</v>
       </c>
       <c r="R175" t="n">
-        <v>6858201</v>
+        <v>6857885</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13126,10 +13126,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132367463</v>
+        <v>132367475</v>
       </c>
       <c r="B105" t="n">
-        <v>79087</v>
+        <v>79086</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13137,37 +13137,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>385332</v>
+        <v>384814</v>
       </c>
       <c r="R105" t="n">
-        <v>6858162</v>
+        <v>6858214</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13208,7 +13205,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -13227,10 +13223,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367466</v>
+        <v>132367394</v>
       </c>
       <c r="B106" t="n">
-        <v>79087</v>
+        <v>79948</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13238,21 +13234,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13262,10 +13258,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>384749</v>
+        <v>384969</v>
       </c>
       <c r="R106" t="n">
-        <v>6858223</v>
+        <v>6858130</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13324,10 +13320,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367475</v>
+        <v>132367501</v>
       </c>
       <c r="B107" t="n">
-        <v>79086</v>
+        <v>78336</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13335,21 +13331,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13359,10 +13355,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>384814</v>
+        <v>385084</v>
       </c>
       <c r="R107" t="n">
-        <v>6858214</v>
+        <v>6858195</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13403,8 +13399,34 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13421,10 +13443,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367394</v>
+        <v>132367444</v>
       </c>
       <c r="B108" t="n">
-        <v>79948</v>
+        <v>57951</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13432,34 +13454,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>384969</v>
+        <v>385280</v>
       </c>
       <c r="R108" t="n">
-        <v>6858130</v>
+        <v>6857923</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13518,10 +13548,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367501</v>
+        <v>132367449</v>
       </c>
       <c r="B109" t="n">
-        <v>78336</v>
+        <v>57951</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13529,34 +13559,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385084</v>
+        <v>385133</v>
       </c>
       <c r="R109" t="n">
-        <v>6858195</v>
+        <v>6858066</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13597,34 +13635,8 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -13641,32 +13653,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367449</v>
+        <v>132367430</v>
       </c>
       <c r="B110" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13674,7 +13686,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -13684,10 +13696,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385133</v>
+        <v>385158</v>
       </c>
       <c r="R110" t="n">
-        <v>6858066</v>
+        <v>6858052</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13746,10 +13758,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132367444</v>
+        <v>132367463</v>
       </c>
       <c r="B111" t="n">
-        <v>57951</v>
+        <v>79087</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13757,31 +13769,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -13789,10 +13796,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>385280</v>
+        <v>385332</v>
       </c>
       <c r="R111" t="n">
-        <v>6857923</v>
+        <v>6858162</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13833,6 +13840,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -13851,10 +13859,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132367443</v>
+        <v>132367466</v>
       </c>
       <c r="B112" t="n">
-        <v>57951</v>
+        <v>79087</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13862,42 +13870,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>385408</v>
+        <v>384749</v>
       </c>
       <c r="R112" t="n">
-        <v>6857862</v>
+        <v>6858223</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13956,32 +13956,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132367430</v>
+        <v>132367443</v>
       </c>
       <c r="B113" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13989,7 +13989,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -13999,10 +13999,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>385158</v>
+        <v>385408</v>
       </c>
       <c r="R113" t="n">
-        <v>6858052</v>
+        <v>6857862</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14376,32 +14376,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132367448</v>
+        <v>132367412</v>
       </c>
       <c r="B117" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14409,7 +14409,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>385252</v>
+        <v>385208</v>
       </c>
       <c r="R117" t="n">
-        <v>6858060</v>
+        <v>6858049</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14481,7 +14481,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132367412</v>
+        <v>132367415</v>
       </c>
       <c r="B118" t="n">
         <v>57142</v>
@@ -14524,10 +14524,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>385208</v>
+        <v>385185</v>
       </c>
       <c r="R118" t="n">
-        <v>6858049</v>
+        <v>6858127</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14560,6 +14560,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14586,32 +14591,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132367415</v>
+        <v>132367448</v>
       </c>
       <c r="B119" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14619,7 +14624,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -14629,10 +14634,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>385185</v>
+        <v>385252</v>
       </c>
       <c r="R119" t="n">
-        <v>6858127</v>
+        <v>6858060</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14665,11 +14670,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14793,10 +14793,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132367428</v>
+        <v>132367470</v>
       </c>
       <c r="B121" t="n">
-        <v>57142</v>
+        <v>8455</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14804,29 +14804,30 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14836,10 +14837,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>385279</v>
+        <v>384910</v>
       </c>
       <c r="R121" t="n">
-        <v>6858073</v>
+        <v>6858203</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14874,17 +14875,13 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -14903,7 +14900,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132367432</v>
+        <v>132367428</v>
       </c>
       <c r="B122" t="n">
         <v>57142</v>
@@ -14946,10 +14943,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>385185</v>
+        <v>385279</v>
       </c>
       <c r="R122" t="n">
-        <v>6858160</v>
+        <v>6858073</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14982,6 +14979,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15008,10 +15010,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132367470</v>
+        <v>132367432</v>
       </c>
       <c r="B123" t="n">
-        <v>8455</v>
+        <v>57142</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15019,30 +15021,29 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -15052,10 +15053,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>384910</v>
+        <v>385185</v>
       </c>
       <c r="R123" t="n">
-        <v>6858203</v>
+        <v>6858160</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15096,7 +15097,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -15220,53 +15220,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367425</v>
+        <v>132367395</v>
       </c>
       <c r="B125" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>385281</v>
+        <v>384944</v>
       </c>
       <c r="R125" t="n">
-        <v>6858170</v>
+        <v>6858169</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15325,10 +15317,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132367395</v>
+        <v>132367446</v>
       </c>
       <c r="B126" t="n">
-        <v>79948</v>
+        <v>57951</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15336,34 +15328,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>384944</v>
+        <v>385178</v>
       </c>
       <c r="R126" t="n">
-        <v>6858169</v>
+        <v>6858121</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15422,10 +15422,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367446</v>
+        <v>132367464</v>
       </c>
       <c r="B127" t="n">
-        <v>57951</v>
+        <v>79087</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15433,42 +15433,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>385178</v>
+        <v>385318</v>
       </c>
       <c r="R127" t="n">
-        <v>6858121</v>
+        <v>6858113</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15527,10 +15519,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367453</v>
+        <v>132367462</v>
       </c>
       <c r="B128" t="n">
-        <v>57951</v>
+        <v>79087</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15538,42 +15530,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>384934</v>
+        <v>385195</v>
       </c>
       <c r="R128" t="n">
-        <v>6858197</v>
+        <v>6858154</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15632,10 +15616,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132367462</v>
+        <v>132367453</v>
       </c>
       <c r="B129" t="n">
-        <v>79087</v>
+        <v>57951</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15643,34 +15627,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>385195</v>
+        <v>384934</v>
       </c>
       <c r="R129" t="n">
-        <v>6858154</v>
+        <v>6858197</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15729,45 +15721,53 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132367464</v>
+        <v>132367425</v>
       </c>
       <c r="B130" t="n">
-        <v>79087</v>
+        <v>57142</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>385318</v>
+        <v>385281</v>
       </c>
       <c r="R130" t="n">
-        <v>6858113</v>
+        <v>6858170</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15826,10 +15826,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367455</v>
+        <v>132367392</v>
       </c>
       <c r="B131" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15837,42 +15837,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>384840</v>
+        <v>385102</v>
       </c>
       <c r="R131" t="n">
-        <v>6858190</v>
+        <v>6858138</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15931,53 +15923,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367417</v>
+        <v>132367402</v>
       </c>
       <c r="B132" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385203</v>
+        <v>385403</v>
       </c>
       <c r="R132" t="n">
-        <v>6858134</v>
+        <v>6857836</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16010,11 +15994,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16041,10 +16020,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367392</v>
+        <v>132367455</v>
       </c>
       <c r="B133" t="n">
-        <v>79948</v>
+        <v>57951</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16052,34 +16031,42 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>385102</v>
+        <v>384840</v>
       </c>
       <c r="R133" t="n">
-        <v>6858138</v>
+        <v>6858190</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16138,45 +16125,53 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132367402</v>
+        <v>132367417</v>
       </c>
       <c r="B134" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>385403</v>
+        <v>385203</v>
       </c>
       <c r="R134" t="n">
-        <v>6857836</v>
+        <v>6858134</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16209,6 +16204,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16235,10 +16235,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367404</v>
+        <v>132367474</v>
       </c>
       <c r="B135" t="n">
-        <v>79919</v>
+        <v>79086</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16246,21 +16246,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16270,10 +16270,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385227</v>
+        <v>385318</v>
       </c>
       <c r="R135" t="n">
-        <v>6857907</v>
+        <v>6858113</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16332,53 +16332,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367421</v>
+        <v>132367399</v>
       </c>
       <c r="B136" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>385249</v>
+        <v>384873</v>
       </c>
       <c r="R136" t="n">
-        <v>6858148</v>
+        <v>6858080</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16437,53 +16429,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367431</v>
+        <v>132367404</v>
       </c>
       <c r="B137" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>384950</v>
+        <v>385227</v>
       </c>
       <c r="R137" t="n">
-        <v>6858169</v>
+        <v>6857907</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16542,7 +16526,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367413</v>
+        <v>132367421</v>
       </c>
       <c r="B138" t="n">
         <v>57142</v>
@@ -16585,10 +16569,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>385181</v>
+        <v>385249</v>
       </c>
       <c r="R138" t="n">
-        <v>6858109</v>
+        <v>6858148</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16647,45 +16631,53 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132367474</v>
+        <v>132367431</v>
       </c>
       <c r="B139" t="n">
-        <v>79086</v>
+        <v>57142</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>385318</v>
+        <v>384950</v>
       </c>
       <c r="R139" t="n">
-        <v>6858113</v>
+        <v>6858169</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16744,45 +16736,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132367399</v>
+        <v>132367413</v>
       </c>
       <c r="B140" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>384873</v>
+        <v>385181</v>
       </c>
       <c r="R140" t="n">
-        <v>6858080</v>
+        <v>6858109</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16841,10 +16841,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367424</v>
+        <v>132367469</v>
       </c>
       <c r="B141" t="n">
-        <v>57142</v>
+        <v>8455</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16852,29 +16852,30 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -16884,10 +16885,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>385276</v>
+        <v>384988</v>
       </c>
       <c r="R141" t="n">
-        <v>6858157</v>
+        <v>6858227</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16928,6 +16929,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16946,7 +16948,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367469</v>
+        <v>132367468</v>
       </c>
       <c r="B142" t="n">
         <v>8455</v>
@@ -16980,7 +16982,7 @@
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -16990,10 +16992,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>384988</v>
+        <v>384943</v>
       </c>
       <c r="R142" t="n">
-        <v>6858227</v>
+        <v>6858164</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17053,54 +17055,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367468</v>
+        <v>132367403</v>
       </c>
       <c r="B143" t="n">
-        <v>8455</v>
+        <v>79919</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>384943</v>
+        <v>385374</v>
       </c>
       <c r="R143" t="n">
-        <v>6858164</v>
+        <v>6857880</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17141,7 +17134,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -17160,45 +17152,53 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367403</v>
+        <v>132367424</v>
       </c>
       <c r="B144" t="n">
-        <v>79919</v>
+        <v>57142</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>385374</v>
+        <v>385276</v>
       </c>
       <c r="R144" t="n">
-        <v>6857880</v>
+        <v>6858157</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17257,32 +17257,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132367427</v>
+        <v>132367458</v>
       </c>
       <c r="B145" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -17290,7 +17290,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -17300,10 +17300,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>385282</v>
+        <v>385095</v>
       </c>
       <c r="R145" t="n">
-        <v>6858105</v>
+        <v>6857937</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17336,11 +17336,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17367,32 +17362,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132367458</v>
+        <v>132367427</v>
       </c>
       <c r="B146" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17400,7 +17395,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -17410,10 +17405,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>385095</v>
+        <v>385282</v>
       </c>
       <c r="R146" t="n">
-        <v>6857937</v>
+        <v>6858105</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17446,6 +17441,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17472,10 +17472,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132367389</v>
+        <v>132367452</v>
       </c>
       <c r="B147" t="n">
-        <v>79948</v>
+        <v>57951</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17483,34 +17483,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>385195</v>
+        <v>384945</v>
       </c>
       <c r="R147" t="n">
-        <v>6858154</v>
+        <v>6858165</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17569,10 +17577,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367452</v>
+        <v>132367407</v>
       </c>
       <c r="B148" t="n">
-        <v>57951</v>
+        <v>79919</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17580,42 +17588,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>384945</v>
+        <v>385124</v>
       </c>
       <c r="R148" t="n">
-        <v>6858165</v>
+        <v>6858064</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17674,10 +17674,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367407</v>
+        <v>132367389</v>
       </c>
       <c r="B149" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17685,21 +17685,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17709,10 +17709,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>385124</v>
+        <v>385195</v>
       </c>
       <c r="R149" t="n">
-        <v>6858064</v>
+        <v>6858154</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17771,45 +17771,53 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132367410</v>
+        <v>132367418</v>
       </c>
       <c r="B150" t="n">
-        <v>79919</v>
+        <v>57142</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>384959</v>
+        <v>385198</v>
       </c>
       <c r="R150" t="n">
-        <v>6858242</v>
+        <v>6858144</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17868,53 +17876,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>132367418</v>
+        <v>132367410</v>
       </c>
       <c r="B151" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>385198</v>
+        <v>384959</v>
       </c>
       <c r="R151" t="n">
-        <v>6858144</v>
+        <v>6858242</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17973,32 +17973,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367405</v>
+        <v>132367459</v>
       </c>
       <c r="B152" t="n">
-        <v>79919</v>
+        <v>97987</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>385332</v>
+        <v>384655</v>
       </c>
       <c r="R152" t="n">
-        <v>6858161</v>
+        <v>6858187</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18044,6 +18044,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18070,32 +18075,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132367459</v>
+        <v>132367405</v>
       </c>
       <c r="B153" t="n">
-        <v>97987</v>
+        <v>79919</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18105,10 +18110,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>384655</v>
+        <v>385332</v>
       </c>
       <c r="R153" t="n">
-        <v>6858187</v>
+        <v>6858161</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18141,11 +18146,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18269,32 +18269,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367434</v>
+        <v>132367416</v>
       </c>
       <c r="B155" t="n">
-        <v>58115</v>
+        <v>57142</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18302,7 +18302,7 @@
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -18312,10 +18312,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385087</v>
+        <v>385185</v>
       </c>
       <c r="R155" t="n">
-        <v>6858055</v>
+        <v>6858146</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18374,45 +18374,53 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367391</v>
+        <v>132367422</v>
       </c>
       <c r="B156" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385129</v>
+        <v>385246</v>
       </c>
       <c r="R156" t="n">
-        <v>6858060</v>
+        <v>6858162</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18471,42 +18479,37 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367416</v>
+        <v>132367406</v>
       </c>
       <c r="B157" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -18514,10 +18517,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385185</v>
+        <v>385318</v>
       </c>
       <c r="R157" t="n">
-        <v>6858146</v>
+        <v>6858113</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18558,6 +18561,7 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -18576,32 +18580,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367422</v>
+        <v>132367434</v>
       </c>
       <c r="B158" t="n">
-        <v>57142</v>
+        <v>58115</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18609,7 +18613,7 @@
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -18619,10 +18623,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385246</v>
+        <v>385087</v>
       </c>
       <c r="R158" t="n">
-        <v>6858162</v>
+        <v>6858055</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18681,10 +18685,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367406</v>
+        <v>132367391</v>
       </c>
       <c r="B159" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18692,37 +18696,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385318</v>
+        <v>385129</v>
       </c>
       <c r="R159" t="n">
-        <v>6858113</v>
+        <v>6858060</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18763,7 +18764,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18887,49 +18887,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367495</v>
+        <v>132367408</v>
       </c>
       <c r="B161" t="n">
-        <v>106248</v>
+        <v>79919</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221144</v>
+        <v>229821</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>384848</v>
+        <v>385062</v>
       </c>
       <c r="R161" t="n">
-        <v>6858075</v>
+        <v>6858092</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18964,18 +18960,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -19091,45 +19081,49 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367408</v>
+        <v>132367495</v>
       </c>
       <c r="B163" t="n">
-        <v>79919</v>
+        <v>106248</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>229821</v>
+        <v>221144</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385062</v>
+        <v>384848</v>
       </c>
       <c r="R163" t="n">
-        <v>6858092</v>
+        <v>6858075</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19164,12 +19158,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -20020,10 +20020,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367409</v>
+        <v>132367401</v>
       </c>
       <c r="B172" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20031,21 +20031,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -20055,10 +20055,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>385075</v>
+        <v>384992</v>
       </c>
       <c r="R172" t="n">
-        <v>6858201</v>
+        <v>6858018</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20117,10 +20117,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132367401</v>
+        <v>132367447</v>
       </c>
       <c r="B173" t="n">
-        <v>79948</v>
+        <v>57951</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20128,34 +20128,42 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>384992</v>
+        <v>385333</v>
       </c>
       <c r="R173" t="n">
-        <v>6858018</v>
+        <v>6858152</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20214,7 +20222,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367447</v>
+        <v>132367457</v>
       </c>
       <c r="B174" t="n">
         <v>57951</v>
@@ -20247,7 +20255,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -20257,10 +20265,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385333</v>
+        <v>385184</v>
       </c>
       <c r="R174" t="n">
-        <v>6858152</v>
+        <v>6857885</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20319,10 +20327,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132367457</v>
+        <v>132367409</v>
       </c>
       <c r="B175" t="n">
-        <v>57951</v>
+        <v>79919</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20330,42 +20338,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>385184</v>
+        <v>385075</v>
       </c>
       <c r="R175" t="n">
-        <v>6857885</v>
+        <v>6858201</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -13443,7 +13443,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367444</v>
+        <v>132367449</v>
       </c>
       <c r="B108" t="n">
         <v>57951</v>
@@ -13476,7 +13476,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -13486,10 +13486,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>385280</v>
+        <v>385133</v>
       </c>
       <c r="R108" t="n">
-        <v>6857923</v>
+        <v>6858066</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367449</v>
+        <v>132367444</v>
       </c>
       <c r="B109" t="n">
         <v>57951</v>
@@ -13581,7 +13581,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -13591,10 +13591,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385133</v>
+        <v>385280</v>
       </c>
       <c r="R109" t="n">
-        <v>6858066</v>
+        <v>6857923</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13653,32 +13653,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367430</v>
+        <v>132367443</v>
       </c>
       <c r="B110" t="n">
-        <v>57142</v>
+        <v>57951</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13686,7 +13686,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -13696,10 +13696,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385158</v>
+        <v>385408</v>
       </c>
       <c r="R110" t="n">
-        <v>6858052</v>
+        <v>6857862</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13956,32 +13956,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132367443</v>
+        <v>132367430</v>
       </c>
       <c r="B113" t="n">
-        <v>57951</v>
+        <v>57142</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13989,7 +13989,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -13999,10 +13999,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>385408</v>
+        <v>385158</v>
       </c>
       <c r="R113" t="n">
-        <v>6857862</v>
+        <v>6858052</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14793,10 +14793,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132367470</v>
+        <v>132367428</v>
       </c>
       <c r="B121" t="n">
-        <v>8455</v>
+        <v>57142</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14804,30 +14804,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -14837,10 +14836,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>384910</v>
+        <v>385279</v>
       </c>
       <c r="R121" t="n">
-        <v>6858203</v>
+        <v>6858073</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14875,13 +14874,17 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -14900,7 +14903,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132367428</v>
+        <v>132367432</v>
       </c>
       <c r="B122" t="n">
         <v>57142</v>
@@ -14943,10 +14946,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>385279</v>
+        <v>385185</v>
       </c>
       <c r="R122" t="n">
-        <v>6858073</v>
+        <v>6858160</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14979,11 +14982,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15010,10 +15008,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132367432</v>
+        <v>132367470</v>
       </c>
       <c r="B123" t="n">
-        <v>57142</v>
+        <v>8455</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15021,29 +15019,30 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -15053,10 +15052,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>385185</v>
+        <v>384910</v>
       </c>
       <c r="R123" t="n">
-        <v>6858160</v>
+        <v>6858203</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15097,6 +15096,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -15422,10 +15422,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132367464</v>
+        <v>132367453</v>
       </c>
       <c r="B127" t="n">
-        <v>79087</v>
+        <v>57951</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15433,34 +15433,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>385318</v>
+        <v>384934</v>
       </c>
       <c r="R127" t="n">
-        <v>6858113</v>
+        <v>6858197</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15519,45 +15527,53 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367462</v>
+        <v>132367425</v>
       </c>
       <c r="B128" t="n">
-        <v>79087</v>
+        <v>57142</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>385195</v>
+        <v>385281</v>
       </c>
       <c r="R128" t="n">
-        <v>6858154</v>
+        <v>6858170</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15616,10 +15632,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132367453</v>
+        <v>132367462</v>
       </c>
       <c r="B129" t="n">
-        <v>57951</v>
+        <v>79087</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15627,42 +15643,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>384934</v>
+        <v>385195</v>
       </c>
       <c r="R129" t="n">
-        <v>6858197</v>
+        <v>6858154</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15721,53 +15729,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132367425</v>
+        <v>132367464</v>
       </c>
       <c r="B130" t="n">
-        <v>57142</v>
+        <v>79087</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>385281</v>
+        <v>385318</v>
       </c>
       <c r="R130" t="n">
-        <v>6858170</v>
+        <v>6858113</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15826,10 +15826,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367392</v>
+        <v>132367455</v>
       </c>
       <c r="B131" t="n">
-        <v>79948</v>
+        <v>57951</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15837,34 +15837,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>385102</v>
+        <v>384840</v>
       </c>
       <c r="R131" t="n">
-        <v>6858138</v>
+        <v>6858190</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15923,45 +15931,53 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367402</v>
+        <v>132367417</v>
       </c>
       <c r="B132" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385403</v>
+        <v>385203</v>
       </c>
       <c r="R132" t="n">
-        <v>6857836</v>
+        <v>6858134</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15994,6 +16010,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16020,10 +16041,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367455</v>
+        <v>132367392</v>
       </c>
       <c r="B133" t="n">
-        <v>57951</v>
+        <v>79948</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16031,42 +16052,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>384840</v>
+        <v>385102</v>
       </c>
       <c r="R133" t="n">
-        <v>6858190</v>
+        <v>6858138</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16125,53 +16138,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132367417</v>
+        <v>132367402</v>
       </c>
       <c r="B134" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>385203</v>
+        <v>385403</v>
       </c>
       <c r="R134" t="n">
-        <v>6858134</v>
+        <v>6857836</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16204,11 +16209,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16235,10 +16235,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367474</v>
+        <v>132367404</v>
       </c>
       <c r="B135" t="n">
-        <v>79086</v>
+        <v>79919</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16246,21 +16246,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16270,10 +16270,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385318</v>
+        <v>385227</v>
       </c>
       <c r="R135" t="n">
-        <v>6858113</v>
+        <v>6857907</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16332,10 +16332,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367399</v>
+        <v>132367474</v>
       </c>
       <c r="B136" t="n">
-        <v>79948</v>
+        <v>79086</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16343,21 +16343,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16367,10 +16367,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>384873</v>
+        <v>385318</v>
       </c>
       <c r="R136" t="n">
-        <v>6858080</v>
+        <v>6858113</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16429,10 +16429,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367404</v>
+        <v>132367399</v>
       </c>
       <c r="B137" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16440,21 +16440,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16464,10 +16464,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385227</v>
+        <v>384873</v>
       </c>
       <c r="R137" t="n">
-        <v>6857907</v>
+        <v>6858080</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16841,54 +16841,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132367469</v>
+        <v>132367403</v>
       </c>
       <c r="B141" t="n">
-        <v>8455</v>
+        <v>79919</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>384988</v>
+        <v>385374</v>
       </c>
       <c r="R141" t="n">
-        <v>6858227</v>
+        <v>6857880</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16929,7 +16920,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16948,10 +16938,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132367468</v>
+        <v>132367424</v>
       </c>
       <c r="B142" t="n">
-        <v>8455</v>
+        <v>57142</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16959,30 +16949,29 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -16992,10 +16981,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>384943</v>
+        <v>385276</v>
       </c>
       <c r="R142" t="n">
-        <v>6858164</v>
+        <v>6858157</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17036,7 +17025,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -17055,45 +17043,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132367403</v>
+        <v>132367469</v>
       </c>
       <c r="B143" t="n">
-        <v>79919</v>
+        <v>8455</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>385374</v>
+        <v>384988</v>
       </c>
       <c r="R143" t="n">
-        <v>6857880</v>
+        <v>6858227</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17134,6 +17131,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -17152,10 +17150,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132367424</v>
+        <v>132367468</v>
       </c>
       <c r="B144" t="n">
-        <v>57142</v>
+        <v>8455</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17163,29 +17161,30 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -17195,10 +17194,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>385276</v>
+        <v>384943</v>
       </c>
       <c r="R144" t="n">
-        <v>6858157</v>
+        <v>6858164</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17239,6 +17238,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -17577,10 +17577,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367407</v>
+        <v>132367389</v>
       </c>
       <c r="B148" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17588,21 +17588,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17612,10 +17612,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>385124</v>
+        <v>385195</v>
       </c>
       <c r="R148" t="n">
-        <v>6858064</v>
+        <v>6858154</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17674,10 +17674,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132367389</v>
+        <v>132367407</v>
       </c>
       <c r="B149" t="n">
-        <v>79948</v>
+        <v>79919</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17685,21 +17685,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17709,10 +17709,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>385195</v>
+        <v>385124</v>
       </c>
       <c r="R149" t="n">
-        <v>6858154</v>
+        <v>6858064</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17973,32 +17973,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367459</v>
+        <v>132367405</v>
       </c>
       <c r="B152" t="n">
-        <v>97987</v>
+        <v>79919</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>384655</v>
+        <v>385332</v>
       </c>
       <c r="R152" t="n">
-        <v>6858187</v>
+        <v>6858161</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18044,11 +18044,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18075,32 +18070,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132367405</v>
+        <v>132367459</v>
       </c>
       <c r="B153" t="n">
-        <v>79919</v>
+        <v>97987</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18110,10 +18105,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>385332</v>
+        <v>384655</v>
       </c>
       <c r="R153" t="n">
-        <v>6858161</v>
+        <v>6858187</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18146,6 +18141,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18269,32 +18269,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367416</v>
+        <v>132367434</v>
       </c>
       <c r="B155" t="n">
-        <v>57142</v>
+        <v>58115</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18302,7 +18302,7 @@
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
@@ -18312,10 +18312,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385185</v>
+        <v>385087</v>
       </c>
       <c r="R155" t="n">
-        <v>6858146</v>
+        <v>6858055</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18374,42 +18374,37 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367422</v>
+        <v>132367406</v>
       </c>
       <c r="B156" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -18417,10 +18412,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385246</v>
+        <v>385318</v>
       </c>
       <c r="R156" t="n">
-        <v>6858162</v>
+        <v>6858113</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18461,6 +18456,7 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -18479,10 +18475,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367406</v>
+        <v>132367391</v>
       </c>
       <c r="B157" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18490,37 +18486,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385318</v>
+        <v>385129</v>
       </c>
       <c r="R157" t="n">
-        <v>6858113</v>
+        <v>6858060</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18561,7 +18554,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -18580,32 +18572,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367434</v>
+        <v>132367416</v>
       </c>
       <c r="B158" t="n">
-        <v>58115</v>
+        <v>57142</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18613,7 +18605,7 @@
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -18623,10 +18615,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385087</v>
+        <v>385185</v>
       </c>
       <c r="R158" t="n">
-        <v>6858055</v>
+        <v>6858146</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18685,45 +18677,53 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367391</v>
+        <v>132367422</v>
       </c>
       <c r="B159" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385129</v>
+        <v>385246</v>
       </c>
       <c r="R159" t="n">
-        <v>6858060</v>
+        <v>6858162</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18782,10 +18782,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367471</v>
+        <v>132367450</v>
       </c>
       <c r="B160" t="n">
-        <v>58086</v>
+        <v>57951</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18793,21 +18793,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18815,7 +18815,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385400</v>
+        <v>385107</v>
       </c>
       <c r="R160" t="n">
-        <v>6857831</v>
+        <v>6858161</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18887,45 +18887,53 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367408</v>
+        <v>132367420</v>
       </c>
       <c r="B161" t="n">
-        <v>79919</v>
+        <v>57142</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385062</v>
+        <v>385235</v>
       </c>
       <c r="R161" t="n">
-        <v>6858092</v>
+        <v>6858146</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18984,45 +18992,53 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367465</v>
+        <v>132367414</v>
       </c>
       <c r="B162" t="n">
-        <v>79087</v>
+        <v>57142</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385131</v>
+        <v>385197</v>
       </c>
       <c r="R162" t="n">
-        <v>6858065</v>
+        <v>6858108</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19081,38 +19097,42 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367495</v>
+        <v>132367471</v>
       </c>
       <c r="B163" t="n">
-        <v>106248</v>
+        <v>58086</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>221144</v>
+        <v>205976</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -19120,10 +19140,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>384848</v>
+        <v>385400</v>
       </c>
       <c r="R163" t="n">
-        <v>6858075</v>
+        <v>6857831</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19158,18 +19178,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -19188,42 +19202,38 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367450</v>
+        <v>132367495</v>
       </c>
       <c r="B164" t="n">
-        <v>57951</v>
+        <v>106248</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19231,10 +19241,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385107</v>
+        <v>384848</v>
       </c>
       <c r="R164" t="n">
-        <v>6858161</v>
+        <v>6858075</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19269,12 +19279,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -19293,53 +19309,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367420</v>
+        <v>132367465</v>
       </c>
       <c r="B165" t="n">
-        <v>57142</v>
+        <v>79087</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385235</v>
+        <v>385131</v>
       </c>
       <c r="R165" t="n">
-        <v>6858146</v>
+        <v>6858065</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19398,53 +19406,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367414</v>
+        <v>132367408</v>
       </c>
       <c r="B166" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385197</v>
+        <v>385062</v>
       </c>
       <c r="R166" t="n">
-        <v>6858108</v>
+        <v>6858092</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19818,53 +19818,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367423</v>
+        <v>132367461</v>
       </c>
       <c r="B170" t="n">
-        <v>57142</v>
+        <v>79087</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385263</v>
+        <v>385227</v>
       </c>
       <c r="R170" t="n">
-        <v>6858153</v>
+        <v>6857907</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19923,45 +19915,53 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367461</v>
+        <v>132367423</v>
       </c>
       <c r="B171" t="n">
-        <v>79087</v>
+        <v>57142</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385227</v>
+        <v>385263</v>
       </c>
       <c r="R171" t="n">
-        <v>6857907</v>
+        <v>6858153</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20222,10 +20222,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367457</v>
+        <v>132367409</v>
       </c>
       <c r="B174" t="n">
-        <v>57951</v>
+        <v>79919</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20233,42 +20233,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385184</v>
+        <v>385075</v>
       </c>
       <c r="R174" t="n">
-        <v>6857885</v>
+        <v>6858201</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20327,10 +20319,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>132367409</v>
+        <v>132367457</v>
       </c>
       <c r="B175" t="n">
-        <v>79919</v>
+        <v>57951</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20338,34 +20330,42 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>385075</v>
+        <v>385184</v>
       </c>
       <c r="R175" t="n">
-        <v>6858201</v>
+        <v>6857885</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -14061,10 +14061,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132367435</v>
+        <v>132367451</v>
       </c>
       <c r="B114" t="n">
-        <v>58115</v>
+        <v>57951</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14072,21 +14072,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -14094,7 +14094,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -14104,10 +14104,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>384859</v>
+        <v>385088</v>
       </c>
       <c r="R114" t="n">
-        <v>6858073</v>
+        <v>6858196</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14166,7 +14166,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132367451</v>
+        <v>132367456</v>
       </c>
       <c r="B115" t="n">
         <v>57951</v>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>385088</v>
+        <v>385112</v>
       </c>
       <c r="R115" t="n">
-        <v>6858196</v>
+        <v>6857918</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14271,10 +14271,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132367456</v>
+        <v>132367435</v>
       </c>
       <c r="B116" t="n">
-        <v>57951</v>
+        <v>58115</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14282,21 +14282,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>385112</v>
+        <v>384859</v>
       </c>
       <c r="R116" t="n">
-        <v>6857918</v>
+        <v>6858073</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15931,53 +15931,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367417</v>
+        <v>132367392</v>
       </c>
       <c r="B132" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385203</v>
+        <v>385102</v>
       </c>
       <c r="R132" t="n">
-        <v>6858134</v>
+        <v>6858138</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16010,11 +16002,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16041,7 +16028,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367392</v>
+        <v>132367402</v>
       </c>
       <c r="B133" t="n">
         <v>79948</v>
@@ -16076,10 +16063,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>385102</v>
+        <v>385403</v>
       </c>
       <c r="R133" t="n">
-        <v>6858138</v>
+        <v>6857836</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16138,45 +16125,53 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132367402</v>
+        <v>132367417</v>
       </c>
       <c r="B134" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>385403</v>
+        <v>385203</v>
       </c>
       <c r="R134" t="n">
-        <v>6857836</v>
+        <v>6858134</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16209,6 +16204,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16235,10 +16235,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367404</v>
+        <v>132367474</v>
       </c>
       <c r="B135" t="n">
-        <v>79919</v>
+        <v>79086</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16246,21 +16246,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16270,10 +16270,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385227</v>
+        <v>385318</v>
       </c>
       <c r="R135" t="n">
-        <v>6857907</v>
+        <v>6858113</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16332,10 +16332,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367474</v>
+        <v>132367399</v>
       </c>
       <c r="B136" t="n">
-        <v>79086</v>
+        <v>79948</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16343,21 +16343,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16367,10 +16367,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>385318</v>
+        <v>384873</v>
       </c>
       <c r="R136" t="n">
-        <v>6858113</v>
+        <v>6858080</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16429,10 +16429,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367399</v>
+        <v>132367404</v>
       </c>
       <c r="B137" t="n">
-        <v>79948</v>
+        <v>79919</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16440,21 +16440,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16464,10 +16464,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>384873</v>
+        <v>385227</v>
       </c>
       <c r="R137" t="n">
-        <v>6858080</v>
+        <v>6857907</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17973,10 +17973,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132367405</v>
+        <v>132367398</v>
       </c>
       <c r="B152" t="n">
-        <v>79919</v>
+        <v>79948</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17984,21 +17984,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18008,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>385332</v>
+        <v>384804</v>
       </c>
       <c r="R152" t="n">
-        <v>6858161</v>
+        <v>6858152</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18172,10 +18172,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132367398</v>
+        <v>132367405</v>
       </c>
       <c r="B154" t="n">
-        <v>79948</v>
+        <v>79919</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18183,21 +18183,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18207,10 +18207,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>384804</v>
+        <v>385332</v>
       </c>
       <c r="R154" t="n">
-        <v>6858152</v>
+        <v>6858161</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18269,10 +18269,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367434</v>
+        <v>132367391</v>
       </c>
       <c r="B155" t="n">
-        <v>58115</v>
+        <v>79948</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18280,42 +18280,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385087</v>
+        <v>385129</v>
       </c>
       <c r="R155" t="n">
-        <v>6858055</v>
+        <v>6858060</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18374,10 +18366,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367406</v>
+        <v>132367434</v>
       </c>
       <c r="B156" t="n">
-        <v>79919</v>
+        <v>58115</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18385,26 +18377,31 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -18412,10 +18409,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385318</v>
+        <v>385087</v>
       </c>
       <c r="R156" t="n">
-        <v>6858113</v>
+        <v>6858055</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18456,7 +18453,6 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -18475,45 +18471,53 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367391</v>
+        <v>132367416</v>
       </c>
       <c r="B157" t="n">
-        <v>79948</v>
+        <v>57142</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385129</v>
+        <v>385185</v>
       </c>
       <c r="R157" t="n">
-        <v>6858060</v>
+        <v>6858146</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18572,7 +18576,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367416</v>
+        <v>132367422</v>
       </c>
       <c r="B158" t="n">
         <v>57142</v>
@@ -18615,10 +18619,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385185</v>
+        <v>385246</v>
       </c>
       <c r="R158" t="n">
-        <v>6858146</v>
+        <v>6858162</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18677,42 +18681,37 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367422</v>
+        <v>132367406</v>
       </c>
       <c r="B159" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18720,10 +18719,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385246</v>
+        <v>385318</v>
       </c>
       <c r="R159" t="n">
-        <v>6858162</v>
+        <v>6858113</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18764,6 +18763,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18887,53 +18887,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367420</v>
+        <v>132367465</v>
       </c>
       <c r="B161" t="n">
-        <v>57142</v>
+        <v>79087</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385235</v>
+        <v>385131</v>
       </c>
       <c r="R161" t="n">
-        <v>6858146</v>
+        <v>6858065</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18992,53 +18984,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367414</v>
+        <v>132367408</v>
       </c>
       <c r="B162" t="n">
-        <v>57142</v>
+        <v>79919</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385197</v>
+        <v>385062</v>
       </c>
       <c r="R162" t="n">
-        <v>6858108</v>
+        <v>6858092</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19097,27 +19081,27 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367471</v>
+        <v>132367420</v>
       </c>
       <c r="B163" t="n">
-        <v>58086</v>
+        <v>57142</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>205976</v>
+        <v>100138</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -19130,7 +19114,7 @@
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
@@ -19140,10 +19124,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385400</v>
+        <v>385235</v>
       </c>
       <c r="R163" t="n">
-        <v>6857831</v>
+        <v>6858146</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19202,10 +19186,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367495</v>
+        <v>132367414</v>
       </c>
       <c r="B164" t="n">
-        <v>106248</v>
+        <v>57142</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19213,27 +19197,31 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -19241,10 +19229,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>384848</v>
+        <v>385197</v>
       </c>
       <c r="R164" t="n">
-        <v>6858075</v>
+        <v>6858108</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19279,18 +19267,12 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -19309,10 +19291,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367465</v>
+        <v>132367471</v>
       </c>
       <c r="B165" t="n">
-        <v>79087</v>
+        <v>58086</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19320,34 +19302,42 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>205976</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385131</v>
+        <v>385400</v>
       </c>
       <c r="R165" t="n">
-        <v>6858065</v>
+        <v>6857831</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19406,45 +19396,49 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367408</v>
+        <v>132367495</v>
       </c>
       <c r="B166" t="n">
-        <v>79919</v>
+        <v>106248</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>229821</v>
+        <v>221144</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385062</v>
+        <v>384848</v>
       </c>
       <c r="R166" t="n">
-        <v>6858092</v>
+        <v>6858075</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19479,12 +19473,18 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY183"/>
+  <dimension ref="A1:AY184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4820,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>72984329</v>
+        <v>128789673</v>
       </c>
       <c r="B40" t="n">
-        <v>93191</v>
+        <v>87387</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4831,39 +4831,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vålåberget S om, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>384835</v>
+        <v>385025</v>
       </c>
       <c r="R40" t="n">
-        <v>6858075</v>
+        <v>6858043</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4887,12 +4894,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4901,26 +4918,25 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens, Helena Björnström</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>72984417</v>
+        <v>72984329</v>
       </c>
       <c r="B41" t="n">
         <v>93191</v>
@@ -4948,16 +4964,8 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4965,10 +4973,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385012</v>
+        <v>384835</v>
       </c>
       <c r="R41" t="n">
-        <v>6858098</v>
+        <v>6858075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5021,14 +5029,14 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens, Helena Björnström, Mikael Gudrunsson, Uno Skog, Elin Götmark</t>
+          <t>Bo karlstens, Helena Björnström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>73263352</v>
+        <v>72984417</v>
       </c>
       <c r="B42" t="n">
         <v>93191</v>
@@ -5056,20 +5064,30 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Vålåberget S om, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>384838</v>
+        <v>385012</v>
       </c>
       <c r="R42" t="n">
-        <v>6858081</v>
+        <v>6858098</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5101,36 +5119,32 @@
           <t>2018-09-02</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>SMF:s kurs om vedsvampar i tallskog</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Uno Skog, Elin Götmark, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
+          <t>Bo karlstens, Helena Björnström, Mikael Gudrunsson, Uno Skog, Elin Götmark</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119546965</v>
+        <v>73263352</v>
       </c>
       <c r="B43" t="n">
         <v>93191</v>
@@ -5158,29 +5172,20 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vålåbergets naturreservat, S om, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>384713</v>
+        <v>384838</v>
       </c>
       <c r="R43" t="n">
-        <v>6858172</v>
+        <v>6858081</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5204,22 +5209,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:16</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:16</t>
+          <t>2018-09-02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>SMF:s kurs om vedsvampar i tallskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5234,19 +5234,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog, Elin Götmark, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128790475</v>
+        <v>119546965</v>
       </c>
       <c r="B44" t="n">
         <v>93191</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5286,17 +5286,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Vålåbergets naturreservat, S om, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>384788</v>
+        <v>384713</v>
       </c>
       <c r="R44" t="n">
-        <v>6858122</v>
+        <v>6858172</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5350,22 +5350,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67646212</v>
+        <v>128790475</v>
       </c>
       <c r="B45" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5373,39 +5373,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385038</v>
+        <v>384788</v>
       </c>
       <c r="R45" t="n">
-        <v>6857994</v>
+        <v>6858122</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5429,12 +5436,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,26 +5460,25 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>67646215</v>
+        <v>67646212</v>
       </c>
       <c r="B46" t="n">
         <v>93197</v>
@@ -5499,10 +5515,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385006</v>
+        <v>385038</v>
       </c>
       <c r="R46" t="n">
-        <v>6858034</v>
+        <v>6857994</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5562,7 +5578,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>72984398</v>
+        <v>67646215</v>
       </c>
       <c r="B47" t="n">
         <v>93197</v>
@@ -5590,30 +5606,22 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vålåberget S om, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>384995</v>
+        <v>385006</v>
       </c>
       <c r="R47" t="n">
-        <v>6858095</v>
+        <v>6858034</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5637,12 +5645,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2017-09-22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2017-09-22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5658,19 +5666,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens, Helena Björnström, Mikael Gudrunsson, Uno Skog</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>73016375</v>
+        <v>72984398</v>
       </c>
       <c r="B48" t="n">
         <v>93197</v>
@@ -5700,12 +5708,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -5715,10 +5723,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>384837</v>
+        <v>384995</v>
       </c>
       <c r="R48" t="n">
-        <v>6858155</v>
+        <v>6858095</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5771,14 +5779,14 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens, Helena Björnström, Elin Götmark</t>
+          <t>Bo karlstens, Helena Björnström, Mikael Gudrunsson, Uno Skog</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>73263356</v>
+        <v>73016375</v>
       </c>
       <c r="B49" t="n">
         <v>93197</v>
@@ -5806,20 +5814,30 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Vålåberget S om, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>384821</v>
+        <v>384837</v>
       </c>
       <c r="R49" t="n">
-        <v>6858112</v>
+        <v>6858155</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5851,36 +5869,32 @@
           <t>2018-09-02</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>SMF:s kurs om vedsvampar i tallskog</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Uno Skog, Elin Götmark, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
+          <t>Bo karlstens, Helena Björnström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>73333849</v>
+        <v>73263356</v>
       </c>
       <c r="B50" t="n">
         <v>93197</v>
@@ -5911,17 +5925,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Norr om Häggesundet, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385049</v>
+        <v>384821</v>
       </c>
       <c r="R50" t="n">
-        <v>6857973</v>
+        <v>6858112</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5955,7 +5969,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>avverkningsanmält</t>
+          <t>SMF:s kurs om vedsvampar i tallskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5966,28 +5980,23 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>talldominerad naturskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog, Elin Götmark, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>73333850</v>
+        <v>73333849</v>
       </c>
       <c r="B51" t="n">
         <v>93197</v>
@@ -6022,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385093</v>
+        <v>385049</v>
       </c>
       <c r="R51" t="n">
-        <v>6857983</v>
+        <v>6857973</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6094,7 +6103,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>73333853</v>
+        <v>73333850</v>
       </c>
       <c r="B52" t="n">
         <v>93197</v>
@@ -6129,10 +6138,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385065</v>
+        <v>385093</v>
       </c>
       <c r="R52" t="n">
-        <v>6858054</v>
+        <v>6857983</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6201,7 +6210,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>73333857</v>
+        <v>73333853</v>
       </c>
       <c r="B53" t="n">
         <v>93197</v>
@@ -6236,10 +6245,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385032</v>
+        <v>385065</v>
       </c>
       <c r="R53" t="n">
-        <v>6858158</v>
+        <v>6858054</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6308,7 +6317,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>73333861</v>
+        <v>73333857</v>
       </c>
       <c r="B54" t="n">
         <v>93197</v>
@@ -6343,10 +6352,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>384959</v>
+        <v>385032</v>
       </c>
       <c r="R54" t="n">
-        <v>6858143</v>
+        <v>6858158</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6415,7 +6424,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>73333867</v>
+        <v>73333861</v>
       </c>
       <c r="B55" t="n">
         <v>93197</v>
@@ -6450,10 +6459,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>384851</v>
+        <v>384959</v>
       </c>
       <c r="R55" t="n">
-        <v>6858168</v>
+        <v>6858143</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6522,7 +6531,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119509708</v>
+        <v>73333867</v>
       </c>
       <c r="B56" t="n">
         <v>93197</v>
@@ -6550,26 +6559,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Norr om Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385004</v>
+        <v>384851</v>
       </c>
       <c r="R56" t="n">
-        <v>6858064</v>
+        <v>6858168</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6596,22 +6596,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>18:18</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>18:18</t>
+          <t>2018-09-02</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>avverkningsanmält</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6622,23 +6617,28 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>talldominerad naturskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119544876</v>
+        <v>119509708</v>
       </c>
       <c r="B57" t="n">
         <v>93197</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6678,14 +6678,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vålåbergets naturreservat, S om, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>384736</v>
+        <v>385004</v>
       </c>
       <c r="R57" t="n">
-        <v>6858206</v>
+        <v>6858064</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,22 +6712,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6742,19 +6742,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119546808</v>
+        <v>119544876</v>
       </c>
       <c r="B58" t="n">
         <v>93197</v>
@@ -6782,17 +6782,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vålåbergets naturreservat, S om, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>384702</v>
+        <v>384736</v>
       </c>
       <c r="R58" t="n">
-        <v>6858179</v>
+        <v>6858206</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6824,7 +6833,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6834,7 +6843,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6861,7 +6870,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119547231</v>
+        <v>119546808</v>
       </c>
       <c r="B59" t="n">
         <v>93197</v>
@@ -6889,26 +6898,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vålåbergets naturreservat, S om, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>384740</v>
+        <v>384702</v>
       </c>
       <c r="R59" t="n">
-        <v>6858133</v>
+        <v>6858179</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6977,7 +6977,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128789354</v>
+        <v>119547231</v>
       </c>
       <c r="B60" t="n">
         <v>93197</v>
@@ -7005,20 +7005,29 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Vålåbergets naturreservat, S om, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>384816</v>
+        <v>384740</v>
       </c>
       <c r="R60" t="n">
-        <v>6858131</v>
+        <v>6858133</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7042,22 +7051,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7072,19 +7081,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128790071</v>
+        <v>128789354</v>
       </c>
       <c r="B61" t="n">
         <v>93197</v>
@@ -7119,10 +7128,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>384986</v>
+        <v>384816</v>
       </c>
       <c r="R61" t="n">
-        <v>6858179</v>
+        <v>6858131</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7154,7 +7163,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7164,7 +7173,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7191,7 +7200,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128790316</v>
+        <v>128790071</v>
       </c>
       <c r="B62" t="n">
         <v>93197</v>
@@ -7226,10 +7235,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>384807</v>
+        <v>384986</v>
       </c>
       <c r="R62" t="n">
-        <v>6858190</v>
+        <v>6858179</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7261,7 +7270,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7271,7 +7280,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7298,57 +7307,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1334648</v>
+        <v>128790316</v>
       </c>
       <c r="B63" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vålåberget mellan vägen och kraftledningen, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>384957</v>
+        <v>384807</v>
       </c>
       <c r="R63" t="n">
-        <v>6858134</v>
+        <v>6858190</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7372,12 +7372,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2008-09-30</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2008-09-30</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7388,28 +7398,23 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>tallåga i diabasblockrik tallskog</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>67646146</v>
+        <v>1334648</v>
       </c>
       <c r="B64" t="n">
         <v>93201</v>
@@ -7439,28 +7444,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>Vålåberget mellan vägen och kraftledningen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385059</v>
+        <v>384957</v>
       </c>
       <c r="R64" t="n">
-        <v>6858183</v>
+        <v>6858134</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7484,17 +7488,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
+          <t>2008-09-30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Under brandstubbe</t>
+          <t>2008-09-30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7503,26 +7502,30 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>tallåga i diabasblockrik tallskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>72984365</v>
+        <v>67646146</v>
       </c>
       <c r="B65" t="n">
         <v>93201</v>
@@ -7550,22 +7553,30 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vålåberget S om, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>384914</v>
+        <v>385059</v>
       </c>
       <c r="R65" t="n">
-        <v>6858140</v>
+        <v>6858183</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7589,17 +7600,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2017-09-22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2017-09-22</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Under tallåga</t>
+          <t>Under brandstubbe</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7615,56 +7626,48 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens, Helena Björnström, Mikael Gudrunsson, Elin Götmark</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>73016179</v>
+        <v>72984365</v>
       </c>
       <c r="B66" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7672,10 +7675,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385010</v>
+        <v>384914</v>
       </c>
       <c r="R66" t="n">
-        <v>6858057</v>
+        <v>6858140</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7710,6 +7713,11 @@
           <t>2018-09-02</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Under tallåga</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7728,14 +7736,14 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bo karlstens, Helena Björnström</t>
+          <t>Bo karlstens, Helena Björnström, Mikael Gudrunsson, Elin Götmark</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>73016285</v>
+        <v>73016179</v>
       </c>
       <c r="B67" t="n">
         <v>93209</v>
@@ -7765,7 +7773,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7780,7 +7788,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385036</v>
+        <v>385010</v>
       </c>
       <c r="R67" t="n">
         <v>6858057</v>
@@ -7836,14 +7844,14 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens, Helena Björnström, Elin Götmark</t>
+          <t>Bo karlstens, Helena Björnström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>73263349</v>
+        <v>73016285</v>
       </c>
       <c r="B68" t="n">
         <v>93209</v>
@@ -7871,20 +7879,30 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Vålåberget S om, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>384848</v>
+        <v>385036</v>
       </c>
       <c r="R68" t="n">
-        <v>6858142</v>
+        <v>6858057</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7916,36 +7934,32 @@
           <t>2018-09-02</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>SMF:s kurs om vedsvampar i tallskog</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Uno Skog, Elin Götmark, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
+          <t>Bo karlstens, Helena Björnström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>73263355</v>
+        <v>73263349</v>
       </c>
       <c r="B69" t="n">
         <v>93209</v>
@@ -7980,10 +7994,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>384821</v>
+        <v>384848</v>
       </c>
       <c r="R69" t="n">
-        <v>6858112</v>
+        <v>6858142</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8047,7 +8061,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>73333848</v>
+        <v>73263355</v>
       </c>
       <c r="B70" t="n">
         <v>93209</v>
@@ -8078,17 +8092,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norr om Häggesundet, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385048</v>
+        <v>384821</v>
       </c>
       <c r="R70" t="n">
-        <v>6857973</v>
+        <v>6858112</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8122,7 +8136,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>avverkningsanmält</t>
+          <t>SMF:s kurs om vedsvampar i tallskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8133,28 +8147,23 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>talldominerad naturskog</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog, Elin Götmark, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119509690</v>
+        <v>73333848</v>
       </c>
       <c r="B71" t="n">
         <v>93209</v>
@@ -8182,26 +8191,17 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Norr om Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>384891</v>
+        <v>385048</v>
       </c>
       <c r="R71" t="n">
-        <v>6858140</v>
+        <v>6857973</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8228,22 +8228,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2018-09-02</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>avverkningsanmält</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8254,23 +8249,28 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>talldominerad naturskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119509957</v>
+        <v>119509690</v>
       </c>
       <c r="B72" t="n">
         <v>93209</v>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8314,10 +8314,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>385075</v>
+        <v>384891</v>
       </c>
       <c r="R72" t="n">
-        <v>6858088</v>
+        <v>6858140</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8386,7 +8386,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119547126</v>
+        <v>119509957</v>
       </c>
       <c r="B73" t="n">
         <v>93209</v>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8426,14 +8426,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vålåbergets naturreservat, S om, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>384713</v>
+        <v>385075</v>
       </c>
       <c r="R73" t="n">
-        <v>6858172</v>
+        <v>6858088</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8460,22 +8460,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8490,19 +8490,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128789742</v>
+        <v>119547126</v>
       </c>
       <c r="B74" t="n">
         <v>93209</v>
@@ -8530,20 +8530,29 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>Vålåbergets naturreservat, S om, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>385025</v>
+        <v>384713</v>
       </c>
       <c r="R74" t="n">
-        <v>6858043</v>
+        <v>6858172</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8567,22 +8576,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8597,22 +8606,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119553050</v>
+        <v>128789742</v>
       </c>
       <c r="B75" t="n">
-        <v>92841</v>
+        <v>93209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8620,46 +8629,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vålåbergets naturreservat, S om, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>384738</v>
+        <v>385025</v>
       </c>
       <c r="R75" t="n">
-        <v>6858168</v>
+        <v>6858043</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8683,22 +8683,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8713,57 +8713,66 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>73333864</v>
+        <v>119553050</v>
       </c>
       <c r="B76" t="n">
-        <v>91872</v>
+        <v>92841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>4745</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norr om Häggesundet, Dlr</t>
+          <t>Vålåbergets naturreservat, S om, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>384859</v>
+        <v>384738</v>
       </c>
       <c r="R76" t="n">
-        <v>6858180</v>
+        <v>6858168</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8790,17 +8799,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>avverkningsanmält</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,74 +8825,64 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>talldominerad naturskog</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>gammal tallåga</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128789115</v>
+        <v>73333864</v>
       </c>
       <c r="B77" t="n">
-        <v>93223</v>
+        <v>91872</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Norr om Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>384719</v>
+        <v>384859</v>
       </c>
       <c r="R77" t="n">
-        <v>6858219</v>
+        <v>6858180</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8902,22 +8906,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2018-09-02</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>avverkningsanmält</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8928,26 +8927,36 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>talldominerad naturskog</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>gammal tallåga</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>73333847</v>
+        <v>128789115</v>
       </c>
       <c r="B78" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8955,37 +8964,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norr om Häggesundet, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>384874</v>
+        <v>384719</v>
       </c>
       <c r="R78" t="n">
-        <v>6858053</v>
+        <v>6858219</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9009,17 +9018,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>avverkningsanmält</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9030,53 +9044,48 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>talldominerad naturskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>73333866</v>
+        <v>73333847</v>
       </c>
       <c r="B79" t="n">
-        <v>93181</v>
+        <v>93235</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9086,10 +9095,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>384854</v>
+        <v>384874</v>
       </c>
       <c r="R79" t="n">
-        <v>6858175</v>
+        <v>6858053</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9141,11 +9150,6 @@
       <c r="AI79" t="inlineStr">
         <is>
           <t>talldominerad naturskog</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>under gammal tallåga</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9163,7 +9167,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119509835</v>
+        <v>73333866</v>
       </c>
       <c r="B80" t="n">
         <v>93181</v>
@@ -9194,14 +9198,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Norr om Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>385015</v>
+        <v>384854</v>
       </c>
       <c r="R80" t="n">
-        <v>6858040</v>
+        <v>6858175</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9228,27 +9232,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>18:18</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>18:18</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Under grov kolad tallåga</t>
+          <t>avverkningsanmält</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9259,26 +9253,36 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>talldominerad naturskog</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>under gammal tallåga</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>67646111</v>
+        <v>119509835</v>
       </c>
       <c r="B81" t="n">
-        <v>90691</v>
+        <v>93181</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9286,47 +9290,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>385115</v>
+        <v>385015</v>
       </c>
       <c r="R81" t="n">
-        <v>6858075</v>
+        <v>6858040</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9350,17 +9344,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>2 fruktkroppar</t>
+          <t>Under grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9369,26 +9373,25 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>68235644</v>
+        <v>67646111</v>
       </c>
       <c r="B82" t="n">
         <v>90691</v>
@@ -9418,22 +9421,28 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>V-sidan vägen m emot Vålåberget, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>384806</v>
+        <v>385115</v>
       </c>
       <c r="R82" t="n">
-        <v>6858009</v>
+        <v>6858075</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9457,12 +9466,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
+          <t>2017-09-22</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
+          <t>2017-09-22</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9475,27 +9489,22 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Janols</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Janols, Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119509925</v>
+        <v>68235644</v>
       </c>
       <c r="B83" t="n">
         <v>90691</v>
@@ -9525,24 +9534,19 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>V-sidan vägen m emot Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>385061</v>
+        <v>384806</v>
       </c>
       <c r="R83" t="n">
-        <v>6858073</v>
+        <v>6858009</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9569,22 +9573,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9593,66 +9587,81 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Anders Janols</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Anders Janols, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>73263348</v>
+        <v>119509925</v>
       </c>
       <c r="B84" t="n">
-        <v>78730</v>
+        <v>90691</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6437</v>
+        <v>6276</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>384919</v>
+        <v>385061</v>
       </c>
       <c r="R84" t="n">
-        <v>6858148</v>
+        <v>6858073</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9676,17 +9685,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>SMF:s kurs om vedsvampar i tallskog</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9706,14 +9720,14 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Uno Skog, Elin Götmark, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>73333859</v>
+        <v>73263348</v>
       </c>
       <c r="B85" t="n">
         <v>78730</v>
@@ -9744,17 +9758,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norr om Häggesundet, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>385039</v>
+        <v>384919</v>
       </c>
       <c r="R85" t="n">
-        <v>6858161</v>
+        <v>6858148</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9788,7 +9802,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>avverkningsanmält</t>
+          <t>SMF:s kurs om vedsvampar i tallskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9799,36 +9813,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>talldominerad naturskog</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>högstubbe tall</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog, Elin Götmark, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132367475</v>
+        <v>73333859</v>
       </c>
       <c r="B86" t="n">
-        <v>79130</v>
+        <v>78730</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9836,34 +9840,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>Norr om Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>384814</v>
+        <v>385039</v>
       </c>
       <c r="R86" t="n">
-        <v>6858214</v>
+        <v>6858161</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9890,12 +9894,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2018-09-02</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>avverkningsanmält</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9906,26 +9915,36 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>talldominerad naturskog</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>högstubbe tall</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>73333869</v>
+        <v>132367475</v>
       </c>
       <c r="B87" t="n">
-        <v>79946</v>
+        <v>79130</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9933,34 +9952,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norr om Häggesundet, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>384844</v>
+        <v>384814</v>
       </c>
       <c r="R87" t="n">
-        <v>6858153</v>
+        <v>6858214</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9987,17 +10006,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>avverkningsanmält</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10008,33 +10022,23 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>talldominerad naturskog</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>silverstubbe</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>73333870</v>
+        <v>73333869</v>
       </c>
       <c r="B88" t="n">
         <v>79946</v>
@@ -10069,10 +10073,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>384793</v>
+        <v>384844</v>
       </c>
       <c r="R88" t="n">
-        <v>6858123</v>
+        <v>6858153</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10146,10 +10150,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132367389</v>
+        <v>73333870</v>
       </c>
       <c r="B89" t="n">
-        <v>79992</v>
+        <v>79946</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10177,14 +10181,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>Norr om Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>385195</v>
+        <v>384793</v>
       </c>
       <c r="R89" t="n">
-        <v>6858154</v>
+        <v>6858123</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10211,12 +10215,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2018-09-02</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>avverkningsanmält</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10227,23 +10236,33 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>talldominerad naturskog</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>silverstubbe</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132367391</v>
+        <v>132367389</v>
       </c>
       <c r="B90" t="n">
         <v>79992</v>
@@ -10278,10 +10297,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>385129</v>
+        <v>385195</v>
       </c>
       <c r="R90" t="n">
-        <v>6858060</v>
+        <v>6858154</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10340,7 +10359,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132367392</v>
+        <v>132367391</v>
       </c>
       <c r="B91" t="n">
         <v>79992</v>
@@ -10375,10 +10394,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>385102</v>
+        <v>385129</v>
       </c>
       <c r="R91" t="n">
-        <v>6858138</v>
+        <v>6858060</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10437,7 +10456,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132367393</v>
+        <v>132367392</v>
       </c>
       <c r="B92" t="n">
         <v>79992</v>
@@ -10472,10 +10491,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>385118</v>
+        <v>385102</v>
       </c>
       <c r="R92" t="n">
-        <v>6858178</v>
+        <v>6858138</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10534,7 +10553,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132367394</v>
+        <v>132367393</v>
       </c>
       <c r="B93" t="n">
         <v>79992</v>
@@ -10569,10 +10588,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>384969</v>
+        <v>385118</v>
       </c>
       <c r="R93" t="n">
-        <v>6858130</v>
+        <v>6858178</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10631,7 +10650,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132367395</v>
+        <v>132367394</v>
       </c>
       <c r="B94" t="n">
         <v>79992</v>
@@ -10666,10 +10685,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>384944</v>
+        <v>384969</v>
       </c>
       <c r="R94" t="n">
-        <v>6858169</v>
+        <v>6858130</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10728,7 +10747,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132367396</v>
+        <v>132367395</v>
       </c>
       <c r="B95" t="n">
         <v>79992</v>
@@ -10763,10 +10782,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>384939</v>
+        <v>384944</v>
       </c>
       <c r="R95" t="n">
-        <v>6858249</v>
+        <v>6858169</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10825,7 +10844,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132367398</v>
+        <v>132367396</v>
       </c>
       <c r="B96" t="n">
         <v>79992</v>
@@ -10860,10 +10879,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>384804</v>
+        <v>384939</v>
       </c>
       <c r="R96" t="n">
-        <v>6858152</v>
+        <v>6858249</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10922,7 +10941,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132367399</v>
+        <v>132367398</v>
       </c>
       <c r="B97" t="n">
         <v>79992</v>
@@ -10957,10 +10976,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>384873</v>
+        <v>384804</v>
       </c>
       <c r="R97" t="n">
-        <v>6858080</v>
+        <v>6858152</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11019,7 +11038,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132367401</v>
+        <v>132367399</v>
       </c>
       <c r="B98" t="n">
         <v>79992</v>
@@ -11054,10 +11073,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>384992</v>
+        <v>384873</v>
       </c>
       <c r="R98" t="n">
-        <v>6858018</v>
+        <v>6858080</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11116,10 +11135,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>73333860</v>
+        <v>132367401</v>
       </c>
       <c r="B99" t="n">
-        <v>78334</v>
+        <v>79992</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11127,34 +11146,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norr om Häggesundet, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>385039</v>
+        <v>384992</v>
       </c>
       <c r="R99" t="n">
-        <v>6858161</v>
+        <v>6858018</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11181,17 +11200,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>avverkningsanmält</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11202,33 +11216,23 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>talldominerad naturskog</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>högstubbe tall</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>73767948</v>
+        <v>73333860</v>
       </c>
       <c r="B100" t="n">
         <v>78334</v>
@@ -11259,14 +11263,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>N, Häggesundet, Idre, Dlr</t>
+          <t>Norr om Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>385037</v>
+        <v>385039</v>
       </c>
       <c r="R100" t="n">
-        <v>6858108</v>
+        <v>6858161</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11301,6 +11305,11 @@
           <t>2018-09-02</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>avverkningsanmält</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11309,26 +11318,36 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>talldominerad naturskog</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>högstubbe tall</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132367501</v>
+        <v>73767948</v>
       </c>
       <c r="B101" t="n">
-        <v>78377</v>
+        <v>78334</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11356,14 +11375,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>N, Häggesundet, Idre, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>385084</v>
+        <v>385037</v>
       </c>
       <c r="R101" t="n">
-        <v>6858195</v>
+        <v>6858108</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11390,12 +11409,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11404,97 +11423,63 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Öppen mark med tall</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132367446</v>
+        <v>132367501</v>
       </c>
       <c r="B102" t="n">
-        <v>57972</v>
+        <v>78377</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>385178</v>
+        <v>385084</v>
       </c>
       <c r="R102" t="n">
-        <v>6858121</v>
+        <v>6858195</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11535,8 +11520,34 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Öppen mark med tall</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11553,7 +11564,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132367449</v>
+        <v>132367446</v>
       </c>
       <c r="B103" t="n">
         <v>57972</v>
@@ -11586,7 +11597,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11596,10 +11607,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>385133</v>
+        <v>385178</v>
       </c>
       <c r="R103" t="n">
-        <v>6858066</v>
+        <v>6858121</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11658,7 +11669,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132367450</v>
+        <v>132367449</v>
       </c>
       <c r="B104" t="n">
         <v>57972</v>
@@ -11691,7 +11702,7 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -11701,10 +11712,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>385107</v>
+        <v>385133</v>
       </c>
       <c r="R104" t="n">
-        <v>6858161</v>
+        <v>6858066</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11763,7 +11774,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132367451</v>
+        <v>132367450</v>
       </c>
       <c r="B105" t="n">
         <v>57972</v>
@@ -11796,7 +11807,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -11806,10 +11817,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>385088</v>
+        <v>385107</v>
       </c>
       <c r="R105" t="n">
-        <v>6858196</v>
+        <v>6858161</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11868,7 +11879,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132367452</v>
+        <v>132367451</v>
       </c>
       <c r="B106" t="n">
         <v>57972</v>
@@ -11901,7 +11912,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -11911,10 +11922,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>384945</v>
+        <v>385088</v>
       </c>
       <c r="R106" t="n">
-        <v>6858165</v>
+        <v>6858196</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11973,7 +11984,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132367453</v>
+        <v>132367452</v>
       </c>
       <c r="B107" t="n">
         <v>57972</v>
@@ -12006,7 +12017,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -12016,10 +12027,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>384934</v>
+        <v>384945</v>
       </c>
       <c r="R107" t="n">
-        <v>6858197</v>
+        <v>6858165</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12078,7 +12089,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132367455</v>
+        <v>132367453</v>
       </c>
       <c r="B108" t="n">
         <v>57972</v>
@@ -12111,7 +12122,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -12121,10 +12132,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>384840</v>
+        <v>384934</v>
       </c>
       <c r="R108" t="n">
-        <v>6858190</v>
+        <v>6858197</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12183,7 +12194,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132367456</v>
+        <v>132367455</v>
       </c>
       <c r="B109" t="n">
         <v>57972</v>
@@ -12216,7 +12227,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -12226,10 +12237,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>385112</v>
+        <v>384840</v>
       </c>
       <c r="R109" t="n">
-        <v>6857918</v>
+        <v>6858190</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12288,7 +12299,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132367457</v>
+        <v>132367456</v>
       </c>
       <c r="B110" t="n">
         <v>57972</v>
@@ -12321,7 +12332,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -12331,10 +12342,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>385184</v>
+        <v>385112</v>
       </c>
       <c r="R110" t="n">
-        <v>6857885</v>
+        <v>6857918</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12393,7 +12404,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132367458</v>
+        <v>132367457</v>
       </c>
       <c r="B111" t="n">
         <v>57972</v>
@@ -12436,10 +12447,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>385095</v>
+        <v>385184</v>
       </c>
       <c r="R111" t="n">
-        <v>6857937</v>
+        <v>6857885</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12498,10 +12509,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132367413</v>
+        <v>132367458</v>
       </c>
       <c r="B112" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12509,21 +12520,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12531,7 +12542,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -12541,10 +12552,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>385181</v>
+        <v>385095</v>
       </c>
       <c r="R112" t="n">
-        <v>6858109</v>
+        <v>6857937</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12603,7 +12614,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132367414</v>
+        <v>132367413</v>
       </c>
       <c r="B113" t="n">
         <v>57162</v>
@@ -12646,10 +12657,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>385197</v>
+        <v>385181</v>
       </c>
       <c r="R113" t="n">
-        <v>6858108</v>
+        <v>6858109</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12708,7 +12719,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132367415</v>
+        <v>132367414</v>
       </c>
       <c r="B114" t="n">
         <v>57162</v>
@@ -12751,10 +12762,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>385185</v>
+        <v>385197</v>
       </c>
       <c r="R114" t="n">
-        <v>6858127</v>
+        <v>6858108</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12787,11 +12798,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12818,7 +12824,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132367416</v>
+        <v>132367415</v>
       </c>
       <c r="B115" t="n">
         <v>57162</v>
@@ -12864,7 +12870,7 @@
         <v>385185</v>
       </c>
       <c r="R115" t="n">
-        <v>6858146</v>
+        <v>6858127</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12897,6 +12903,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt med färsk spillning inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12923,7 +12934,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132367430</v>
+        <v>132367416</v>
       </c>
       <c r="B116" t="n">
         <v>57162</v>
@@ -12966,10 +12977,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>385158</v>
+        <v>385185</v>
       </c>
       <c r="R116" t="n">
-        <v>6858052</v>
+        <v>6858146</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13028,7 +13039,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132367431</v>
+        <v>132367430</v>
       </c>
       <c r="B117" t="n">
         <v>57162</v>
@@ -13071,10 +13082,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>384950</v>
+        <v>385158</v>
       </c>
       <c r="R117" t="n">
-        <v>6858169</v>
+        <v>6858052</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13133,7 +13144,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132367432</v>
+        <v>132367431</v>
       </c>
       <c r="B118" t="n">
         <v>57162</v>
@@ -13176,10 +13187,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>385185</v>
+        <v>384950</v>
       </c>
       <c r="R118" t="n">
-        <v>6858160</v>
+        <v>6858169</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13238,7 +13249,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132367433</v>
+        <v>132367432</v>
       </c>
       <c r="B119" t="n">
         <v>57162</v>
@@ -13281,10 +13292,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>384844</v>
+        <v>385185</v>
       </c>
       <c r="R119" t="n">
-        <v>6858114</v>
+        <v>6858160</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13343,32 +13354,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132367434</v>
+        <v>132367433</v>
       </c>
       <c r="B120" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13376,7 +13387,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -13386,10 +13397,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>385087</v>
+        <v>384844</v>
       </c>
       <c r="R120" t="n">
-        <v>6858055</v>
+        <v>6858114</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13448,7 +13459,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132367435</v>
+        <v>132367434</v>
       </c>
       <c r="B121" t="n">
         <v>58136</v>
@@ -13491,10 +13502,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>384859</v>
+        <v>385087</v>
       </c>
       <c r="R121" t="n">
-        <v>6858073</v>
+        <v>6858055</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13553,41 +13564,40 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132367468</v>
+        <v>132367435</v>
       </c>
       <c r="B122" t="n">
-        <v>8460</v>
+        <v>58136</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -13597,10 +13607,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>384943</v>
+        <v>384859</v>
       </c>
       <c r="R122" t="n">
-        <v>6858164</v>
+        <v>6858073</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13641,7 +13651,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13660,7 +13669,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132367469</v>
+        <v>132367468</v>
       </c>
       <c r="B123" t="n">
         <v>8460</v>
@@ -13694,7 +13703,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -13704,10 +13713,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>384988</v>
+        <v>384943</v>
       </c>
       <c r="R123" t="n">
-        <v>6858227</v>
+        <v>6858164</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13767,7 +13776,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132367470</v>
+        <v>132367469</v>
       </c>
       <c r="B124" t="n">
         <v>8460</v>
@@ -13811,10 +13820,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>384910</v>
+        <v>384988</v>
       </c>
       <c r="R124" t="n">
-        <v>6858203</v>
+        <v>6858227</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13874,40 +13883,41 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132367388</v>
+        <v>132367470</v>
       </c>
       <c r="B125" t="n">
-        <v>56706</v>
+        <v>8460</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>206046</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -13917,10 +13927,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>385176</v>
+        <v>384910</v>
       </c>
       <c r="R125" t="n">
-        <v>6857892</v>
+        <v>6858203</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13961,6 +13971,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13979,49 +13990,53 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>72984327</v>
+        <v>132367388</v>
       </c>
       <c r="B126" t="n">
-        <v>106244</v>
+        <v>56706</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221144</v>
+        <v>206046</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Vålåberget S om, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>384835</v>
+        <v>385176</v>
       </c>
       <c r="R126" t="n">
-        <v>6858075</v>
+        <v>6857892</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14048,12 +14063,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14062,26 +14077,25 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Bo karlstens, Helena Björnström</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>73263351</v>
+        <v>72984327</v>
       </c>
       <c r="B127" t="n">
         <v>106244</v>
@@ -14110,19 +14124,23 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Vålåberget S om, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>384838</v>
+        <v>384835</v>
       </c>
       <c r="R127" t="n">
-        <v>6858081</v>
+        <v>6858075</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14154,39 +14172,35 @@
           <t>2018-09-02</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>SMF:s kurs om vedsvampar i tallskog</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Uno Skog, Elin Götmark, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
+          <t>Bo karlstens, Helena Björnström</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132367495</v>
+        <v>73263351</v>
       </c>
       <c r="B128" t="n">
-        <v>106324</v>
+        <v>106244</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14212,23 +14226,19 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>384848</v>
+        <v>384838</v>
       </c>
       <c r="R128" t="n">
-        <v>6858075</v>
+        <v>6858081</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14252,17 +14262,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Flertalet plantor inom en radie av 1 meter</t>
+          <t>SMF:s kurs om vedsvampar i tallskog</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14271,29 +14281,28 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Uno Skog, Elin Götmark, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132367459</v>
+        <v>132367495</v>
       </c>
       <c r="B129" t="n">
-        <v>98060</v>
+        <v>106324</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14301,34 +14310,38 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>384655</v>
+        <v>384848</v>
       </c>
       <c r="R129" t="n">
-        <v>6858187</v>
+        <v>6858075</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14365,7 +14378,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Underjordisk bäck hörs porlande.</t>
+          <t>Flertalet plantor inom en radie av 1 meter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14374,6 +14387,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14392,45 +14406,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121738118</v>
+        <v>132367459</v>
       </c>
       <c r="B130" t="n">
-        <v>79085</v>
+        <v>98060</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>385195</v>
+        <v>384655</v>
       </c>
       <c r="R130" t="n">
-        <v>6858148</v>
+        <v>6858187</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14457,12 +14471,17 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Underjordisk bäck hörs porlande.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14477,22 +14496,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132367462</v>
+        <v>121738118</v>
       </c>
       <c r="B131" t="n">
-        <v>79131</v>
+        <v>79085</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14520,14 +14539,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
         <v>385195</v>
       </c>
       <c r="R131" t="n">
-        <v>6858154</v>
+        <v>6858148</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14554,12 +14573,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14574,19 +14593,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132367465</v>
+        <v>132367462</v>
       </c>
       <c r="B132" t="n">
         <v>79131</v>
@@ -14621,10 +14640,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>385131</v>
+        <v>385195</v>
       </c>
       <c r="R132" t="n">
-        <v>6858065</v>
+        <v>6858154</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14683,7 +14702,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132367466</v>
+        <v>132367465</v>
       </c>
       <c r="B133" t="n">
         <v>79131</v>
@@ -14718,10 +14737,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>384749</v>
+        <v>385131</v>
       </c>
       <c r="R133" t="n">
-        <v>6858223</v>
+        <v>6858065</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14780,7 +14799,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132367467</v>
+        <v>132367466</v>
       </c>
       <c r="B134" t="n">
         <v>79131</v>
@@ -14815,10 +14834,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>384838</v>
+        <v>384749</v>
       </c>
       <c r="R134" t="n">
-        <v>6858114</v>
+        <v>6858223</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14877,10 +14896,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132367407</v>
+        <v>132367467</v>
       </c>
       <c r="B135" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14888,21 +14907,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14912,10 +14931,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>385124</v>
+        <v>384838</v>
       </c>
       <c r="R135" t="n">
-        <v>6858064</v>
+        <v>6858114</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14974,7 +14993,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132367408</v>
+        <v>132367407</v>
       </c>
       <c r="B136" t="n">
         <v>79963</v>
@@ -15009,10 +15028,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>385062</v>
+        <v>385124</v>
       </c>
       <c r="R136" t="n">
-        <v>6858092</v>
+        <v>6858064</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15071,7 +15090,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132367409</v>
+        <v>132367408</v>
       </c>
       <c r="B137" t="n">
         <v>79963</v>
@@ -15106,10 +15125,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>385075</v>
+        <v>385062</v>
       </c>
       <c r="R137" t="n">
-        <v>6858201</v>
+        <v>6858092</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15168,7 +15187,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132367410</v>
+        <v>132367409</v>
       </c>
       <c r="B138" t="n">
         <v>79963</v>
@@ -15203,10 +15222,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>384959</v>
+        <v>385075</v>
       </c>
       <c r="R138" t="n">
-        <v>6858242</v>
+        <v>6858201</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15265,58 +15284,48 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>67646143</v>
+        <v>132367410</v>
       </c>
       <c r="B139" t="n">
-        <v>93228</v>
+        <v>79963</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>232140</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>385059</v>
+        <v>384959</v>
       </c>
       <c r="R139" t="n">
-        <v>6858183</v>
+        <v>6858242</v>
       </c>
       <c r="S139" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15340,17 +15349,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Under brandstubbe som vält. Ca 7 st fruktkroppar. Tillsammans med smalfotad.</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15359,67 +15363,76 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>68235650</v>
+        <v>67646143</v>
       </c>
       <c r="B140" t="n">
-        <v>91402</v>
+        <v>93228</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>256703</v>
+        <v>232140</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Vålåbeget  NO om kraftledn, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>384930</v>
+        <v>385059</v>
       </c>
       <c r="R140" t="n">
-        <v>6858323</v>
+        <v>6858183</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15443,12 +15456,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
+          <t>2017-09-22</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
+          <t>2017-09-22</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Under brandstubbe som vält. Ca 7 st fruktkroppar. Tillsammans med smalfotad.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15461,27 +15479,22 @@
       <c r="AG140" t="b">
         <v>0</v>
       </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anders Janols</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anders Janols, Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>73263350</v>
+        <v>68235650</v>
       </c>
       <c r="B141" t="n">
         <v>91402</v>
@@ -15512,17 +15525,17 @@
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Vålåberget, Dlr</t>
+          <t>Vålåbeget  NO om kraftledn, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>384844</v>
+        <v>384930</v>
       </c>
       <c r="R141" t="n">
-        <v>6858095</v>
+        <v>6858323</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15546,17 +15559,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>SMF:s kurs om vedsvampar i tallskog</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15565,25 +15573,31 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Anders Janols</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Uno Skog, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
+          <t>Anders Janols, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>73263361</v>
+        <v>73263350</v>
       </c>
       <c r="B142" t="n">
         <v>91402</v>
@@ -15618,10 +15632,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>384779</v>
+        <v>384844</v>
       </c>
       <c r="R142" t="n">
-        <v>6858138</v>
+        <v>6858095</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15685,7 +15699,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119509950</v>
+        <v>73263361</v>
       </c>
       <c r="B143" t="n">
         <v>91402</v>
@@ -15713,29 +15727,20 @@
           <t>R.H.Petersen</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>385075</v>
+        <v>384779</v>
       </c>
       <c r="R143" t="n">
-        <v>6858088</v>
+        <v>6858138</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15759,22 +15764,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>18:32</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>18:32</t>
+          <t>2018-09-02</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>SMF:s kurs om vedsvampar i tallskog</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15794,14 +15794,14 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Sofia Lundell, Andreas Öster, Olli Manninen, Helena Björnström, Andreas Bernhold, Freja Lina Bergquist, Bo karlstens, Linnea Helmersson, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119510014</v>
+        <v>119509950</v>
       </c>
       <c r="B144" t="n">
         <v>91402</v>
@@ -15845,10 +15845,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>384976</v>
+        <v>385075</v>
       </c>
       <c r="R144" t="n">
-        <v>6858126</v>
+        <v>6858088</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15917,10 +15917,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119509537</v>
+        <v>119510014</v>
       </c>
       <c r="B145" t="n">
-        <v>91431</v>
+        <v>91402</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15928,16 +15928,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6039941</v>
+        <v>256703</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15955,18 +15955,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>384740</v>
+        <v>384976</v>
       </c>
       <c r="R145" t="n">
-        <v>6858226</v>
+        <v>6858126</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15998,7 +15996,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16008,12 +16006,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ingen tydlig doft. Väldigt glatt i köttet. Diabas i marken. Tallskog.</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16022,7 +16015,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -16041,7 +16033,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119546030</v>
+        <v>119509537</v>
       </c>
       <c r="B146" t="n">
         <v>91431</v>
@@ -16083,14 +16075,14 @@
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Vålåbergets naturreservat, S om, Dlr</t>
+          <t>Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>384745</v>
+        <v>384740</v>
       </c>
       <c r="R146" t="n">
-        <v>6858231</v>
+        <v>6858226</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16117,22 +16109,27 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ingen tydlig doft. Väldigt glatt i köttet. Diabas i marken. Tallskog.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16148,61 +16145,68 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>68235646</v>
+        <v>119546030</v>
       </c>
       <c r="B147" t="n">
-        <v>87195</v>
+        <v>91431</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>426</v>
+        <v>6039941</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>O-sidan vägen m emot Vålåberget, Dlr</t>
+          <t>Vålåbergets naturreservat, S om, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>385222</v>
+        <v>384745</v>
       </c>
       <c r="R147" t="n">
-        <v>6857857</v>
+        <v>6858231</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16229,12 +16233,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16243,71 +16257,68 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Anders Janols</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Anders Janols, Janolof Hermansson</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132367411</v>
+        <v>68235646</v>
       </c>
       <c r="B148" t="n">
-        <v>79468</v>
+        <v>87195</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>967</v>
+        <v>426</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>O-sidan vägen m emot Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>385334</v>
+        <v>385222</v>
       </c>
       <c r="R148" t="n">
-        <v>6858171</v>
+        <v>6857857</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16334,12 +16345,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16348,29 +16359,33 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anders Janols</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anders Janols, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>67646073</v>
+        <v>132367411</v>
       </c>
       <c r="B149" t="n">
-        <v>91962</v>
+        <v>79468</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16378,47 +16393,40 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2079</v>
+        <v>967</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>385254</v>
+        <v>385334</v>
       </c>
       <c r="R149" t="n">
-        <v>6857874</v>
+        <v>6858171</v>
       </c>
       <c r="S149" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16442,12 +16450,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16463,22 +16471,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>67646050</v>
+        <v>67646073</v>
       </c>
       <c r="B150" t="n">
-        <v>93197</v>
+        <v>91962</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16486,21 +16494,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -16510,7 +16518,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -16520,13 +16528,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>385218</v>
+        <v>385254</v>
       </c>
       <c r="R150" t="n">
-        <v>6858097</v>
+        <v>6857874</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16583,7 +16591,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>67646079</v>
+        <v>67646050</v>
       </c>
       <c r="B151" t="n">
         <v>93197</v>
@@ -16628,13 +16636,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>385254</v>
+        <v>385218</v>
       </c>
       <c r="R151" t="n">
-        <v>6857874</v>
+        <v>6858097</v>
       </c>
       <c r="S151" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16691,10 +16699,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>67646048</v>
+        <v>67646079</v>
       </c>
       <c r="B152" t="n">
-        <v>90522</v>
+        <v>93197</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16702,21 +16710,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -16736,13 +16744,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>385218</v>
+        <v>385254</v>
       </c>
       <c r="R152" t="n">
-        <v>6858097</v>
+        <v>6857874</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16772,11 +16780,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2017-09-22</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16804,10 +16807,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>68235645</v>
+        <v>67646048</v>
       </c>
       <c r="B153" t="n">
-        <v>93223</v>
+        <v>90522</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16815,41 +16818,47 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5448</v>
+        <v>4962</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>O-sidan vägen m emot Vålåberget, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>385277</v>
+        <v>385218</v>
       </c>
       <c r="R153" t="n">
-        <v>6857893</v>
+        <v>6858097</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16873,12 +16882,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
+          <t>2017-09-22</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
+          <t>2017-09-22</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16887,33 +16901,29 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Anders Janols</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Anders Janols, Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>67646045</v>
+        <v>68235645</v>
       </c>
       <c r="B154" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16921,47 +16931,41 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
+          <t>54</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>O-sidan vägen m emot Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>385203</v>
+        <v>385277</v>
       </c>
       <c r="R154" t="n">
-        <v>6858222</v>
+        <v>6857893</v>
       </c>
       <c r="S154" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16985,12 +16989,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2017-09-22</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16999,29 +17003,33 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Anders Janols</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Anders Janols, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132367502</v>
+        <v>67646045</v>
       </c>
       <c r="B155" t="n">
-        <v>78776</v>
+        <v>93235</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17029,40 +17037,47 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6437</v>
+        <v>5966</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>385349</v>
+        <v>385203</v>
       </c>
       <c r="R155" t="n">
-        <v>6857860</v>
+        <v>6858222</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17086,12 +17101,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2017-09-22</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2017-09-22</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17104,45 +17119,25 @@
       <c r="AG155" t="b">
         <v>0</v>
       </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132367474</v>
+        <v>132367502</v>
       </c>
       <c r="B156" t="n">
-        <v>79130</v>
+        <v>78776</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17150,34 +17145,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>385318</v>
+        <v>385349</v>
       </c>
       <c r="R156" t="n">
-        <v>6858113</v>
+        <v>6857860</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17218,8 +17216,29 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris var. sylvestris</t>
+        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
@@ -17236,10 +17255,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132367402</v>
+        <v>132367474</v>
       </c>
       <c r="B157" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17247,21 +17266,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17271,10 +17290,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>385403</v>
+        <v>385318</v>
       </c>
       <c r="R157" t="n">
-        <v>6857836</v>
+        <v>6858113</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17333,53 +17352,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132367443</v>
+        <v>132367402</v>
       </c>
       <c r="B158" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>385408</v>
+        <v>385403</v>
       </c>
       <c r="R158" t="n">
-        <v>6857862</v>
+        <v>6857836</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17438,7 +17449,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132367444</v>
+        <v>132367443</v>
       </c>
       <c r="B159" t="n">
         <v>57972</v>
@@ -17481,10 +17492,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>385280</v>
+        <v>385408</v>
       </c>
       <c r="R159" t="n">
-        <v>6857923</v>
+        <v>6857862</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17543,7 +17554,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132367447</v>
+        <v>132367444</v>
       </c>
       <c r="B160" t="n">
         <v>57972</v>
@@ -17576,7 +17587,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
@@ -17586,10 +17597,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>385333</v>
+        <v>385280</v>
       </c>
       <c r="R160" t="n">
-        <v>6858152</v>
+        <v>6857923</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17648,7 +17659,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132367448</v>
+        <v>132367447</v>
       </c>
       <c r="B161" t="n">
         <v>57972</v>
@@ -17691,10 +17702,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>385252</v>
+        <v>385333</v>
       </c>
       <c r="R161" t="n">
-        <v>6858060</v>
+        <v>6858152</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17753,10 +17764,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132367412</v>
+        <v>132367448</v>
       </c>
       <c r="B162" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17764,21 +17775,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17786,7 +17797,7 @@
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -17796,10 +17807,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>385208</v>
+        <v>385252</v>
       </c>
       <c r="R162" t="n">
-        <v>6858049</v>
+        <v>6858060</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17858,7 +17869,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132367417</v>
+        <v>132367412</v>
       </c>
       <c r="B163" t="n">
         <v>57162</v>
@@ -17901,10 +17912,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>385203</v>
+        <v>385208</v>
       </c>
       <c r="R163" t="n">
-        <v>6858134</v>
+        <v>6858049</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17937,11 +17948,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17968,7 +17974,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132367418</v>
+        <v>132367417</v>
       </c>
       <c r="B164" t="n">
         <v>57162</v>
@@ -18011,10 +18017,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>385198</v>
+        <v>385203</v>
       </c>
       <c r="R164" t="n">
-        <v>6858144</v>
+        <v>6858134</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18047,6 +18053,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Spelplats. Rikligt med färsk spillning inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18073,7 +18084,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132367420</v>
+        <v>132367418</v>
       </c>
       <c r="B165" t="n">
         <v>57162</v>
@@ -18116,10 +18127,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>385235</v>
+        <v>385198</v>
       </c>
       <c r="R165" t="n">
-        <v>6858146</v>
+        <v>6858144</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18178,7 +18189,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132367421</v>
+        <v>132367420</v>
       </c>
       <c r="B166" t="n">
         <v>57162</v>
@@ -18221,10 +18232,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>385249</v>
+        <v>385235</v>
       </c>
       <c r="R166" t="n">
-        <v>6858148</v>
+        <v>6858146</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18283,7 +18294,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>132367422</v>
+        <v>132367421</v>
       </c>
       <c r="B167" t="n">
         <v>57162</v>
@@ -18326,10 +18337,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>385246</v>
+        <v>385249</v>
       </c>
       <c r="R167" t="n">
-        <v>6858162</v>
+        <v>6858148</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18388,7 +18399,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132367423</v>
+        <v>132367422</v>
       </c>
       <c r="B168" t="n">
         <v>57162</v>
@@ -18431,10 +18442,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>385263</v>
+        <v>385246</v>
       </c>
       <c r="R168" t="n">
-        <v>6858153</v>
+        <v>6858162</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18493,7 +18504,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>132367424</v>
+        <v>132367423</v>
       </c>
       <c r="B169" t="n">
         <v>57162</v>
@@ -18536,10 +18547,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>385276</v>
+        <v>385263</v>
       </c>
       <c r="R169" t="n">
-        <v>6858157</v>
+        <v>6858153</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18598,7 +18609,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132367425</v>
+        <v>132367424</v>
       </c>
       <c r="B170" t="n">
         <v>57162</v>
@@ -18641,10 +18652,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>385281</v>
+        <v>385276</v>
       </c>
       <c r="R170" t="n">
-        <v>6858170</v>
+        <v>6858157</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18703,7 +18714,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132367427</v>
+        <v>132367425</v>
       </c>
       <c r="B171" t="n">
         <v>57162</v>
@@ -18746,10 +18757,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>385282</v>
+        <v>385281</v>
       </c>
       <c r="R171" t="n">
-        <v>6858105</v>
+        <v>6858170</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18782,11 +18793,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18813,7 +18819,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132367428</v>
+        <v>132367427</v>
       </c>
       <c r="B172" t="n">
         <v>57162</v>
@@ -18856,10 +18862,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>385279</v>
+        <v>385282</v>
       </c>
       <c r="R172" t="n">
-        <v>6858073</v>
+        <v>6858105</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18896,7 +18902,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
+          <t>Spelplats.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18923,7 +18929,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132367429</v>
+        <v>132367428</v>
       </c>
       <c r="B173" t="n">
         <v>57162</v>
@@ -18966,10 +18972,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>385284</v>
+        <v>385279</v>
       </c>
       <c r="R173" t="n">
-        <v>6858070</v>
+        <v>6858073</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19002,6 +19008,11 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Spelplats för tjäder. Rikligt med tjäderspillning inom en radie av 35 m.</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19028,10 +19039,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>132367471</v>
+        <v>132367429</v>
       </c>
       <c r="B174" t="n">
-        <v>58107</v>
+        <v>57162</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19039,16 +19050,16 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>205976</v>
+        <v>100138</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -19061,7 +19072,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
@@ -19071,10 +19082,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>385400</v>
+        <v>385284</v>
       </c>
       <c r="R174" t="n">
-        <v>6857831</v>
+        <v>6858070</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19133,10 +19144,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119690679</v>
+        <v>132367471</v>
       </c>
       <c r="B175" t="n">
-        <v>97983</v>
+        <v>58107</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19144,41 +19155,45 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>221945</v>
+        <v>205976</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Häggesundet, Idre, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>385352</v>
+        <v>385400</v>
       </c>
       <c r="R175" t="n">
-        <v>6857803</v>
+        <v>6857831</v>
       </c>
       <c r="S175" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19202,12 +19217,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19216,67 +19231,70 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>132367461</v>
+        <v>119690679</v>
       </c>
       <c r="B176" t="n">
-        <v>79131</v>
+        <v>97983</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>Häggesundet, Idre, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>385227</v>
+        <v>385352</v>
       </c>
       <c r="R176" t="n">
-        <v>6857907</v>
+        <v>6857803</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19300,12 +19318,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19314,25 +19332,26 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>132367463</v>
+        <v>132367461</v>
       </c>
       <c r="B177" t="n">
         <v>79131</v>
@@ -19361,19 +19380,16 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>385332</v>
+        <v>385227</v>
       </c>
       <c r="R177" t="n">
-        <v>6858162</v>
+        <v>6857907</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19414,7 +19430,6 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19433,7 +19448,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>132367464</v>
+        <v>132367463</v>
       </c>
       <c r="B178" t="n">
         <v>79131</v>
@@ -19462,16 +19477,19 @@
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>385318</v>
+        <v>385332</v>
       </c>
       <c r="R178" t="n">
-        <v>6858113</v>
+        <v>6858162</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19512,6 +19530,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19530,45 +19549,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>68235643</v>
+        <v>132367464</v>
       </c>
       <c r="B179" t="n">
-        <v>80392</v>
+        <v>79131</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>V-sidan vägen m emot Vålåberget, Dlr</t>
+          <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>385342</v>
+        <v>385318</v>
       </c>
       <c r="R179" t="n">
-        <v>6857805</v>
+        <v>6858113</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19595,17 +19614,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>På stor asp</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19616,66 +19630,61 @@
       </c>
       <c r="AG179" t="b">
         <v>0</v>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Anders Janols</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Anders Janols, Janolof Hermansson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>132367403</v>
+        <v>68235643</v>
       </c>
       <c r="B180" t="n">
-        <v>79963</v>
+        <v>80392</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>229821</v>
+        <v>229497</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Häggesundet, Dlr</t>
+          <t>V-sidan vägen m emot Vålåberget, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>385374</v>
+        <v>385342</v>
       </c>
       <c r="R180" t="n">
-        <v>6857880</v>
+        <v>6857805</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19702,12 +19711,17 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2017-09-27</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2017-09-27</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>På stor asp</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19718,23 +19732,28 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anders Janols</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anders Janols, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>132367404</v>
+        <v>132367403</v>
       </c>
       <c r="B181" t="n">
         <v>79963</v>
@@ -19769,10 +19788,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>385227</v>
+        <v>385374</v>
       </c>
       <c r="R181" t="n">
-        <v>6857907</v>
+        <v>6857880</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19831,7 +19850,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>132367405</v>
+        <v>132367404</v>
       </c>
       <c r="B182" t="n">
         <v>79963</v>
@@ -19866,10 +19885,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>385332</v>
+        <v>385227</v>
       </c>
       <c r="R182" t="n">
-        <v>6858161</v>
+        <v>6857907</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19928,7 +19947,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>132367406</v>
+        <v>132367405</v>
       </c>
       <c r="B183" t="n">
         <v>79963</v>
@@ -19957,19 +19976,16 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Häggesundet, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>385318</v>
+        <v>385332</v>
       </c>
       <c r="R183" t="n">
-        <v>6858113</v>
+        <v>6858161</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20010,7 +20026,6 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -20026,6 +20041,107 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>132367406</v>
+      </c>
+      <c r="B184" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Häggesundet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>385318</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6858113</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY184"/>
+  <dimension ref="A1:AZ184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646033</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83727</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333856</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646036</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646166</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646219</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333851</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333863</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119510275</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1761,6 +1811,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119544174</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,6 +1932,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119545863</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,6 +2061,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128788740</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2113,6 +2178,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333855</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/485205</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2327,6 +2402,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333854</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2439,6 +2519,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333858</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2551,6 +2636,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333868</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2658,6 +2748,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119509855</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2758,6 +2853,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646038</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2871,6 +2971,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646133</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2981,6 +3086,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73016490</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3092,6 +3202,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263357</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3203,6 +3318,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263358</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3314,6 +3434,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263359</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3425,6 +3550,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263360</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3527,6 +3657,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263362</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3624,6 +3759,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73767949</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3739,6 +3879,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78985131</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3862,6 +4007,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101115364</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3970,6 +4120,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646096</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4072,6 +4227,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263354</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4174,6 +4334,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68235648</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4282,6 +4447,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73016319</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4382,6 +4552,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646170</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4482,6 +4657,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646175</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4594,6 +4774,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333852</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4710,6 +4895,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74962329</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4817,6 +5007,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119509472</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4933,6 +5128,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789673</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5033,6 +5233,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72984329</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5141,6 +5346,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72984417</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5243,6 +5453,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263352</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5359,6 +5574,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119546965</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5475,6 +5695,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790475</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5575,6 +5800,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646212</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5675,6 +5905,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646215</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5783,6 +6018,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72984398</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5891,6 +6131,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73016375</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5993,6 +6238,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263356</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6100,6 +6350,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333849</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6207,6 +6462,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333850</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6314,6 +6574,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333853</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6421,6 +6686,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333857</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6528,6 +6798,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333861</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6635,6 +6910,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333867</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6751,6 +7031,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119509708</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6867,6 +7152,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119544876</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6974,6 +7264,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119546808</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7090,6 +7385,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119547231</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7197,6 +7497,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789354</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7304,6 +7609,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790071</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7411,6 +7721,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790316</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7522,6 +7837,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1334648</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7635,6 +7955,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646146</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7740,6 +8065,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72984365</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7848,6 +8178,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73016179</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7956,6 +8291,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73016285</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8058,6 +8398,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263349</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8160,6 +8505,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263355</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8267,6 +8617,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333848</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8383,6 +8738,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119509690</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8499,6 +8859,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119509957</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8615,6 +8980,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119547126</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8722,6 +9092,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789742</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8838,6 +9213,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119553050</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8950,6 +9330,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333864</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9057,6 +9442,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128789115</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9164,6 +9554,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333847</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9276,6 +9671,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333866</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9388,6 +9788,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119509835</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9501,6 +9906,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646111</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9608,6 +10018,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68235644</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9724,6 +10139,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119509925</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9826,6 +10246,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263348</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9938,6 +10363,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333859</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10035,6 +10465,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367475</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10147,6 +10582,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333869</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10259,6 +10699,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333870</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10356,6 +10801,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367389</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10453,6 +10903,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367391</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10550,6 +11005,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367392</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10647,6 +11107,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367393</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10744,6 +11209,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367394</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10841,6 +11311,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367395</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10938,6 +11413,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367396</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11035,6 +11515,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367398</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11132,6 +11617,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367399</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11229,6 +11719,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367401</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11341,6 +11836,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73333860</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11438,6 +11938,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73767948</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11561,6 +12066,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367501</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11666,6 +12176,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367446</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11771,6 +12286,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367449</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11876,6 +12396,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367450</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11981,6 +12506,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367451</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12086,6 +12616,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367452</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12191,6 +12726,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367453</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12296,6 +12836,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367455</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12401,6 +12946,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367456</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12506,6 +13056,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367457</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12611,6 +13166,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367458</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12716,6 +13276,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367413</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12821,6 +13386,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367414</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12931,6 +13501,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367415</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13036,6 +13611,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367416</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13141,6 +13721,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367430</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13246,6 +13831,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367431</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13351,6 +13941,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367432</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13456,6 +14051,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367433</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13561,6 +14161,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367434</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13666,6 +14271,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367435</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13773,6 +14383,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367468</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13880,6 +14495,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367469</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13987,6 +14607,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367470</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14092,6 +14717,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367388</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14194,6 +14824,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72984327</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14296,6 +14931,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263351</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14403,6 +15043,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367495</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14505,6 +15150,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367459</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14602,6 +15252,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121738118</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14699,6 +15354,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367462</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14796,6 +15456,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367465</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14893,6 +15558,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367466</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14990,6 +15660,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367467</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15087,6 +15762,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367407</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15184,6 +15864,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367408</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15281,6 +15966,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367409</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15378,6 +16068,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367410</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15491,6 +16186,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646143</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15594,6 +16294,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68235650</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15696,6 +16401,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263350</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15798,6 +16508,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263361</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15914,6 +16629,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119509950</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16030,6 +16750,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119510014</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16154,6 +16879,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119509537</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16273,6 +17003,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119546030</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16379,6 +17114,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68235646</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16480,6 +17220,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367411</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16588,6 +17333,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646073</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16696,6 +17446,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646050</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16804,6 +17559,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646079</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16917,6 +17677,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646048</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17023,6 +17788,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68235645</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17131,6 +17901,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67646045</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17252,6 +18027,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367502</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17349,6 +18129,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367474</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17446,6 +18231,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367402</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17551,6 +18341,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367443</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17656,6 +18451,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367444</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17761,6 +18561,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367447</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17866,6 +18671,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367448</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17971,6 +18781,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367412</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18081,6 +18896,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367417</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18186,6 +19006,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367418</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18291,6 +19116,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367420</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18396,6 +19226,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367421</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18501,6 +19336,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367422</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18606,6 +19446,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367423</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18711,6 +19556,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367424</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18816,6 +19666,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367425</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18926,6 +19781,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367427</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19036,6 +19896,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367428</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19141,6 +20006,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367429</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19246,6 +20116,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367471</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19348,6 +20223,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119690679</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19445,6 +20325,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367461</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19546,6 +20431,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367463</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19643,6 +20533,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367464</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19750,6 +20645,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68235643</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19847,6 +20747,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367403</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19944,6 +20849,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367404</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20041,6 +20951,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367405</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20142,8 +21057,198 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132367406</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -5018,7 +5018,7 @@
         <v>128789673</v>
       </c>
       <c r="B40" t="n">
-        <v>87387</v>
+        <v>87427</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -5018,7 +5018,7 @@
         <v>128789673</v>
       </c>
       <c r="B40" t="n">
-        <v>87427</v>
+        <v>87454</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
